--- a/input_processing/reg_estimates_ES_toClean/reg_employmentSelection_ES.xlsx
+++ b/input_processing/reg_estimates_ES_toClean/reg_employmentSelection_ES.xlsx
@@ -112,7 +112,7 @@
     <t>Dcpst_Partnered_L1</t>
   </si>
   <si>
-    <t>D_Children_L1</t>
+    <t>Dnc1_plus_L1</t>
   </si>
   <si>
     <t>Dhe_Fair</t>
@@ -501,76 +501,76 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>-1.5090670259752375</v>
+        <v>-1.5639821051047229</v>
       </c>
       <c r="C2">
-        <v>0.0009293715671375211</v>
+        <v>0.00078416851707491719</v>
       </c>
       <c r="D2">
-        <v>6.5939590218764928e-05</v>
+        <v>5.6510429966023098e-05</v>
       </c>
       <c r="E2">
-        <v>3.8964058081485925e-05</v>
+        <v>3.7635611863224171e-05</v>
       </c>
       <c r="F2">
-        <v>-3.6747856855345921e-07</v>
+        <v>-3.6283733161908621e-07</v>
       </c>
       <c r="G2">
-        <v>-8.2649467598979083e-05</v>
+        <v>-7.039577270400799e-05</v>
       </c>
       <c r="H2">
-        <v>0.00014546984069706937</v>
+        <v>6.5030443682439386e-05</v>
       </c>
       <c r="I2">
-        <v>1.4063014012856656e-06</v>
+        <v>1.2315124902761905e-06</v>
       </c>
       <c r="J2">
-        <v>-2.8928945045269539e-06</v>
+        <v>-1.3182613244439658e-06</v>
       </c>
       <c r="K2">
-        <v>2.7976290864514004e-05</v>
+        <v>2.1378629626480057e-05</v>
       </c>
       <c r="L2">
-        <v>-0.00032551784212786472</v>
+        <v>1.3131742014200829e-06</v>
       </c>
       <c r="M2">
-        <v>4.1338163344759515e-06</v>
+        <v>7.0215748909776632e-07</v>
       </c>
       <c r="N2">
-        <v>7.6788026095513063e-06</v>
+        <v>5.3289683635173845e-06</v>
       </c>
       <c r="O2">
-        <v>7.8073842175752648e-06</v>
+        <v>4.9740709114392471e-06</v>
       </c>
       <c r="P2">
-        <v>7.5573288102211253e-06</v>
+        <v>1.9876746229329357e-06</v>
       </c>
       <c r="Q2">
-        <v>4.2636101886433158e-06</v>
+        <v>2.8493485357173865e-06</v>
       </c>
       <c r="R2">
-        <v>5.575094918599639e-06</v>
+        <v>3.7886423362497602e-06</v>
       </c>
       <c r="S2">
-        <v>-1.4976374090251716e-06</v>
+        <v>6.4079993556668044e-07</v>
       </c>
       <c r="T2">
-        <v>7.5926666273633648e-06</v>
+        <v>5.7738368143280504e-06</v>
       </c>
       <c r="U2">
-        <v>5.7726603500998899e-06</v>
+        <v>6.4399516836442697e-06</v>
       </c>
       <c r="V2">
-        <v>6.0233655465737843e-07</v>
+        <v>-4.1962939247760638e-07</v>
       </c>
       <c r="W2">
-        <v>1.0357376828053962e-05</v>
+        <v>9.9562976616470948e-06</v>
       </c>
       <c r="X2">
-        <v>7.0355137455296531e-06</v>
+        <v>4.3000236693587114e-06</v>
       </c>
       <c r="Y2">
-        <v>-0.0010549303565369052</v>
+        <v>-0.000988449099072807</v>
       </c>
     </row>
     <row r="3">
@@ -578,76 +578,76 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>-2.1844827448042201</v>
+        <v>-2.211386952091174</v>
       </c>
       <c r="C3">
-        <v>6.5939590218764928e-05</v>
+        <v>5.6510429966023098e-05</v>
       </c>
       <c r="D3">
-        <v>0.00014204296070054702</v>
+        <v>0.00012475674006656997</v>
       </c>
       <c r="E3">
-        <v>3.7426069445123086e-06</v>
+        <v>3.017744319980551e-06</v>
       </c>
       <c r="F3">
-        <v>-3.6928959970728824e-08</v>
+        <v>-3.1029971572066036e-08</v>
       </c>
       <c r="G3">
-        <v>9.869928802659639e-06</v>
+        <v>5.1666718248454747e-06</v>
       </c>
       <c r="H3">
-        <v>-7.1111208068774362e-06</v>
+        <v>-2.2170649792781237e-06</v>
       </c>
       <c r="I3">
-        <v>-5.5831150859886049e-07</v>
+        <v>-3.4820038044586338e-07</v>
       </c>
       <c r="J3">
-        <v>-4.5753298564472916e-07</v>
+        <v>-3.9934781626548072e-07</v>
       </c>
       <c r="K3">
-        <v>-5.5584865270452876e-06</v>
+        <v>-3.5473730971942918e-06</v>
       </c>
       <c r="L3">
-        <v>7.7053693409763462e-06</v>
+        <v>-4.5310110640387007e-06</v>
       </c>
       <c r="M3">
-        <v>4.1652921443208112e-06</v>
+        <v>2.9258082990574438e-06</v>
       </c>
       <c r="N3">
-        <v>1.0034603960398511e-05</v>
+        <v>8.3163865729851295e-06</v>
       </c>
       <c r="O3">
-        <v>1.3329044110333632e-05</v>
+        <v>1.06937542840598e-05</v>
       </c>
       <c r="P3">
-        <v>1.6490280799426178e-05</v>
+        <v>1.2852034929053951e-05</v>
       </c>
       <c r="Q3">
-        <v>3.2379203620187892e-06</v>
+        <v>2.1422429351680539e-06</v>
       </c>
       <c r="R3">
-        <v>6.0245040494769332e-06</v>
+        <v>3.1392237086245195e-06</v>
       </c>
       <c r="S3">
-        <v>-2.0398014275715767e-06</v>
+        <v>-2.167488109638385e-06</v>
       </c>
       <c r="T3">
-        <v>2.5797321779958534e-06</v>
+        <v>1.7903095210014873e-06</v>
       </c>
       <c r="U3">
-        <v>-6.3772008551939256e-06</v>
+        <v>-6.2092317259988623e-06</v>
       </c>
       <c r="V3">
-        <v>-5.1722876145704883e-06</v>
+        <v>-4.7750209927426335e-06</v>
       </c>
       <c r="W3">
-        <v>6.449379893992628e-06</v>
+        <v>5.711084054726912e-06</v>
       </c>
       <c r="X3">
-        <v>1.1898052516156756e-05</v>
+        <v>9.0455988857617261e-06</v>
       </c>
       <c r="Y3">
-        <v>-0.00014452076130769679</v>
+        <v>-0.00011661033011537262</v>
       </c>
     </row>
     <row r="4">
@@ -655,76 +655,76 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>0.13647218693108973</v>
+        <v>0.16108450835381913</v>
       </c>
       <c r="C4">
-        <v>3.8964058081485925e-05</v>
+        <v>3.7635611863224171e-05</v>
       </c>
       <c r="D4">
-        <v>3.7426069445123086e-06</v>
+        <v>3.017744319980551e-06</v>
       </c>
       <c r="E4">
-        <v>1.2041441634318664e-05</v>
+        <v>1.1223192227731414e-05</v>
       </c>
       <c r="F4">
-        <v>-1.2469087893979793e-07</v>
+        <v>-1.1694061406071668e-07</v>
       </c>
       <c r="G4">
-        <v>3.2449595164339233e-05</v>
+        <v>3.3610049370447209e-05</v>
       </c>
       <c r="H4">
-        <v>1.6968785943824576e-05</v>
+        <v>3.3000727896372248e-05</v>
       </c>
       <c r="I4">
-        <v>-6.7691213419160087e-07</v>
+        <v>-7.1261346565590155e-07</v>
       </c>
       <c r="J4">
-        <v>-3.1021621967327237e-07</v>
+        <v>-6.4716647053636789e-07</v>
       </c>
       <c r="K4">
-        <v>-1.4545161526152748e-05</v>
+        <v>-8.5858951284043146e-06</v>
       </c>
       <c r="L4">
-        <v>4.6097793289385932e-05</v>
+        <v>-1.2849626124034959e-05</v>
       </c>
       <c r="M4">
-        <v>2.1742794418809269e-06</v>
+        <v>2.2092011821935227e-06</v>
       </c>
       <c r="N4">
-        <v>4.6444781233828095e-06</v>
+        <v>4.8071559307926343e-06</v>
       </c>
       <c r="O4">
-        <v>5.9720767372216962e-06</v>
+        <v>6.4945157506179902e-06</v>
       </c>
       <c r="P4">
-        <v>1.0198964825918879e-05</v>
+        <v>1.0515512924367032e-05</v>
       </c>
       <c r="Q4">
-        <v>7.2614108078310702e-07</v>
+        <v>1.4292546320355303e-06</v>
       </c>
       <c r="R4">
-        <v>5.7393906957967364e-08</v>
+        <v>1.1910413340624589e-06</v>
       </c>
       <c r="S4">
-        <v>1.0909093054176679e-07</v>
+        <v>4.8703722193004131e-07</v>
       </c>
       <c r="T4">
-        <v>8.570012247718916e-07</v>
+        <v>1.6663707198308055e-06</v>
       </c>
       <c r="U4">
-        <v>-3.8601954097936526e-08</v>
+        <v>3.2829403045377973e-07</v>
       </c>
       <c r="V4">
-        <v>-2.1091692782088654e-06</v>
+        <v>-1.5924073443884118e-06</v>
       </c>
       <c r="W4">
-        <v>4.239596629926488e-07</v>
+        <v>5.1319639636195038e-07</v>
       </c>
       <c r="X4">
-        <v>-4.8358358493944411e-07</v>
+        <v>3.5952893214442572e-07</v>
       </c>
       <c r="Y4">
-        <v>-0.0002714613930900531</v>
+        <v>-0.00025058045398493442</v>
       </c>
     </row>
     <row r="5">
@@ -732,76 +732,76 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>-0.0017092736789568205</v>
+        <v>-0.0019619241892195132</v>
       </c>
       <c r="C5">
-        <v>-3.6747856855345921e-07</v>
+        <v>-3.6283733161908621e-07</v>
       </c>
       <c r="D5">
-        <v>-3.6928959970728824e-08</v>
+        <v>-3.1029971572066036e-08</v>
       </c>
       <c r="E5">
-        <v>-1.2469087893979793e-07</v>
+        <v>-1.1694061406071668e-07</v>
       </c>
       <c r="F5">
-        <v>1.3658747726850149e-09</v>
+        <v>1.2838258062748602e-09</v>
       </c>
       <c r="G5">
-        <v>-8.4268201218108507e-08</v>
+        <v>-1.3819125315440107e-07</v>
       </c>
       <c r="H5">
-        <v>1.1015148704404287e-07</v>
+        <v>-1.2238019519191427e-07</v>
       </c>
       <c r="I5">
-        <v>1.1468194863817829e-09</v>
+        <v>2.5299765949039795e-09</v>
       </c>
       <c r="J5">
-        <v>-3.3357207361747394e-09</v>
+        <v>1.6560383094180782e-09</v>
       </c>
       <c r="K5">
-        <v>1.4307032349910165e-07</v>
+        <v>7.5035629993986244e-08</v>
       </c>
       <c r="L5">
-        <v>-5.4480093930321596e-07</v>
+        <v>1.5406217445556951e-07</v>
       </c>
       <c r="M5">
-        <v>-2.3604867355907627e-08</v>
+        <v>-2.499418773271056e-08</v>
       </c>
       <c r="N5">
-        <v>-4.7920189695280926e-08</v>
+        <v>-5.1140697227538733e-08</v>
       </c>
       <c r="O5">
-        <v>-5.3242234643711658e-08</v>
+        <v>-6.1787783522582937e-08</v>
       </c>
       <c r="P5">
-        <v>-8.3101626087108728e-08</v>
+        <v>-9.1527524773972747e-08</v>
       </c>
       <c r="Q5">
-        <v>-1.0031208201299662e-08</v>
+        <v>-1.800406641222405e-08</v>
       </c>
       <c r="R5">
-        <v>-4.9873484225541933e-09</v>
+        <v>-1.7016004741115924e-08</v>
       </c>
       <c r="S5">
-        <v>-6.5535565323370044e-10</v>
+        <v>-4.731693085333438e-09</v>
       </c>
       <c r="T5">
-        <v>-1.1251710434941407e-08</v>
+        <v>-2.0071084534453949e-08</v>
       </c>
       <c r="U5">
-        <v>3.4145696828080349e-09</v>
+        <v>-1.0096604103184873e-09</v>
       </c>
       <c r="V5">
-        <v>2.4040497405546126e-08</v>
+        <v>1.8423286454227841e-08</v>
       </c>
       <c r="W5">
-        <v>-6.8730687389085826e-09</v>
+        <v>-6.605817393049726e-09</v>
       </c>
       <c r="X5">
-        <v>1.7531733545419866e-09</v>
+        <v>-6.2584565743969258e-09</v>
       </c>
       <c r="Y5">
-        <v>2.6517524962267183e-06</v>
+        <v>2.468879685493119e-06</v>
       </c>
     </row>
     <row r="6">
@@ -809,76 +809,76 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>-0.49208265491103315</v>
+        <v>-0.41785121806622522</v>
       </c>
       <c r="C6">
-        <v>-8.2649467598979083e-05</v>
+        <v>-7.039577270400799e-05</v>
       </c>
       <c r="D6">
-        <v>9.869928802659639e-06</v>
+        <v>5.1666718248454747e-06</v>
       </c>
       <c r="E6">
-        <v>3.2449595164339233e-05</v>
+        <v>3.3610049370447209e-05</v>
       </c>
       <c r="F6">
-        <v>-8.4268201218108507e-08</v>
+        <v>-1.3819125315440107e-07</v>
       </c>
       <c r="G6">
-        <v>0.0027406658040213753</v>
+        <v>0.0024000527169121873</v>
       </c>
       <c r="H6">
-        <v>0.0011847725792919531</v>
+        <v>0.0010589709655374269</v>
       </c>
       <c r="I6">
-        <v>-5.7327128045770827e-05</v>
+        <v>-4.9910978295631958e-05</v>
       </c>
       <c r="J6">
-        <v>-2.5177852508779739e-05</v>
+        <v>-2.2347408961617136e-05</v>
       </c>
       <c r="K6">
-        <v>-2.3877242956462883e-05</v>
+        <v>-5.7516142519885521e-06</v>
       </c>
       <c r="L6">
-        <v>-0.00011092495913184315</v>
+        <v>-5.3936625776325893e-05</v>
       </c>
       <c r="M6">
-        <v>3.4651126689636989e-06</v>
+        <v>7.2504078839186843e-06</v>
       </c>
       <c r="N6">
-        <v>3.9735423690947288e-06</v>
+        <v>8.397672489878123e-06</v>
       </c>
       <c r="O6">
-        <v>3.9036656278633539e-06</v>
+        <v>1.1239893869760726e-05</v>
       </c>
       <c r="P6">
-        <v>2.9754531112494045e-05</v>
+        <v>3.2628129655894026e-05</v>
       </c>
       <c r="Q6">
-        <v>2.8620203262038928e-06</v>
+        <v>4.445423449641639e-06</v>
       </c>
       <c r="R6">
-        <v>-1.0267717028836291e-07</v>
+        <v>1.5113902613509924e-06</v>
       </c>
       <c r="S6">
-        <v>-5.1497703129434517e-06</v>
+        <v>-1.9115657197659095e-06</v>
       </c>
       <c r="T6">
-        <v>-1.1543054323875125e-05</v>
+        <v>-5.6664484676520657e-06</v>
       </c>
       <c r="U6">
-        <v>-1.700380279706316e-05</v>
+        <v>-1.1448503958290276e-05</v>
       </c>
       <c r="V6">
-        <v>-1.522079164008946e-05</v>
+        <v>-1.0149676103076937e-05</v>
       </c>
       <c r="W6">
-        <v>8.6955938711988e-06</v>
+        <v>6.7976865026077628e-06</v>
       </c>
       <c r="X6">
-        <v>8.379934847303358e-06</v>
+        <v>6.1670635498055813e-06</v>
       </c>
       <c r="Y6">
-        <v>-0.0013105522706281948</v>
+        <v>-0.0012440409183924889</v>
       </c>
     </row>
     <row r="7">
@@ -886,76 +886,76 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-0.46536382102111468</v>
+        <v>-0.56218065557254982</v>
       </c>
       <c r="C7">
-        <v>0.00014546984069706937</v>
+        <v>6.5030443682439386e-05</v>
       </c>
       <c r="D7">
-        <v>-7.1111208068774362e-06</v>
+        <v>-2.2170649792781237e-06</v>
       </c>
       <c r="E7">
-        <v>1.6968785943824576e-05</v>
+        <v>3.3000727896372248e-05</v>
       </c>
       <c r="F7">
-        <v>1.1015148704404287e-07</v>
+        <v>-1.2238019519191427e-07</v>
       </c>
       <c r="G7">
-        <v>0.0011847725792919531</v>
+        <v>0.0010589709655374269</v>
       </c>
       <c r="H7">
-        <v>0.0025549319742349647</v>
+        <v>0.0021822171272897709</v>
       </c>
       <c r="I7">
-        <v>-2.5353589372427201e-05</v>
+        <v>-2.2490125244901001e-05</v>
       </c>
       <c r="J7">
-        <v>-5.1657051188189589e-05</v>
+        <v>-4.4131453235267739e-05</v>
       </c>
       <c r="K7">
-        <v>-1.4611121202416772e-05</v>
+        <v>1.2559438219915094e-05</v>
       </c>
       <c r="L7">
-        <v>-0.00082336219691097723</v>
+        <v>-0.00010929767442597621</v>
       </c>
       <c r="M7">
-        <v>9.1695621981783713e-06</v>
+        <v>1.213231572676465e-05</v>
       </c>
       <c r="N7">
-        <v>1.1024378804380761e-06</v>
+        <v>1.0834434063884267e-05</v>
       </c>
       <c r="O7">
-        <v>-6.7846411801802064e-06</v>
+        <v>9.6105601958717439e-06</v>
       </c>
       <c r="P7">
-        <v>3.1322992523865581e-05</v>
+        <v>3.8898908288649526e-05</v>
       </c>
       <c r="Q7">
-        <v>4.2939548835341625e-06</v>
+        <v>7.9633759505789005e-06</v>
       </c>
       <c r="R7">
-        <v>-1.1069092011884696e-05</v>
+        <v>-5.5233640045138422e-06</v>
       </c>
       <c r="S7">
-        <v>-2.902826063173506e-05</v>
+        <v>-1.7014921598287376e-05</v>
       </c>
       <c r="T7">
-        <v>-2.3206953553328635e-05</v>
+        <v>-1.3287409139150585e-05</v>
       </c>
       <c r="U7">
-        <v>-5.5925882771811329e-05</v>
+        <v>-3.5950549136931192e-05</v>
       </c>
       <c r="V7">
-        <v>-2.8529712476297917e-05</v>
+        <v>-1.9387934875485656e-05</v>
       </c>
       <c r="W7">
-        <v>1.5581745572557169e-05</v>
+        <v>1.5502196411901637e-05</v>
       </c>
       <c r="X7">
-        <v>1.6524604911675522e-05</v>
+        <v>1.5542241449421002e-05</v>
       </c>
       <c r="Y7">
-        <v>-0.0010286658564525621</v>
+        <v>-0.0012388207517911992</v>
       </c>
     </row>
     <row r="8">
@@ -963,76 +963,76 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.0081780660329256252</v>
+        <v>0.005073429261713152</v>
       </c>
       <c r="C8">
-        <v>1.4063014012856656e-06</v>
+        <v>1.2315124902761905e-06</v>
       </c>
       <c r="D8">
-        <v>-5.5831150859886049e-07</v>
+        <v>-3.4820038044586338e-07</v>
       </c>
       <c r="E8">
-        <v>-6.7691213419160087e-07</v>
+        <v>-7.1261346565590155e-07</v>
       </c>
       <c r="F8">
-        <v>1.1468194863817829e-09</v>
+        <v>2.5299765949039795e-09</v>
       </c>
       <c r="G8">
-        <v>-5.7327128045770827e-05</v>
+        <v>-4.9910978295631958e-05</v>
       </c>
       <c r="H8">
-        <v>-2.5353589372427201e-05</v>
+        <v>-2.2490125244901001e-05</v>
       </c>
       <c r="I8">
-        <v>1.3023850692425051e-06</v>
+        <v>1.1265527512108246e-06</v>
       </c>
       <c r="J8">
-        <v>5.8332498396481159e-07</v>
+        <v>5.1285198580812575e-07</v>
       </c>
       <c r="K8">
-        <v>4.636455775020252e-07</v>
+        <v>6.3907408000988397e-08</v>
       </c>
       <c r="L8">
-        <v>2.4606077090752738e-06</v>
+        <v>1.2225484190903565e-06</v>
       </c>
       <c r="M8">
-        <v>-2.6253920270744545e-08</v>
+        <v>-1.2074615915184401e-07</v>
       </c>
       <c r="N8">
-        <v>-3.2402927123500821e-08</v>
+        <v>-1.195793569453512e-07</v>
       </c>
       <c r="O8">
-        <v>1.9240449379248079e-07</v>
+        <v>-4.2281365264753337e-09</v>
       </c>
       <c r="P8">
-        <v>-1.7569416165642021e-07</v>
+        <v>-3.1814625114640597e-07</v>
       </c>
       <c r="Q8">
-        <v>5.7718601815146839e-08</v>
+        <v>-1.7877272226906577e-09</v>
       </c>
       <c r="R8">
-        <v>1.0356089281036475e-07</v>
+        <v>1.6470714984843657e-08</v>
       </c>
       <c r="S8">
-        <v>1.1168479755137243e-07</v>
+        <v>3.2785114306925699e-08</v>
       </c>
       <c r="T8">
-        <v>1.7111120631175475e-07</v>
+        <v>3.6338635616813778e-08</v>
       </c>
       <c r="U8">
-        <v>3.0278273217855394e-07</v>
+        <v>1.784541399021381e-07</v>
       </c>
       <c r="V8">
-        <v>2.5497860948027182e-07</v>
+        <v>1.5115619323630546e-07</v>
       </c>
       <c r="W8">
-        <v>-1.0280251246839305e-07</v>
+        <v>-8.0470731857337259e-08</v>
       </c>
       <c r="X8">
-        <v>-5.2568120058640001e-08</v>
+        <v>-5.4897924928440445e-08</v>
       </c>
       <c r="Y8">
-        <v>2.6685349817706093e-05</v>
+        <v>2.5491124340933407e-05</v>
       </c>
     </row>
     <row r="9">
@@ -1040,76 +1040,76 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>0.0034527525758931412</v>
+        <v>0.0034851226663128172</v>
       </c>
       <c r="C9">
-        <v>-2.8928945045269539e-06</v>
+        <v>-1.3182613244439658e-06</v>
       </c>
       <c r="D9">
-        <v>-4.5753298564472916e-07</v>
+        <v>-3.9934781626548072e-07</v>
       </c>
       <c r="E9">
-        <v>-3.1021621967327237e-07</v>
+        <v>-6.4716647053636789e-07</v>
       </c>
       <c r="F9">
-        <v>-3.3357207361747394e-09</v>
+        <v>1.6560383094180782e-09</v>
       </c>
       <c r="G9">
-        <v>-2.5177852508779739e-05</v>
+        <v>-2.2347408961617136e-05</v>
       </c>
       <c r="H9">
-        <v>-5.1657051188189589e-05</v>
+        <v>-4.4131453235267739e-05</v>
       </c>
       <c r="I9">
-        <v>5.8332498396481159e-07</v>
+        <v>5.1285198580812575e-07</v>
       </c>
       <c r="J9">
-        <v>1.1275439917184828e-06</v>
+        <v>9.6431705659565206e-07</v>
       </c>
       <c r="K9">
-        <v>1.2998879535794256e-07</v>
+        <v>-4.4040107225794681e-07</v>
       </c>
       <c r="L9">
-        <v>1.5869858793830436e-05</v>
+        <v>2.3358430651709334e-06</v>
       </c>
       <c r="M9">
-        <v>-2.3012902127943347e-07</v>
+        <v>-3.1838925744568299e-07</v>
       </c>
       <c r="N9">
-        <v>2.5283880043404898e-08</v>
+        <v>-2.2587083220543757e-07</v>
       </c>
       <c r="O9">
-        <v>6.4985493886801833e-07</v>
+        <v>1.7742873602856898e-07</v>
       </c>
       <c r="P9">
-        <v>1.2444968043174353e-07</v>
+        <v>-2.3193825979991529e-07</v>
       </c>
       <c r="Q9">
-        <v>8.3425119060992701e-08</v>
+        <v>-2.5994502078208996e-08</v>
       </c>
       <c r="R9">
-        <v>5.6141453734698148e-07</v>
+        <v>3.6804642476238213e-07</v>
       </c>
       <c r="S9">
-        <v>3.6555775350960959e-07</v>
+        <v>1.4522606577529837e-07</v>
       </c>
       <c r="T9">
-        <v>4.5347012479434286e-07</v>
+        <v>2.406435429129941e-07</v>
       </c>
       <c r="U9">
-        <v>7.974185894975233e-07</v>
+        <v>4.2919121904164667e-07</v>
       </c>
       <c r="V9">
-        <v>4.3578735223408231e-07</v>
+        <v>2.6854037537018175e-07</v>
       </c>
       <c r="W9">
-        <v>-1.5285424393132197e-07</v>
+        <v>-2.0894545913527595e-07</v>
       </c>
       <c r="X9">
-        <v>-3.9044512839800034e-08</v>
+        <v>-1.2396507342169301e-07</v>
       </c>
       <c r="Y9">
-        <v>1.9701823854459415e-05</v>
+        <v>2.4221675374156273e-05</v>
       </c>
     </row>
     <row r="10">
@@ -1117,76 +1117,76 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>-0.084203674159357533</v>
+        <v>-0.047879868588837291</v>
       </c>
       <c r="C10">
-        <v>2.7976290864514004e-05</v>
+        <v>2.1378629626480057e-05</v>
       </c>
       <c r="D10">
-        <v>-5.5584865270452876e-06</v>
+        <v>-3.5473730971942918e-06</v>
       </c>
       <c r="E10">
-        <v>-1.4545161526152748e-05</v>
+        <v>-8.5858951284043146e-06</v>
       </c>
       <c r="F10">
-        <v>1.4307032349910165e-07</v>
+        <v>7.5035629993986244e-08</v>
       </c>
       <c r="G10">
-        <v>-2.3877242956462883e-05</v>
+        <v>-5.7516142519885521e-06</v>
       </c>
       <c r="H10">
-        <v>-1.4611121202416772e-05</v>
+        <v>1.2559438219915094e-05</v>
       </c>
       <c r="I10">
-        <v>4.636455775020252e-07</v>
+        <v>6.3907408000988397e-08</v>
       </c>
       <c r="J10">
-        <v>1.2998879535794256e-07</v>
+        <v>-4.4040107225794681e-07</v>
       </c>
       <c r="K10">
-        <v>0.00017177482479434065</v>
+        <v>0.00016652515357767087</v>
       </c>
       <c r="L10">
-        <v>-2.9636703580534476e-05</v>
+        <v>-5.1532009367745993e-05</v>
       </c>
       <c r="M10">
-        <v>-9.0753645074032009e-06</v>
+        <v>-6.5288587245640478e-06</v>
       </c>
       <c r="N10">
-        <v>-2.1792949305867839e-05</v>
+        <v>-1.5842017212085519e-05</v>
       </c>
       <c r="O10">
-        <v>-3.2235304277782257e-05</v>
+        <v>-2.364816035365556e-05</v>
       </c>
       <c r="P10">
-        <v>-3.1327524633515145e-05</v>
+        <v>-2.2938093223347163e-05</v>
       </c>
       <c r="Q10">
-        <v>-5.9580706376392294e-06</v>
+        <v>-2.7587541248345288e-06</v>
       </c>
       <c r="R10">
-        <v>1.3416188361933879e-06</v>
+        <v>2.9565684692139051e-06</v>
       </c>
       <c r="S10">
-        <v>-5.2425375587558747e-06</v>
+        <v>-3.3105430912645903e-06</v>
       </c>
       <c r="T10">
-        <v>-5.1141406128629676e-06</v>
+        <v>-2.5221500356785842e-06</v>
       </c>
       <c r="U10">
-        <v>-2.3615602021981738e-06</v>
+        <v>3.3716769143997658e-08</v>
       </c>
       <c r="V10">
-        <v>1.3846801038372074e-05</v>
+        <v>1.1505396567742331e-05</v>
       </c>
       <c r="W10">
-        <v>-1.3345004104120418e-06</v>
+        <v>-8.8210213924130594e-07</v>
       </c>
       <c r="X10">
-        <v>-6.8615739832329165e-07</v>
+        <v>4.0556182386317124e-07</v>
       </c>
       <c r="Y10">
-        <v>0.00026755006816287787</v>
+        <v>0.00016157160861471681</v>
       </c>
     </row>
     <row r="11">
@@ -1194,76 +1194,76 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>-0.77192596621563891</v>
+        <v>-0.11382159883560995</v>
       </c>
       <c r="C11">
-        <v>-0.00032551784212786472</v>
+        <v>1.3131742014200829e-06</v>
       </c>
       <c r="D11">
-        <v>7.7053693409763462e-06</v>
+        <v>-4.5310110640387007e-06</v>
       </c>
       <c r="E11">
-        <v>4.6097793289385932e-05</v>
+        <v>-1.2849626124034959e-05</v>
       </c>
       <c r="F11">
-        <v>-5.4480093930321596e-07</v>
+        <v>1.5406217445556951e-07</v>
       </c>
       <c r="G11">
-        <v>-0.00011092495913184315</v>
+        <v>-5.3936625776325893e-05</v>
       </c>
       <c r="H11">
-        <v>-0.00082336219691097723</v>
+        <v>-0.00010929767442597621</v>
       </c>
       <c r="I11">
-        <v>2.4606077090752738e-06</v>
+        <v>1.2225484190903565e-06</v>
       </c>
       <c r="J11">
-        <v>1.5869858793830436e-05</v>
+        <v>2.3358430651709334e-06</v>
       </c>
       <c r="K11">
-        <v>-2.9636703580534476e-05</v>
+        <v>-5.1532009367745993e-05</v>
       </c>
       <c r="L11">
-        <v>0.0057540055331795365</v>
+        <v>0.00017559153000910627</v>
       </c>
       <c r="M11">
-        <v>3.8612528387516943e-06</v>
+        <v>-5.0293050855584149e-06</v>
       </c>
       <c r="N11">
-        <v>1.3955470321749656e-05</v>
+        <v>-1.0765851420839752e-05</v>
       </c>
       <c r="O11">
-        <v>1.7397590282903228e-05</v>
+        <v>-1.6521843496977614e-05</v>
       </c>
       <c r="P11">
-        <v>4.4750517046325869e-06</v>
+        <v>-1.8568543181393855e-05</v>
       </c>
       <c r="Q11">
-        <v>-4.1510337420614264e-06</v>
+        <v>-7.2214097515647985e-06</v>
       </c>
       <c r="R11">
-        <v>4.2027737865672014e-06</v>
+        <v>-7.3758746655500656e-06</v>
       </c>
       <c r="S11">
-        <v>1.6923700458096433e-05</v>
+        <v>-4.312334110483636e-06</v>
       </c>
       <c r="T11">
-        <v>4.0933953295506993e-06</v>
+        <v>-7.1298840373377753e-06</v>
       </c>
       <c r="U11">
-        <v>3.2814391434223279e-05</v>
+        <v>-6.2404596342951593e-06</v>
       </c>
       <c r="V11">
-        <v>1.6026598790000384e-05</v>
+        <v>-2.7339106883459257e-07</v>
       </c>
       <c r="W11">
-        <v>-7.2863947464846939e-06</v>
+        <v>-2.0963572648921408e-06</v>
       </c>
       <c r="X11">
-        <v>-2.9528375826878163e-05</v>
+        <v>-5.0720331981070855e-06</v>
       </c>
       <c r="Y11">
-        <v>-0.00088185876998194172</v>
+        <v>0.00022785976442534005</v>
       </c>
     </row>
     <row r="12">
@@ -1271,76 +1271,76 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>0.24633238664013499</v>
+        <v>0.25102880918005366</v>
       </c>
       <c r="C12">
-        <v>4.1338163344759515e-06</v>
+        <v>7.0215748909776632e-07</v>
       </c>
       <c r="D12">
-        <v>4.1652921443208112e-06</v>
+        <v>2.9258082990574438e-06</v>
       </c>
       <c r="E12">
-        <v>2.1742794418809269e-06</v>
+        <v>2.2092011821935227e-06</v>
       </c>
       <c r="F12">
-        <v>-2.3604867355907627e-08</v>
+        <v>-2.499418773271056e-08</v>
       </c>
       <c r="G12">
-        <v>3.4651126689636989e-06</v>
+        <v>7.2504078839186843e-06</v>
       </c>
       <c r="H12">
-        <v>9.1695621981783713e-06</v>
+        <v>1.213231572676465e-05</v>
       </c>
       <c r="I12">
-        <v>-2.6253920270744545e-08</v>
+        <v>-1.2074615915184401e-07</v>
       </c>
       <c r="J12">
-        <v>-2.3012902127943347e-07</v>
+        <v>-3.1838925744568299e-07</v>
       </c>
       <c r="K12">
-        <v>-9.0753645074032009e-06</v>
+        <v>-6.5288587245640478e-06</v>
       </c>
       <c r="L12">
-        <v>3.8612528387516943e-06</v>
+        <v>-5.0293050855584149e-06</v>
       </c>
       <c r="M12">
-        <v>0.0052078460204913486</v>
+        <v>0.0043513499012550767</v>
       </c>
       <c r="N12">
-        <v>0.0043007060841178772</v>
+        <v>0.0035703204687164009</v>
       </c>
       <c r="O12">
-        <v>0.0043000530682319642</v>
+        <v>0.0035693703197701211</v>
       </c>
       <c r="P12">
-        <v>0.004299143650955994</v>
+        <v>0.0035680951857395928</v>
       </c>
       <c r="Q12">
-        <v>4.536155307830573e-06</v>
+        <v>7.244894926365883e-06</v>
       </c>
       <c r="R12">
-        <v>1.2774472026211097e-05</v>
+        <v>1.2911383648716147e-05</v>
       </c>
       <c r="S12">
-        <v>1.7062806309530191e-06</v>
+        <v>4.5776914590981024e-06</v>
       </c>
       <c r="T12">
-        <v>7.8058066934647512e-06</v>
+        <v>9.7991299640515841e-06</v>
       </c>
       <c r="U12">
-        <v>2.0303412738913006e-06</v>
+        <v>2.6405051996475392e-06</v>
       </c>
       <c r="V12">
-        <v>9.6240102269608946e-06</v>
+        <v>1.0781726965084075e-05</v>
       </c>
       <c r="W12">
-        <v>-2.1881698121816384e-06</v>
+        <v>-2.659226834504982e-06</v>
       </c>
       <c r="X12">
-        <v>4.3516053563866506e-06</v>
+        <v>2.8522856670761173e-06</v>
       </c>
       <c r="Y12">
-        <v>-0.0043468763354454132</v>
+        <v>-0.0036145091879106</v>
       </c>
     </row>
     <row r="13">
@@ -1348,76 +1348,76 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>0.50923638874010424</v>
+        <v>0.520951020332732</v>
       </c>
       <c r="C13">
-        <v>7.6788026095513063e-06</v>
+        <v>5.3289683635173845e-06</v>
       </c>
       <c r="D13">
-        <v>1.0034603960398511e-05</v>
+        <v>8.3163865729851295e-06</v>
       </c>
       <c r="E13">
-        <v>4.6444781233828095e-06</v>
+        <v>4.8071559307926343e-06</v>
       </c>
       <c r="F13">
-        <v>-4.7920189695280926e-08</v>
+        <v>-5.1140697227538733e-08</v>
       </c>
       <c r="G13">
-        <v>3.9735423690947288e-06</v>
+        <v>8.397672489878123e-06</v>
       </c>
       <c r="H13">
-        <v>1.1024378804380761e-06</v>
+        <v>1.0834434063884267e-05</v>
       </c>
       <c r="I13">
-        <v>-3.2402927123500821e-08</v>
+        <v>-1.195793569453512e-07</v>
       </c>
       <c r="J13">
-        <v>2.5283880043404898e-08</v>
+        <v>-2.2587083220543757e-07</v>
       </c>
       <c r="K13">
-        <v>-2.1792949305867839e-05</v>
+        <v>-1.5842017212085519e-05</v>
       </c>
       <c r="L13">
-        <v>1.3955470321749656e-05</v>
+        <v>-1.0765851420839752e-05</v>
       </c>
       <c r="M13">
-        <v>0.0043007060841178772</v>
+        <v>0.0035703204687164009</v>
       </c>
       <c r="N13">
-        <v>0.0044757530923939734</v>
+        <v>0.0037206624654834916</v>
       </c>
       <c r="O13">
-        <v>0.0043059613841144005</v>
+        <v>0.0035747873517132777</v>
       </c>
       <c r="P13">
-        <v>0.0043075386652724193</v>
+        <v>0.0035760122346091888</v>
       </c>
       <c r="Q13">
-        <v>-1.6781364933534645e-06</v>
+        <v>1.8399964780818195e-06</v>
       </c>
       <c r="R13">
-        <v>4.2312743863822614e-06</v>
+        <v>5.6532644853852615e-06</v>
       </c>
       <c r="S13">
-        <v>-7.4026137389406044e-06</v>
+        <v>-2.6796835551761859e-06</v>
       </c>
       <c r="T13">
-        <v>4.9934415580902061e-06</v>
+        <v>6.9866038140402347e-06</v>
       </c>
       <c r="U13">
-        <v>-6.510458729558588e-06</v>
+        <v>-4.7112244350561817e-06</v>
       </c>
       <c r="V13">
-        <v>-5.4920975788681298e-06</v>
+        <v>-8.029157398520406e-07</v>
       </c>
       <c r="W13">
-        <v>-7.1226765481819864e-06</v>
+        <v>-6.8262886919653498e-06</v>
       </c>
       <c r="X13">
-        <v>3.2200834082005357e-06</v>
+        <v>2.2617914458459829e-06</v>
       </c>
       <c r="Y13">
-        <v>-0.0044000963654414939</v>
+        <v>-0.0036696532994213793</v>
       </c>
     </row>
     <row r="14">
@@ -1425,76 +1425,76 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0.65043610121229956</v>
+        <v>0.67871006496297759</v>
       </c>
       <c r="C14">
-        <v>7.8073842175752648e-06</v>
+        <v>4.9740709114392471e-06</v>
       </c>
       <c r="D14">
-        <v>1.3329044110333632e-05</v>
+        <v>1.06937542840598e-05</v>
       </c>
       <c r="E14">
-        <v>5.9720767372216962e-06</v>
+        <v>6.4945157506179902e-06</v>
       </c>
       <c r="F14">
-        <v>-5.3242234643711658e-08</v>
+        <v>-6.1787783522582937e-08</v>
       </c>
       <c r="G14">
-        <v>3.9036656278633539e-06</v>
+        <v>1.1239893869760726e-05</v>
       </c>
       <c r="H14">
-        <v>-6.7846411801802064e-06</v>
+        <v>9.6105601958717439e-06</v>
       </c>
       <c r="I14">
-        <v>1.9240449379248079e-07</v>
+        <v>-4.2281365264753337e-09</v>
       </c>
       <c r="J14">
-        <v>6.4985493886801833e-07</v>
+        <v>1.7742873602856898e-07</v>
       </c>
       <c r="K14">
-        <v>-3.2235304277782257e-05</v>
+        <v>-2.364816035365556e-05</v>
       </c>
       <c r="L14">
-        <v>1.7397590282903228e-05</v>
+        <v>-1.6521843496977614e-05</v>
       </c>
       <c r="M14">
-        <v>0.0043000530682319642</v>
+        <v>0.0035693703197701211</v>
       </c>
       <c r="N14">
-        <v>0.0043059613841144005</v>
+        <v>0.0035747873517132777</v>
       </c>
       <c r="O14">
-        <v>0.0043705842032816982</v>
+        <v>0.0036312711649776168</v>
       </c>
       <c r="P14">
-        <v>0.0043292655799181678</v>
+        <v>0.0035940650119536226</v>
       </c>
       <c r="Q14">
-        <v>-1.0402552457463308e-05</v>
+        <v>-4.5278148072298315e-06</v>
       </c>
       <c r="R14">
-        <v>-2.0015504535873709e-06</v>
+        <v>1.4764703699844011e-06</v>
       </c>
       <c r="S14">
-        <v>-1.6216094678504019e-05</v>
+        <v>-9.7091994508373408e-06</v>
       </c>
       <c r="T14">
-        <v>-2.9173039289013191e-07</v>
+        <v>3.7743477250128951e-06</v>
       </c>
       <c r="U14">
-        <v>-1.2557784687938035e-05</v>
+        <v>-9.2885581969664831e-06</v>
       </c>
       <c r="V14">
-        <v>1.4695235030674021e-06</v>
+        <v>5.0788656043477425e-06</v>
       </c>
       <c r="W14">
-        <v>-6.2455986156359512e-06</v>
+        <v>-7.1179462224887442e-06</v>
       </c>
       <c r="X14">
-        <v>7.2239502471942131e-06</v>
+        <v>4.895541103505398e-06</v>
       </c>
       <c r="Y14">
-        <v>-0.0044612043691336827</v>
+        <v>-0.0037313408862465368</v>
       </c>
     </row>
     <row r="15">
@@ -1502,76 +1502,76 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>0.61675190926548218</v>
+        <v>0.67172158065640086</v>
       </c>
       <c r="C15">
-        <v>7.5573288102211253e-06</v>
+        <v>1.9876746229329357e-06</v>
       </c>
       <c r="D15">
-        <v>1.6490280799426178e-05</v>
+        <v>1.2852034929053951e-05</v>
       </c>
       <c r="E15">
-        <v>1.0198964825918879e-05</v>
+        <v>1.0515512924367032e-05</v>
       </c>
       <c r="F15">
-        <v>-8.3101626087108728e-08</v>
+        <v>-9.1527524773972747e-08</v>
       </c>
       <c r="G15">
-        <v>2.9754531112494045e-05</v>
+        <v>3.2628129655894026e-05</v>
       </c>
       <c r="H15">
-        <v>3.1322992523865581e-05</v>
+        <v>3.8898908288649526e-05</v>
       </c>
       <c r="I15">
-        <v>-1.7569416165642021e-07</v>
+        <v>-3.1814625114640597e-07</v>
       </c>
       <c r="J15">
-        <v>1.2444968043174353e-07</v>
+        <v>-2.3193825979991529e-07</v>
       </c>
       <c r="K15">
-        <v>-3.1327524633515145e-05</v>
+        <v>-2.2938093223347163e-05</v>
       </c>
       <c r="L15">
-        <v>4.4750517046325869e-06</v>
+        <v>-1.8568543181393855e-05</v>
       </c>
       <c r="M15">
-        <v>0.004299143650955994</v>
+        <v>0.0035680951857395928</v>
       </c>
       <c r="N15">
-        <v>0.0043075386652724193</v>
+        <v>0.0035760122346091888</v>
       </c>
       <c r="O15">
-        <v>0.0043292655799181678</v>
+        <v>0.0035940650119536226</v>
       </c>
       <c r="P15">
-        <v>0.0045274589691009911</v>
+        <v>0.0037737378252681989</v>
       </c>
       <c r="Q15">
-        <v>-1.8721883572335427e-05</v>
+        <v>-1.2042210257219639e-05</v>
       </c>
       <c r="R15">
-        <v>-1.2408239390042952e-05</v>
+        <v>-7.5414786816058968e-06</v>
       </c>
       <c r="S15">
-        <v>-2.0682266280592468e-05</v>
+        <v>-1.3507510707194651e-05</v>
       </c>
       <c r="T15">
-        <v>-1.5831521131190614e-05</v>
+        <v>-8.9710496959651904e-06</v>
       </c>
       <c r="U15">
-        <v>-2.4676664520045875e-05</v>
+        <v>-1.9415624512475184e-05</v>
       </c>
       <c r="V15">
-        <v>-1.0234499504098115e-05</v>
+        <v>-5.5689124964271585e-06</v>
       </c>
       <c r="W15">
-        <v>-1.0576543168340934e-05</v>
+        <v>-1.1797723467004485e-05</v>
       </c>
       <c r="X15">
-        <v>7.1690052865917662e-06</v>
+        <v>4.4898699790875024e-06</v>
       </c>
       <c r="Y15">
-        <v>-0.0045967698067886833</v>
+        <v>-0.0038544324578319118</v>
       </c>
     </row>
     <row r="16">
@@ -1579,76 +1579,76 @@
         <v>36</v>
       </c>
       <c r="B16">
-        <v>0.043299145993451374</v>
+        <v>0.073692222743085373</v>
       </c>
       <c r="C16">
-        <v>4.2636101886433158e-06</v>
+        <v>2.8493485357173865e-06</v>
       </c>
       <c r="D16">
-        <v>3.2379203620187892e-06</v>
+        <v>2.1422429351680539e-06</v>
       </c>
       <c r="E16">
-        <v>7.2614108078310702e-07</v>
+        <v>1.4292546320355303e-06</v>
       </c>
       <c r="F16">
-        <v>-1.0031208201299662e-08</v>
+        <v>-1.800406641222405e-08</v>
       </c>
       <c r="G16">
-        <v>2.8620203262038928e-06</v>
+        <v>4.445423449641639e-06</v>
       </c>
       <c r="H16">
-        <v>4.2939548835341625e-06</v>
+        <v>7.9633759505789005e-06</v>
       </c>
       <c r="I16">
-        <v>5.7718601815146839e-08</v>
+        <v>-1.7877272226906577e-09</v>
       </c>
       <c r="J16">
-        <v>8.3425119060992701e-08</v>
+        <v>-2.5994502078208996e-08</v>
       </c>
       <c r="K16">
-        <v>-5.9580706376392294e-06</v>
+        <v>-2.7587541248345288e-06</v>
       </c>
       <c r="L16">
-        <v>-4.1510337420614264e-06</v>
+        <v>-7.2214097515647985e-06</v>
       </c>
       <c r="M16">
-        <v>4.536155307830573e-06</v>
+        <v>7.244894926365883e-06</v>
       </c>
       <c r="N16">
-        <v>-1.6781364933534645e-06</v>
+        <v>1.8399964780818195e-06</v>
       </c>
       <c r="O16">
-        <v>-1.0402552457463308e-05</v>
+        <v>-4.5278148072298315e-06</v>
       </c>
       <c r="P16">
-        <v>-1.8721883572335427e-05</v>
+        <v>-1.2042210257219639e-05</v>
       </c>
       <c r="Q16">
-        <v>0.00044138068346047545</v>
+        <v>0.00039857818172638548</v>
       </c>
       <c r="R16">
-        <v>0.00023213212747061733</v>
+        <v>0.00020916679615355069</v>
       </c>
       <c r="S16">
-        <v>0.00023043838941843884</v>
+        <v>0.00020784636961141418</v>
       </c>
       <c r="T16">
-        <v>0.00023131015545587539</v>
+        <v>0.00020863600195786676</v>
       </c>
       <c r="U16">
-        <v>0.00022998618130566442</v>
+        <v>0.00020758448624725895</v>
       </c>
       <c r="V16">
-        <v>0.00022914413497782379</v>
+        <v>0.00020675818443960476</v>
       </c>
       <c r="W16">
-        <v>1.0728623583437715e-06</v>
+        <v>1.375355982132621e-06</v>
       </c>
       <c r="X16">
-        <v>-2.5669139939127136e-07</v>
+        <v>8.2531002632138115e-08</v>
       </c>
       <c r="Y16">
-        <v>-0.00023393594692061324</v>
+        <v>-0.00022892873610641688</v>
       </c>
     </row>
     <row r="17">
@@ -1656,76 +1656,76 @@
         <v>37</v>
       </c>
       <c r="B17">
-        <v>-0.016221274505915744</v>
+        <v>0.05126475579648359</v>
       </c>
       <c r="C17">
-        <v>5.575094918599639e-06</v>
+        <v>3.7886423362497602e-06</v>
       </c>
       <c r="D17">
-        <v>6.0245040494769332e-06</v>
+        <v>3.1392237086245195e-06</v>
       </c>
       <c r="E17">
-        <v>5.7393906957967364e-08</v>
+        <v>1.1910413340624589e-06</v>
       </c>
       <c r="F17">
-        <v>-4.9873484225541933e-09</v>
+        <v>-1.7016004741115924e-08</v>
       </c>
       <c r="G17">
-        <v>-1.0267717028836291e-07</v>
+        <v>1.5113902613509924e-06</v>
       </c>
       <c r="H17">
-        <v>-1.1069092011884696e-05</v>
+        <v>-5.5233640045138422e-06</v>
       </c>
       <c r="I17">
-        <v>1.0356089281036475e-07</v>
+        <v>1.6470714984843657e-08</v>
       </c>
       <c r="J17">
-        <v>5.6141453734698148e-07</v>
+        <v>3.6804642476238213e-07</v>
       </c>
       <c r="K17">
-        <v>1.3416188361933879e-06</v>
+        <v>2.9565684692139051e-06</v>
       </c>
       <c r="L17">
-        <v>4.2027737865672014e-06</v>
+        <v>-7.3758746655500656e-06</v>
       </c>
       <c r="M17">
-        <v>1.2774472026211097e-05</v>
+        <v>1.2911383648716147e-05</v>
       </c>
       <c r="N17">
-        <v>4.2312743863822614e-06</v>
+        <v>5.6532644853852615e-06</v>
       </c>
       <c r="O17">
-        <v>-2.0015504535873709e-06</v>
+        <v>1.4764703699844011e-06</v>
       </c>
       <c r="P17">
-        <v>-1.2408239390042952e-05</v>
+        <v>-7.5414786816058968e-06</v>
       </c>
       <c r="Q17">
-        <v>0.00023213212747061733</v>
+        <v>0.00020916679615355069</v>
       </c>
       <c r="R17">
-        <v>0.00053377643211219414</v>
+        <v>0.00047853684428967132</v>
       </c>
       <c r="S17">
-        <v>0.00022982842768083639</v>
+        <v>0.00020734517434658174</v>
       </c>
       <c r="T17">
-        <v>0.00023142961487592555</v>
+        <v>0.00020873398824343837</v>
       </c>
       <c r="U17">
-        <v>0.00022947164752944421</v>
+        <v>0.00020723874029475849</v>
       </c>
       <c r="V17">
-        <v>0.0002297127653882869</v>
+        <v>0.00020723423948553212</v>
       </c>
       <c r="W17">
-        <v>-1.843736926814521e-06</v>
+        <v>-8.9308460403442874e-07</v>
       </c>
       <c r="X17">
-        <v>-7.7675370219925999e-06</v>
+        <v>-4.7206916125607647e-06</v>
       </c>
       <c r="Y17">
-        <v>-0.00023047971297573627</v>
+        <v>-0.00023084883665623171</v>
       </c>
     </row>
     <row r="18">
@@ -1733,76 +1733,76 @@
         <v>38</v>
       </c>
       <c r="B18">
-        <v>-0.0388117146229063</v>
+        <v>-0.014076818221382494</v>
       </c>
       <c r="C18">
-        <v>-1.4976374090251716e-06</v>
+        <v>6.4079993556668044e-07</v>
       </c>
       <c r="D18">
-        <v>-2.0398014275715767e-06</v>
+        <v>-2.167488109638385e-06</v>
       </c>
       <c r="E18">
-        <v>1.0909093054176679e-07</v>
+        <v>4.8703722193004131e-07</v>
       </c>
       <c r="F18">
-        <v>-6.5535565323370044e-10</v>
+        <v>-4.731693085333438e-09</v>
       </c>
       <c r="G18">
-        <v>-5.1497703129434517e-06</v>
+        <v>-1.9115657197659095e-06</v>
       </c>
       <c r="H18">
-        <v>-2.902826063173506e-05</v>
+        <v>-1.7014921598287376e-05</v>
       </c>
       <c r="I18">
-        <v>1.1168479755137243e-07</v>
+        <v>3.2785114306925699e-08</v>
       </c>
       <c r="J18">
-        <v>3.6555775350960959e-07</v>
+        <v>1.4522606577529837e-07</v>
       </c>
       <c r="K18">
-        <v>-5.2425375587558747e-06</v>
+        <v>-3.3105430912645903e-06</v>
       </c>
       <c r="L18">
-        <v>1.6923700458096433e-05</v>
+        <v>-4.312334110483636e-06</v>
       </c>
       <c r="M18">
-        <v>1.7062806309530191e-06</v>
+        <v>4.5776914590981024e-06</v>
       </c>
       <c r="N18">
-        <v>-7.4026137389406044e-06</v>
+        <v>-2.6796835551761859e-06</v>
       </c>
       <c r="O18">
-        <v>-1.6216094678504019e-05</v>
+        <v>-9.7091994508373408e-06</v>
       </c>
       <c r="P18">
-        <v>-2.0682266280592468e-05</v>
+        <v>-1.3507510707194651e-05</v>
       </c>
       <c r="Q18">
-        <v>0.00023043838941843884</v>
+        <v>0.00020784636961141418</v>
       </c>
       <c r="R18">
-        <v>0.00022982842768083639</v>
+        <v>0.00020734517434658174</v>
       </c>
       <c r="S18">
-        <v>0.0004299858484190636</v>
+        <v>0.00038720143444915628</v>
       </c>
       <c r="T18">
-        <v>0.00023103523410615933</v>
+        <v>0.00020828084976414133</v>
       </c>
       <c r="U18">
-        <v>0.00023328250313897292</v>
+        <v>0.00021008513291280714</v>
       </c>
       <c r="V18">
-        <v>0.00023069392649076326</v>
+        <v>0.0002078348288325775</v>
       </c>
       <c r="W18">
-        <v>-6.1420063790584963e-06</v>
+        <v>-4.9775195416931294e-06</v>
       </c>
       <c r="X18">
-        <v>-6.9327736194005213e-06</v>
+        <v>-5.8113497166520079e-06</v>
       </c>
       <c r="Y18">
-        <v>-0.00021071833549293878</v>
+        <v>-0.00020253055970155418</v>
       </c>
     </row>
     <row r="19">
@@ -1810,76 +1810,76 @@
         <v>39</v>
       </c>
       <c r="B19">
-        <v>0.057025108645005963</v>
+        <v>0.09378628572061265</v>
       </c>
       <c r="C19">
-        <v>7.5926666273633648e-06</v>
+        <v>5.7738368143280504e-06</v>
       </c>
       <c r="D19">
-        <v>2.5797321779958534e-06</v>
+        <v>1.7903095210014873e-06</v>
       </c>
       <c r="E19">
-        <v>8.570012247718916e-07</v>
+        <v>1.6663707198308055e-06</v>
       </c>
       <c r="F19">
-        <v>-1.1251710434941407e-08</v>
+        <v>-2.0071084534453949e-08</v>
       </c>
       <c r="G19">
-        <v>-1.1543054323875125e-05</v>
+        <v>-5.6664484676520657e-06</v>
       </c>
       <c r="H19">
-        <v>-2.3206953553328635e-05</v>
+        <v>-1.3287409139150585e-05</v>
       </c>
       <c r="I19">
-        <v>1.7111120631175475e-07</v>
+        <v>3.6338635616813778e-08</v>
       </c>
       <c r="J19">
-        <v>4.5347012479434286e-07</v>
+        <v>2.406435429129941e-07</v>
       </c>
       <c r="K19">
-        <v>-5.1141406128629676e-06</v>
+        <v>-2.5221500356785842e-06</v>
       </c>
       <c r="L19">
-        <v>4.0933953295506993e-06</v>
+        <v>-7.1298840373377753e-06</v>
       </c>
       <c r="M19">
-        <v>7.8058066934647512e-06</v>
+        <v>9.7991299640515841e-06</v>
       </c>
       <c r="N19">
-        <v>4.9934415580902061e-06</v>
+        <v>6.9866038140402347e-06</v>
       </c>
       <c r="O19">
-        <v>-2.9173039289013191e-07</v>
+        <v>3.7743477250128951e-06</v>
       </c>
       <c r="P19">
-        <v>-1.5831521131190614e-05</v>
+        <v>-8.9710496959651904e-06</v>
       </c>
       <c r="Q19">
-        <v>0.00023131015545587539</v>
+        <v>0.00020863600195786676</v>
       </c>
       <c r="R19">
-        <v>0.00023142961487592555</v>
+        <v>0.00020873398824343837</v>
       </c>
       <c r="S19">
-        <v>0.00023103523410615933</v>
+        <v>0.00020828084976414133</v>
       </c>
       <c r="T19">
-        <v>0.0003710893458051386</v>
+        <v>0.00032751469574160804</v>
       </c>
       <c r="U19">
-        <v>0.00023185269557246871</v>
+        <v>0.00020900457198413748</v>
       </c>
       <c r="V19">
-        <v>0.00023057587495740349</v>
+        <v>0.00020786332807523817</v>
       </c>
       <c r="W19">
-        <v>4.8301752520641106e-06</v>
+        <v>6.4923544262157329e-06</v>
       </c>
       <c r="X19">
-        <v>4.2025562091222498e-06</v>
+        <v>5.9119263836670848e-06</v>
       </c>
       <c r="Y19">
-        <v>-0.00024062626068008437</v>
+        <v>-0.00023757989767552652</v>
       </c>
     </row>
     <row r="20">
@@ -1887,76 +1887,76 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <v>-0.14042850568275228</v>
+        <v>-0.1015328748478599</v>
       </c>
       <c r="C20">
-        <v>5.7726603500998899e-06</v>
+        <v>6.4399516836442697e-06</v>
       </c>
       <c r="D20">
-        <v>-6.3772008551939256e-06</v>
+        <v>-6.2092317259988623e-06</v>
       </c>
       <c r="E20">
-        <v>-3.8601954097936526e-08</v>
+        <v>3.2829403045377973e-07</v>
       </c>
       <c r="F20">
-        <v>3.4145696828080349e-09</v>
+        <v>-1.0096604103184873e-09</v>
       </c>
       <c r="G20">
-        <v>-1.700380279706316e-05</v>
+        <v>-1.1448503958290276e-05</v>
       </c>
       <c r="H20">
-        <v>-5.5925882771811329e-05</v>
+        <v>-3.5950549136931192e-05</v>
       </c>
       <c r="I20">
-        <v>3.0278273217855394e-07</v>
+        <v>1.784541399021381e-07</v>
       </c>
       <c r="J20">
-        <v>7.974185894975233e-07</v>
+        <v>4.2919121904164667e-07</v>
       </c>
       <c r="K20">
-        <v>-2.3615602021981738e-06</v>
+        <v>3.3716769143997658e-08</v>
       </c>
       <c r="L20">
-        <v>3.2814391434223279e-05</v>
+        <v>-6.2404596342951593e-06</v>
       </c>
       <c r="M20">
-        <v>2.0303412738913006e-06</v>
+        <v>2.6405051996475392e-06</v>
       </c>
       <c r="N20">
-        <v>-6.510458729558588e-06</v>
+        <v>-4.7112244350561817e-06</v>
       </c>
       <c r="O20">
-        <v>-1.2557784687938035e-05</v>
+        <v>-9.2885581969664831e-06</v>
       </c>
       <c r="P20">
-        <v>-2.4676664520045875e-05</v>
+        <v>-1.9415624512475184e-05</v>
       </c>
       <c r="Q20">
-        <v>0.00022998618130566442</v>
+        <v>0.00020758448624725895</v>
       </c>
       <c r="R20">
-        <v>0.00022947164752944421</v>
+        <v>0.00020723874029475849</v>
       </c>
       <c r="S20">
-        <v>0.00023328250313897292</v>
+        <v>0.00021008513291280714</v>
       </c>
       <c r="T20">
-        <v>0.00023185269557246871</v>
+        <v>0.00020900457198413748</v>
       </c>
       <c r="U20">
-        <v>0.00039680243525847382</v>
+        <v>0.00035523530052020022</v>
       </c>
       <c r="V20">
-        <v>0.00023288449335761612</v>
+        <v>0.00020958615474129622</v>
       </c>
       <c r="W20">
-        <v>-1.9573508040404356e-06</v>
+        <v>-2.0323145377481024e-07</v>
       </c>
       <c r="X20">
-        <v>-4.0247167864966488e-06</v>
+        <v>-1.9230246924610818e-06</v>
       </c>
       <c r="Y20">
-        <v>-0.00021355649063945054</v>
+        <v>-0.000201066317566371</v>
       </c>
     </row>
     <row r="21">
@@ -1964,76 +1964,76 @@
         <v>41</v>
       </c>
       <c r="B21">
-        <v>-0.074457721263041524</v>
+        <v>-0.049806128178538564</v>
       </c>
       <c r="C21">
-        <v>6.0233655465737843e-07</v>
+        <v>-4.1962939247760638e-07</v>
       </c>
       <c r="D21">
-        <v>-5.1722876145704883e-06</v>
+        <v>-4.7750209927426335e-06</v>
       </c>
       <c r="E21">
-        <v>-2.1091692782088654e-06</v>
+        <v>-1.5924073443884118e-06</v>
       </c>
       <c r="F21">
-        <v>2.4040497405546126e-08</v>
+        <v>1.8423286454227841e-08</v>
       </c>
       <c r="G21">
-        <v>-1.522079164008946e-05</v>
+        <v>-1.0149676103076937e-05</v>
       </c>
       <c r="H21">
-        <v>-2.8529712476297917e-05</v>
+        <v>-1.9387934875485656e-05</v>
       </c>
       <c r="I21">
-        <v>2.5497860948027182e-07</v>
+        <v>1.5115619323630546e-07</v>
       </c>
       <c r="J21">
-        <v>4.3578735223408231e-07</v>
+        <v>2.6854037537018175e-07</v>
       </c>
       <c r="K21">
-        <v>1.3846801038372074e-05</v>
+        <v>1.1505396567742331e-05</v>
       </c>
       <c r="L21">
-        <v>1.6026598790000384e-05</v>
+        <v>-2.7339106883459257e-07</v>
       </c>
       <c r="M21">
-        <v>9.6240102269608946e-06</v>
+        <v>1.0781726965084075e-05</v>
       </c>
       <c r="N21">
-        <v>-5.4920975788681298e-06</v>
+        <v>-8.029157398520406e-07</v>
       </c>
       <c r="O21">
-        <v>1.4695235030674021e-06</v>
+        <v>5.0788656043477425e-06</v>
       </c>
       <c r="P21">
-        <v>-1.0234499504098115e-05</v>
+        <v>-5.5689124964271585e-06</v>
       </c>
       <c r="Q21">
-        <v>0.00022914413497782379</v>
+        <v>0.00020675818443960476</v>
       </c>
       <c r="R21">
-        <v>0.0002297127653882869</v>
+        <v>0.00020723423948553212</v>
       </c>
       <c r="S21">
-        <v>0.00023069392649076326</v>
+        <v>0.0002078348288325775</v>
       </c>
       <c r="T21">
-        <v>0.00023057587495740349</v>
+        <v>0.00020786332807523817</v>
       </c>
       <c r="U21">
-        <v>0.00023288449335761612</v>
+        <v>0.00020958615474129622</v>
       </c>
       <c r="V21">
-        <v>0.001026855962446144</v>
+        <v>0.00091779250483804752</v>
       </c>
       <c r="W21">
-        <v>5.0137147331231602e-06</v>
+        <v>5.2602395908732781e-06</v>
       </c>
       <c r="X21">
-        <v>4.976984367818873e-06</v>
+        <v>5.6574551329543511e-06</v>
       </c>
       <c r="Y21">
-        <v>-0.00019078624041394076</v>
+        <v>-0.00018173958476425619</v>
       </c>
     </row>
     <row r="22">
@@ -2041,76 +2041,76 @@
         <v>42</v>
       </c>
       <c r="B22">
-        <v>-0.057299250243023528</v>
+        <v>-0.0923495704559784</v>
       </c>
       <c r="C22">
-        <v>1.0357376828053962e-05</v>
+        <v>9.9562976616470948e-06</v>
       </c>
       <c r="D22">
-        <v>6.449379893992628e-06</v>
+        <v>5.711084054726912e-06</v>
       </c>
       <c r="E22">
-        <v>4.239596629926488e-07</v>
+        <v>5.1319639636195038e-07</v>
       </c>
       <c r="F22">
-        <v>-6.8730687389085826e-09</v>
+        <v>-6.605817393049726e-09</v>
       </c>
       <c r="G22">
-        <v>8.6955938711988e-06</v>
+        <v>6.7976865026077628e-06</v>
       </c>
       <c r="H22">
-        <v>1.5581745572557169e-05</v>
+        <v>1.5502196411901637e-05</v>
       </c>
       <c r="I22">
-        <v>-1.0280251246839305e-07</v>
+        <v>-8.0470731857337259e-08</v>
       </c>
       <c r="J22">
-        <v>-1.5285424393132197e-07</v>
+        <v>-2.0894545913527595e-07</v>
       </c>
       <c r="K22">
-        <v>-1.3345004104120418e-06</v>
+        <v>-8.8210213924130594e-07</v>
       </c>
       <c r="L22">
-        <v>-7.2863947464846939e-06</v>
+        <v>-2.0963572648921408e-06</v>
       </c>
       <c r="M22">
-        <v>-2.1881698121816384e-06</v>
+        <v>-2.659226834504982e-06</v>
       </c>
       <c r="N22">
-        <v>-7.1226765481819864e-06</v>
+        <v>-6.8262886919653498e-06</v>
       </c>
       <c r="O22">
-        <v>-6.2455986156359512e-06</v>
+        <v>-7.1179462224887442e-06</v>
       </c>
       <c r="P22">
-        <v>-1.0576543168340934e-05</v>
+        <v>-1.1797723467004485e-05</v>
       </c>
       <c r="Q22">
-        <v>1.0728623583437715e-06</v>
+        <v>1.375355982132621e-06</v>
       </c>
       <c r="R22">
-        <v>-1.843736926814521e-06</v>
+        <v>-8.9308460403442874e-07</v>
       </c>
       <c r="S22">
-        <v>-6.1420063790584963e-06</v>
+        <v>-4.9775195416931294e-06</v>
       </c>
       <c r="T22">
-        <v>4.8301752520641106e-06</v>
+        <v>6.4923544262157329e-06</v>
       </c>
       <c r="U22">
-        <v>-1.9573508040404356e-06</v>
+        <v>-2.0323145377481024e-07</v>
       </c>
       <c r="V22">
-        <v>5.0137147331231602e-06</v>
+        <v>5.2602395908732781e-06</v>
       </c>
       <c r="W22">
-        <v>0.0005116466051101749</v>
+        <v>0.00051575269920147078</v>
       </c>
       <c r="X22">
-        <v>3.759728127852206e-05</v>
+        <v>3.236362748455832e-05</v>
       </c>
       <c r="Y22">
-        <v>-3.8807915643076574e-05</v>
+        <v>-3.7151624126349185e-05</v>
       </c>
     </row>
     <row r="23">
@@ -2118,76 +2118,76 @@
         <v>43</v>
       </c>
       <c r="B23">
-        <v>0.037129283881508407</v>
+        <v>0.040627500029932775</v>
       </c>
       <c r="C23">
-        <v>7.0355137455296531e-06</v>
+        <v>4.3000236693587114e-06</v>
       </c>
       <c r="D23">
-        <v>1.1898052516156756e-05</v>
+        <v>9.0455988857617261e-06</v>
       </c>
       <c r="E23">
-        <v>-4.8358358493944411e-07</v>
+        <v>3.5952893214442572e-07</v>
       </c>
       <c r="F23">
-        <v>1.7531733545419866e-09</v>
+        <v>-6.2584565743969258e-09</v>
       </c>
       <c r="G23">
-        <v>8.379934847303358e-06</v>
+        <v>6.1670635498055813e-06</v>
       </c>
       <c r="H23">
-        <v>1.6524604911675522e-05</v>
+        <v>1.5542241449421002e-05</v>
       </c>
       <c r="I23">
-        <v>-5.2568120058640001e-08</v>
+        <v>-5.4897924928440445e-08</v>
       </c>
       <c r="J23">
-        <v>-3.9044512839800034e-08</v>
+        <v>-1.2396507342169301e-07</v>
       </c>
       <c r="K23">
-        <v>-6.8615739832329165e-07</v>
+        <v>4.0556182386317124e-07</v>
       </c>
       <c r="L23">
-        <v>-2.9528375826878163e-05</v>
+        <v>-5.0720331981070855e-06</v>
       </c>
       <c r="M23">
-        <v>4.3516053563866506e-06</v>
+        <v>2.8522856670761173e-06</v>
       </c>
       <c r="N23">
-        <v>3.2200834082005357e-06</v>
+        <v>2.2617914458459829e-06</v>
       </c>
       <c r="O23">
-        <v>7.2239502471942131e-06</v>
+        <v>4.895541103505398e-06</v>
       </c>
       <c r="P23">
-        <v>7.1690052865917662e-06</v>
+        <v>4.4898699790875024e-06</v>
       </c>
       <c r="Q23">
-        <v>-2.5669139939127136e-07</v>
+        <v>8.2531002632138115e-08</v>
       </c>
       <c r="R23">
-        <v>-7.7675370219925999e-06</v>
+        <v>-4.7206916125607647e-06</v>
       </c>
       <c r="S23">
-        <v>-6.9327736194005213e-06</v>
+        <v>-5.8113497166520079e-06</v>
       </c>
       <c r="T23">
-        <v>4.2025562091222498e-06</v>
+        <v>5.9119263836670848e-06</v>
       </c>
       <c r="U23">
-        <v>-4.0247167864966488e-06</v>
+        <v>-1.9230246924610818e-06</v>
       </c>
       <c r="V23">
-        <v>4.976984367818873e-06</v>
+        <v>5.6574551329543511e-06</v>
       </c>
       <c r="W23">
-        <v>3.759728127852206e-05</v>
+        <v>3.236362748455832e-05</v>
       </c>
       <c r="X23">
-        <v>0.00060266800858814387</v>
+        <v>0.00061848160784097475</v>
       </c>
       <c r="Y23">
-        <v>-3.4024001492931245e-05</v>
+        <v>-4.4096993446648153e-05</v>
       </c>
     </row>
     <row r="24">
@@ -2195,76 +2195,76 @@
         <v>44</v>
       </c>
       <c r="B24">
-        <v>-1.6668664512367881</v>
+        <v>-2.1863205181631735</v>
       </c>
       <c r="C24">
-        <v>-0.0010549303565369052</v>
+        <v>-0.000988449099072807</v>
       </c>
       <c r="D24">
-        <v>-0.00014452076130769679</v>
+        <v>-0.00011661033011537262</v>
       </c>
       <c r="E24">
-        <v>-0.0002714613930900531</v>
+        <v>-0.00025058045398493442</v>
       </c>
       <c r="F24">
-        <v>2.6517524962267183e-06</v>
+        <v>2.468879685493119e-06</v>
       </c>
       <c r="G24">
-        <v>-0.0013105522706281948</v>
+        <v>-0.0012440409183924889</v>
       </c>
       <c r="H24">
-        <v>-0.0010286658564525621</v>
+        <v>-0.0012388207517911992</v>
       </c>
       <c r="I24">
-        <v>2.6685349817706093e-05</v>
+        <v>2.5491124340933407e-05</v>
       </c>
       <c r="J24">
-        <v>1.9701823854459415e-05</v>
+        <v>2.4221675374156273e-05</v>
       </c>
       <c r="K24">
-        <v>0.00026755006816287787</v>
+        <v>0.00016157160861471681</v>
       </c>
       <c r="L24">
-        <v>-0.00088185876998194172</v>
+        <v>0.00022785976442534005</v>
       </c>
       <c r="M24">
-        <v>-0.0043468763354454132</v>
+        <v>-0.0036145091879106</v>
       </c>
       <c r="N24">
-        <v>-0.0044000963654414939</v>
+        <v>-0.0036696532994213793</v>
       </c>
       <c r="O24">
-        <v>-0.0044612043691336827</v>
+        <v>-0.0037313408862465368</v>
       </c>
       <c r="P24">
-        <v>-0.0045967698067886833</v>
+        <v>-0.0038544324578319118</v>
       </c>
       <c r="Q24">
-        <v>-0.00023393594692061324</v>
+        <v>-0.00022892873610641688</v>
       </c>
       <c r="R24">
-        <v>-0.00023047971297573627</v>
+        <v>-0.00023084883665623171</v>
       </c>
       <c r="S24">
-        <v>-0.00021071833549293878</v>
+        <v>-0.00020253055970155418</v>
       </c>
       <c r="T24">
-        <v>-0.00024062626068008437</v>
+        <v>-0.00023757989767552652</v>
       </c>
       <c r="U24">
-        <v>-0.00021355649063945054</v>
+        <v>-0.000201066317566371</v>
       </c>
       <c r="V24">
-        <v>-0.00019078624041394076</v>
+        <v>-0.00018173958476425619</v>
       </c>
       <c r="W24">
-        <v>-3.8807915643076574e-05</v>
+        <v>-3.7151624126349185e-05</v>
       </c>
       <c r="X24">
-        <v>-3.4024001492931245e-05</v>
+        <v>-4.4096993446648153e-05</v>
       </c>
       <c r="Y24">
-        <v>0.011099175054119295</v>
+        <v>0.0097744381883295758</v>
       </c>
     </row>
   </sheetData>
@@ -2358,76 +2358,76 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>-1.4931074320606004</v>
+        <v>-1.5460064491678762</v>
       </c>
       <c r="C2">
-        <v>0.00088126224871907328</v>
+        <v>0.00074185927597689031</v>
       </c>
       <c r="D2">
-        <v>8.1034713460495839e-05</v>
+        <v>7.1127309180528319e-05</v>
       </c>
       <c r="E2">
-        <v>3.7480134356225276e-05</v>
+        <v>3.8262834476235461e-05</v>
       </c>
       <c r="F2">
-        <v>-3.4713581164327136e-07</v>
+        <v>-3.6678866170883542e-07</v>
       </c>
       <c r="G2">
-        <v>-6.9159806415700065e-06</v>
+        <v>1.2316807841300401e-05</v>
       </c>
       <c r="H2">
-        <v>0.00020736673415861295</v>
+        <v>0.00014361884622716918</v>
       </c>
       <c r="I2">
-        <v>3.3097525688243883e-09</v>
+        <v>-3.3654529133260882e-07</v>
       </c>
       <c r="J2">
-        <v>-3.9889513541697308e-06</v>
+        <v>-2.7787692507174424e-06</v>
       </c>
       <c r="K2">
-        <v>2.1181623876570087e-05</v>
+        <v>2.9299995597658994e-05</v>
       </c>
       <c r="L2">
-        <v>-0.00028683737752833061</v>
+        <v>-3.0593206335037479e-05</v>
       </c>
       <c r="M2">
-        <v>-2.5807732715972184e-06</v>
+        <v>8.1451424063230457e-07</v>
       </c>
       <c r="N2">
-        <v>2.2449223507265445e-06</v>
+        <v>5.2516755494281457e-06</v>
       </c>
       <c r="O2">
-        <v>1.1131559091931821e-05</v>
+        <v>1.3574403627642298e-05</v>
       </c>
       <c r="P2">
-        <v>9.0443193928869113e-06</v>
+        <v>1.0409829902196513e-05</v>
       </c>
       <c r="Q2">
-        <v>7.2456559364568627e-06</v>
+        <v>4.7139542634746805e-06</v>
       </c>
       <c r="R2">
-        <v>4.6786959759314729e-06</v>
+        <v>1.475789271907036e-06</v>
       </c>
       <c r="S2">
-        <v>4.4968088864321487e-06</v>
+        <v>5.0773710577164088e-06</v>
       </c>
       <c r="T2">
-        <v>5.5963377198540407e-06</v>
+        <v>5.0413155862304047e-06</v>
       </c>
       <c r="U2">
-        <v>-3.7407432588798661e-06</v>
+        <v>-5.5285281196880353e-07</v>
       </c>
       <c r="V2">
-        <v>-2.0324119055380697e-06</v>
+        <v>2.8447485046941679e-07</v>
       </c>
       <c r="W2">
-        <v>9.6384478227815581e-06</v>
+        <v>9.8708634542819802e-06</v>
       </c>
       <c r="X2">
-        <v>2.9188835806084935e-06</v>
+        <v>5.8212419359163504e-07</v>
       </c>
       <c r="Y2">
-        <v>-0.0010294999162681253</v>
+        <v>-0.0010091629345850475</v>
       </c>
     </row>
     <row r="3">
@@ -2435,76 +2435,76 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>-2.0066162176245093</v>
+        <v>-2.0631663802872913</v>
       </c>
       <c r="C3">
-        <v>8.1034713460495839e-05</v>
+        <v>7.1127309180528319e-05</v>
       </c>
       <c r="D3">
-        <v>0.00016668502886221123</v>
+        <v>0.00014736760412597174</v>
       </c>
       <c r="E3">
-        <v>6.5249011384914685e-06</v>
+        <v>5.2247219769474625e-06</v>
       </c>
       <c r="F3">
-        <v>-6.8383320854421358e-08</v>
+        <v>-5.5171957437349748e-08</v>
       </c>
       <c r="G3">
-        <v>1.659225433474523e-05</v>
+        <v>1.2304378202020726e-05</v>
       </c>
       <c r="H3">
-        <v>-5.6122550013353312e-06</v>
+        <v>-4.7313988346049695e-06</v>
       </c>
       <c r="I3">
-        <v>-7.2051756438039053e-07</v>
+        <v>-4.8536132895246721e-07</v>
       </c>
       <c r="J3">
-        <v>-5.2305558349983376e-07</v>
+        <v>-3.6189512696978139e-07</v>
       </c>
       <c r="K3">
-        <v>1.8908203754649223e-05</v>
+        <v>1.3554640395691092e-05</v>
       </c>
       <c r="L3">
-        <v>1.2143907099235864e-05</v>
+        <v>3.0899032643850771e-06</v>
       </c>
       <c r="M3">
-        <v>5.5022057819434356e-06</v>
+        <v>6.1584748857115287e-06</v>
       </c>
       <c r="N3">
-        <v>1.0633711617590407e-05</v>
+        <v>8.7362210170806128e-06</v>
       </c>
       <c r="O3">
-        <v>2.0418435026734166e-05</v>
+        <v>1.6296170461959572e-05</v>
       </c>
       <c r="P3">
-        <v>2.5592259870643269e-05</v>
+        <v>2.0649284692382934e-05</v>
       </c>
       <c r="Q3">
-        <v>7.5294385777120658e-06</v>
+        <v>5.6289877470251649e-06</v>
       </c>
       <c r="R3">
-        <v>5.8498764915852253e-06</v>
+        <v>4.9529091190151011e-06</v>
       </c>
       <c r="S3">
-        <v>3.461372794127233e-06</v>
+        <v>3.7391885805211703e-06</v>
       </c>
       <c r="T3">
-        <v>3.6105993138311025e-06</v>
+        <v>2.8678310875438164e-06</v>
       </c>
       <c r="U3">
-        <v>-5.2066045992323442e-06</v>
+        <v>-3.6402324597503306e-06</v>
       </c>
       <c r="V3">
-        <v>-8.9386513252424649e-06</v>
+        <v>-7.5315705023342392e-06</v>
       </c>
       <c r="W3">
-        <v>8.1890817646018631e-06</v>
+        <v>6.7521108945201596e-06</v>
       </c>
       <c r="X3">
-        <v>9.5969579910589285e-06</v>
+        <v>6.5766276111471332e-06</v>
       </c>
       <c r="Y3">
-        <v>-0.00021579444375254827</v>
+        <v>-0.00017795279878205056</v>
       </c>
     </row>
     <row r="4">
@@ -2512,76 +2512,76 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>0.14516237783823921</v>
+        <v>0.16261647740890892</v>
       </c>
       <c r="C4">
-        <v>3.7480134356225276e-05</v>
+        <v>3.8262834476235461e-05</v>
       </c>
       <c r="D4">
-        <v>6.5249011384914685e-06</v>
+        <v>5.2247219769474625e-06</v>
       </c>
       <c r="E4">
-        <v>1.1303171481240903e-05</v>
+        <v>1.0207595034967712e-05</v>
       </c>
       <c r="F4">
-        <v>-1.1337954842942293e-07</v>
+        <v>-1.0295275784698111e-07</v>
       </c>
       <c r="G4">
-        <v>4.4775093548048516e-05</v>
+        <v>4.2941379733458038e-05</v>
       </c>
       <c r="H4">
-        <v>3.8467759561372122e-05</v>
+        <v>4.7396015767334004e-05</v>
       </c>
       <c r="I4">
-        <v>-9.2352878403446254e-07</v>
+        <v>-8.9389413889426779e-07</v>
       </c>
       <c r="J4">
-        <v>-7.6994277698212685e-07</v>
+        <v>-9.5176883071592331e-07</v>
       </c>
       <c r="K4">
-        <v>-1.2594004191337129e-05</v>
+        <v>-4.6891523105274465e-06</v>
       </c>
       <c r="L4">
-        <v>3.841691273959718e-05</v>
+        <v>-1.1340096863135722e-05</v>
       </c>
       <c r="M4">
-        <v>1.4913293897839792e-06</v>
+        <v>1.7972441888854037e-06</v>
       </c>
       <c r="N4">
-        <v>3.7773045482607974e-06</v>
+        <v>3.9677836071922204e-06</v>
       </c>
       <c r="O4">
-        <v>5.7320576508925695e-06</v>
+        <v>5.9906863780168437e-06</v>
       </c>
       <c r="P4">
-        <v>1.1524196383877076e-05</v>
+        <v>1.1405668610090365e-05</v>
       </c>
       <c r="Q4">
-        <v>3.5215394732287934e-07</v>
+        <v>1.1376983638802547e-06</v>
       </c>
       <c r="R4">
-        <v>-4.788584723277864e-07</v>
+        <v>1.3520636707573905e-07</v>
       </c>
       <c r="S4">
-        <v>3.1799205785004463e-07</v>
+        <v>3.856358699013978e-07</v>
       </c>
       <c r="T4">
-        <v>3.3620727800952382e-07</v>
+        <v>1.0623117599141848e-06</v>
       </c>
       <c r="U4">
-        <v>-7.8068490041055079e-07</v>
+        <v>-3.9097935948372816e-07</v>
       </c>
       <c r="V4">
-        <v>-1.6160452525814243e-06</v>
+        <v>-1.7237746172763759e-06</v>
       </c>
       <c r="W4">
-        <v>3.3325530035804443e-07</v>
+        <v>5.2972168521386966e-07</v>
       </c>
       <c r="X4">
-        <v>-6.7546704682154576e-07</v>
+        <v>2.81561731566845e-07</v>
       </c>
       <c r="Y4">
-        <v>-0.00026373953153217405</v>
+        <v>-0.00023829272713437683</v>
       </c>
     </row>
     <row r="5">
@@ -2589,76 +2589,76 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>-0.0019110229600048333</v>
+        <v>-0.0020783381670518601</v>
       </c>
       <c r="C5">
-        <v>-3.4713581164327136e-07</v>
+        <v>-3.6678866170883542e-07</v>
       </c>
       <c r="D5">
-        <v>-6.8383320854421358e-08</v>
+        <v>-5.5171957437349748e-08</v>
       </c>
       <c r="E5">
-        <v>-1.1337954842942293e-07</v>
+        <v>-1.0295275784698111e-07</v>
       </c>
       <c r="F5">
-        <v>1.2148699399149345e-09</v>
+        <v>1.1086094879298779e-09</v>
       </c>
       <c r="G5">
-        <v>-1.9092117360212847e-07</v>
+        <v>-2.0853527006566698e-07</v>
       </c>
       <c r="H5">
-        <v>-9.9344048452925519e-08</v>
+        <v>-2.4801098632227966e-07</v>
       </c>
       <c r="I5">
-        <v>3.5606115341832966e-09</v>
+        <v>4.1153924732624663e-09</v>
       </c>
       <c r="J5">
-        <v>1.473734371004006e-09</v>
+        <v>4.5961776018602967e-09</v>
       </c>
       <c r="K5">
-        <v>1.0115109968394638e-07</v>
+        <v>8.1772473813449551e-09</v>
       </c>
       <c r="L5">
-        <v>-4.4555498084698835e-07</v>
+        <v>1.4277629272208715e-07</v>
       </c>
       <c r="M5">
-        <v>-1.813676760997569e-08</v>
+        <v>-2.0742673358443559e-08</v>
       </c>
       <c r="N5">
-        <v>-4.2587128415869166e-08</v>
+        <v>-4.4417070425668185e-08</v>
       </c>
       <c r="O5">
-        <v>-5.3362782066716421e-08</v>
+        <v>-5.7511358333741033e-08</v>
       </c>
       <c r="P5">
-        <v>-9.7211342333525317e-08</v>
+        <v>-9.9584726958435395e-08</v>
       </c>
       <c r="Q5">
-        <v>-3.5589737379494572e-09</v>
+        <v>-1.3023512750519646e-08</v>
       </c>
       <c r="R5">
-        <v>5.1556238432710148e-09</v>
+        <v>-2.1917872757918884e-09</v>
       </c>
       <c r="S5">
-        <v>-1.2916800895048729e-09</v>
+        <v>-2.2879595987887436e-09</v>
       </c>
       <c r="T5">
-        <v>-3.1192837767867353e-09</v>
+        <v>-1.135626081217945e-08</v>
       </c>
       <c r="U5">
-        <v>1.1404235299276586e-08</v>
+        <v>6.7051813669920668e-09</v>
       </c>
       <c r="V5">
-        <v>1.8967771427845141e-08</v>
+        <v>2.0539560819921629e-08</v>
       </c>
       <c r="W5">
-        <v>-5.4103383631268919e-09</v>
+        <v>-6.811222601876056e-09</v>
       </c>
       <c r="X5">
-        <v>2.8470515065478158e-09</v>
+        <v>-7.3035174080840374e-09</v>
       </c>
       <c r="Y5">
-        <v>2.4784389354271559e-06</v>
+        <v>2.2520893764479928e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2666,76 +2666,76 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>-0.40215590192922041</v>
+        <v>-0.40445329507655498</v>
       </c>
       <c r="C6">
-        <v>-6.9159806415700065e-06</v>
+        <v>1.2316807841300401e-05</v>
       </c>
       <c r="D6">
-        <v>1.659225433474523e-05</v>
+        <v>1.2304378202020726e-05</v>
       </c>
       <c r="E6">
-        <v>4.4775093548048516e-05</v>
+        <v>4.2941379733458038e-05</v>
       </c>
       <c r="F6">
-        <v>-1.9092117360212847e-07</v>
+        <v>-2.0853527006566698e-07</v>
       </c>
       <c r="G6">
-        <v>0.0028092678154449909</v>
+        <v>0.0024676833570865804</v>
       </c>
       <c r="H6">
-        <v>0.001385333930858524</v>
+        <v>0.0012416490308238912</v>
       </c>
       <c r="I6">
-        <v>-5.7387063380046889e-05</v>
+        <v>-5.004752773841493e-05</v>
       </c>
       <c r="J6">
-        <v>-2.8006970596586216e-05</v>
+        <v>-2.4903501124605532e-05</v>
       </c>
       <c r="K6">
-        <v>-1.1428228747573122e-05</v>
+        <v>3.0675842468176357e-06</v>
       </c>
       <c r="L6">
-        <v>-6.0332344000403756e-05</v>
+        <v>-3.2808599970423157e-05</v>
       </c>
       <c r="M6">
-        <v>-1.0566522706814078e-06</v>
+        <v>6.2998570857282109e-06</v>
       </c>
       <c r="N6">
-        <v>4.4415982986075906e-06</v>
+        <v>1.1616314376034311e-05</v>
       </c>
       <c r="O6">
-        <v>1.7965915899443305e-06</v>
+        <v>1.0634478621029562e-05</v>
       </c>
       <c r="P6">
-        <v>1.837633076279049e-05</v>
+        <v>2.3313705154268485e-05</v>
       </c>
       <c r="Q6">
-        <v>1.3598296649109354e-05</v>
+        <v>1.033380214884674e-05</v>
       </c>
       <c r="R6">
-        <v>3.3446012570931049e-07</v>
+        <v>-1.5983658163690932e-06</v>
       </c>
       <c r="S6">
-        <v>3.0979378589852233e-06</v>
+        <v>3.2841584103402222e-06</v>
       </c>
       <c r="T6">
-        <v>1.4234135488934159e-07</v>
+        <v>1.2198167281873962e-06</v>
       </c>
       <c r="U6">
-        <v>-9.657051726672173e-06</v>
+        <v>-7.1341812363080214e-06</v>
       </c>
       <c r="V6">
-        <v>-1.6736609328579967e-05</v>
+        <v>-1.6149463471300828e-05</v>
       </c>
       <c r="W6">
-        <v>6.4824673322319149e-06</v>
+        <v>3.5164232718433765e-06</v>
       </c>
       <c r="X6">
-        <v>1.0146859009114377e-05</v>
+        <v>6.1814706224520246e-06</v>
       </c>
       <c r="Y6">
-        <v>-0.0017176667705921383</v>
+        <v>-0.0015973748514898495</v>
       </c>
     </row>
     <row r="7">
@@ -2743,76 +2743,76 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-0.45801965394433925</v>
+        <v>-0.55952293906001582</v>
       </c>
       <c r="C7">
-        <v>0.00020736673415861295</v>
+        <v>0.00014361884622716918</v>
       </c>
       <c r="D7">
-        <v>-5.6122550013353312e-06</v>
+        <v>-4.7313988346049695e-06</v>
       </c>
       <c r="E7">
-        <v>3.8467759561372122e-05</v>
+        <v>4.7396015767334004e-05</v>
       </c>
       <c r="F7">
-        <v>-9.9344048452925519e-08</v>
+        <v>-2.4801098632227966e-07</v>
       </c>
       <c r="G7">
-        <v>0.001385333930858524</v>
+        <v>0.0012416490308238912</v>
       </c>
       <c r="H7">
-        <v>0.002354545014179088</v>
+        <v>0.0020375968091834659</v>
       </c>
       <c r="I7">
-        <v>-2.8009827272141567e-05</v>
+        <v>-2.4931311946448055e-05</v>
       </c>
       <c r="J7">
-        <v>-4.6816232067668888e-05</v>
+        <v>-4.0423737980276256e-05</v>
       </c>
       <c r="K7">
-        <v>-1.6319347368878732e-05</v>
+        <v>2.187496206123607e-05</v>
       </c>
       <c r="L7">
-        <v>-0.00056997044953129613</v>
+        <v>-9.3552762080917795e-05</v>
       </c>
       <c r="M7">
-        <v>5.9926171016395566e-06</v>
+        <v>6.595168468449342e-06</v>
       </c>
       <c r="N7">
-        <v>7.2397517129888693e-06</v>
+        <v>9.7102020257150727e-06</v>
       </c>
       <c r="O7">
-        <v>2.3097342580070783e-06</v>
+        <v>8.9704729425338402e-06</v>
       </c>
       <c r="P7">
-        <v>3.7842266690118836e-05</v>
+        <v>3.8080107364049523e-05</v>
       </c>
       <c r="Q7">
-        <v>1.7006070005523222e-05</v>
+        <v>1.3755952924265165e-05</v>
       </c>
       <c r="R7">
-        <v>1.1214253004292201e-05</v>
+        <v>6.0822533613291908e-06</v>
       </c>
       <c r="S7">
-        <v>-1.3339835607572016e-05</v>
+        <v>-9.8248169219184643e-06</v>
       </c>
       <c r="T7">
-        <v>-9.6056342678271775e-06</v>
+        <v>-6.5845070314333895e-06</v>
       </c>
       <c r="U7">
-        <v>-3.6630246879555746e-05</v>
+        <v>-2.6950809347737109e-05</v>
       </c>
       <c r="V7">
-        <v>-2.0791676948765986e-05</v>
+        <v>-1.6774356798898917e-05</v>
       </c>
       <c r="W7">
-        <v>1.5942545712687472e-05</v>
+        <v>1.3440128479261074e-05</v>
       </c>
       <c r="X7">
-        <v>1.282983737758712e-05</v>
+        <v>8.0929138313141475e-06</v>
       </c>
       <c r="Y7">
-        <v>-0.001641534893640093</v>
+        <v>-0.0017070767879386211</v>
       </c>
     </row>
     <row r="8">
@@ -2820,76 +2820,76 @@
         <v>28</v>
       </c>
       <c r="B8">
-        <v>0.010630982645658406</v>
+        <v>0.0078531881034314167</v>
       </c>
       <c r="C8">
-        <v>3.3097525688243883e-09</v>
+        <v>-3.3654529133260882e-07</v>
       </c>
       <c r="D8">
-        <v>-7.2051756438039053e-07</v>
+        <v>-4.8536132895246721e-07</v>
       </c>
       <c r="E8">
-        <v>-9.2352878403446254e-07</v>
+        <v>-8.9389413889426779e-07</v>
       </c>
       <c r="F8">
-        <v>3.5606115341832966e-09</v>
+        <v>4.1153924732624663e-09</v>
       </c>
       <c r="G8">
-        <v>-5.7387063380046889e-05</v>
+        <v>-5.004752773841493e-05</v>
       </c>
       <c r="H8">
-        <v>-2.8009827272141567e-05</v>
+        <v>-2.4931311946448055e-05</v>
       </c>
       <c r="I8">
-        <v>1.2823656123542237e-06</v>
+        <v>1.1118684232665928e-06</v>
       </c>
       <c r="J8">
-        <v>6.1311620070001059e-07</v>
+        <v>5.4216338944754081e-07</v>
       </c>
       <c r="K8">
-        <v>2.3015098171596306e-07</v>
+        <v>-1.4959815778763455e-07</v>
       </c>
       <c r="L8">
-        <v>1.2263063017742003e-06</v>
+        <v>7.7595637113846023e-07</v>
       </c>
       <c r="M8">
-        <v>-6.0968424069681744e-08</v>
+        <v>-2.1086753819495792e-07</v>
       </c>
       <c r="N8">
-        <v>-1.0139020786646742e-07</v>
+        <v>-2.9243053409817955e-07</v>
       </c>
       <c r="O8">
-        <v>1.9437373507396579e-07</v>
+        <v>-7.754482250792062e-08</v>
       </c>
       <c r="P8">
-        <v>-4.7402737994483427e-08</v>
+        <v>-2.4438220384864619e-07</v>
       </c>
       <c r="Q8">
-        <v>-2.3188828964921934e-07</v>
+        <v>-1.7597343318703924e-07</v>
       </c>
       <c r="R8">
-        <v>2.0222481588391114e-07</v>
+        <v>2.0023807243427352e-07</v>
       </c>
       <c r="S8">
-        <v>-1.3976972193366799e-07</v>
+        <v>-1.4347763511109743e-07</v>
       </c>
       <c r="T8">
-        <v>-4.96494742982345e-08</v>
+        <v>-7.8919752797592873e-08</v>
       </c>
       <c r="U8">
-        <v>1.1420549954854578e-07</v>
+        <v>6.7134884473391549e-08</v>
       </c>
       <c r="V8">
-        <v>2.3154987275362712e-07</v>
+        <v>2.489725370848461e-07</v>
       </c>
       <c r="W8">
-        <v>-1.5242565842766108e-07</v>
+        <v>-8.9457257439142707e-08</v>
       </c>
       <c r="X8">
-        <v>-1.3822898401567202e-07</v>
+        <v>-9.0324261697324879e-08</v>
       </c>
       <c r="Y8">
-        <v>3.4119827807001024e-05</v>
+        <v>3.1810528837995031e-05</v>
       </c>
     </row>
     <row r="9">
@@ -2897,76 +2897,76 @@
         <v>29</v>
       </c>
       <c r="B9">
-        <v>0.0086888111991849475</v>
+        <v>0.0080208465668391727</v>
       </c>
       <c r="C9">
-        <v>-3.9889513541697308e-06</v>
+        <v>-2.7787692507174424e-06</v>
       </c>
       <c r="D9">
-        <v>-5.2305558349983376e-07</v>
+        <v>-3.6189512696978139e-07</v>
       </c>
       <c r="E9">
-        <v>-7.6994277698212685e-07</v>
+        <v>-9.5176883071592331e-07</v>
       </c>
       <c r="F9">
-        <v>1.473734371004006e-09</v>
+        <v>4.5961776018602967e-09</v>
       </c>
       <c r="G9">
-        <v>-2.8006970596586216e-05</v>
+        <v>-2.4903501124605532e-05</v>
       </c>
       <c r="H9">
-        <v>-4.6816232067668888e-05</v>
+        <v>-4.0423737980276256e-05</v>
       </c>
       <c r="I9">
-        <v>6.1311620070001059e-07</v>
+        <v>5.4216338944754081e-07</v>
       </c>
       <c r="J9">
-        <v>1.0110165189889259e-06</v>
+        <v>8.7344236838964641e-07</v>
       </c>
       <c r="K9">
-        <v>2.7627077212290344e-07</v>
+        <v>-5.5213885212638789e-07</v>
       </c>
       <c r="L9">
-        <v>1.0771681665320797e-05</v>
+        <v>1.9192673242762582e-06</v>
       </c>
       <c r="M9">
-        <v>-1.7037559348692194e-07</v>
+        <v>-1.8240829761097256e-07</v>
       </c>
       <c r="N9">
-        <v>-3.4626067462249874e-08</v>
+        <v>-1.3375345390145304e-07</v>
       </c>
       <c r="O9">
-        <v>4.8762065098008017e-07</v>
+        <v>2.3673839023044497e-07</v>
       </c>
       <c r="P9">
-        <v>-1.0748778501240509e-08</v>
+        <v>-1.5338639367471443e-07</v>
       </c>
       <c r="Q9">
-        <v>-1.3740885584091291e-07</v>
+        <v>-1.0494553494808636e-07</v>
       </c>
       <c r="R9">
-        <v>2.5273990251856378e-07</v>
+        <v>2.8374691822122306e-07</v>
       </c>
       <c r="S9">
-        <v>-6.6261763486728533e-08</v>
+        <v>-1.0341255561561333e-07</v>
       </c>
       <c r="T9">
-        <v>2.4506734068147263e-07</v>
+        <v>1.7205688342084376e-07</v>
       </c>
       <c r="U9">
-        <v>4.7437413414241964e-07</v>
+        <v>2.9814959143307689e-07</v>
       </c>
       <c r="V9">
-        <v>3.4264700537060355e-07</v>
+        <v>2.8503368931597679e-07</v>
       </c>
       <c r="W9">
-        <v>-2.47302376772063e-07</v>
+        <v>-2.3589796548736957e-07</v>
       </c>
       <c r="X9">
-        <v>-7.2897794159852285e-08</v>
+        <v>-5.2446991717774343e-08</v>
       </c>
       <c r="Y9">
-        <v>3.1628269683129238e-05</v>
+        <v>3.3037982872207643e-05</v>
       </c>
     </row>
     <row r="10">
@@ -2974,76 +2974,76 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>0.15410316476893779</v>
+        <v>0.20605154236790166</v>
       </c>
       <c r="C10">
-        <v>2.1181623876570087e-05</v>
+        <v>2.9299995597658994e-05</v>
       </c>
       <c r="D10">
-        <v>1.8908203754649223e-05</v>
+        <v>1.3554640395691092e-05</v>
       </c>
       <c r="E10">
-        <v>-1.2594004191337129e-05</v>
+        <v>-4.6891523105274465e-06</v>
       </c>
       <c r="F10">
-        <v>1.0115109968394638e-07</v>
+        <v>8.1772473813449551e-09</v>
       </c>
       <c r="G10">
-        <v>-1.1428228747573122e-05</v>
+        <v>3.0675842468176357e-06</v>
       </c>
       <c r="H10">
-        <v>-1.6319347368878732e-05</v>
+        <v>2.187496206123607e-05</v>
       </c>
       <c r="I10">
-        <v>2.3015098171596306e-07</v>
+        <v>-1.4959815778763455e-07</v>
       </c>
       <c r="J10">
-        <v>2.7627077212290344e-07</v>
+        <v>-5.5213885212638789e-07</v>
       </c>
       <c r="K10">
-        <v>0.00019427740912200949</v>
+        <v>0.00023008369371460257</v>
       </c>
       <c r="L10">
-        <v>-3.9218961996986305e-05</v>
+        <v>-0.00011035552383841623</v>
       </c>
       <c r="M10">
-        <v>-7.6004769005007201e-06</v>
+        <v>-7.0570154316241152e-06</v>
       </c>
       <c r="N10">
-        <v>-1.218270947647014e-05</v>
+        <v>-8.1620334106983963e-06</v>
       </c>
       <c r="O10">
-        <v>-1.8584357651659845e-05</v>
+        <v>-1.135505270575036e-05</v>
       </c>
       <c r="P10">
-        <v>-1.9633909771095949e-05</v>
+        <v>-1.2200835958301007e-05</v>
       </c>
       <c r="Q10">
-        <v>-1.5982326030038879e-06</v>
+        <v>1.5913325136274265e-06</v>
       </c>
       <c r="R10">
-        <v>-6.1145754506021908e-06</v>
+        <v>-3.9312042216032015e-06</v>
       </c>
       <c r="S10">
-        <v>-7.1006594844046298e-07</v>
+        <v>4.8638431624895905e-07</v>
       </c>
       <c r="T10">
-        <v>-5.254379638952359e-06</v>
+        <v>-2.4263538692595373e-06</v>
       </c>
       <c r="U10">
-        <v>-8.2404119105670048e-06</v>
+        <v>-4.0107813510467981e-06</v>
       </c>
       <c r="V10">
-        <v>4.9793400878022437e-06</v>
+        <v>2.8524696327124353e-06</v>
       </c>
       <c r="W10">
-        <v>2.9848961278604991e-06</v>
+        <v>2.7034192129034835e-06</v>
       </c>
       <c r="X10">
-        <v>6.4606430594300683e-06</v>
+        <v>8.1932214358755726e-06</v>
       </c>
       <c r="Y10">
-        <v>0.00024292610784200461</v>
+        <v>0.0001003666649968226</v>
       </c>
     </row>
     <row r="11">
@@ -3051,76 +3051,76 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>-0.56950909896412427</v>
+        <v>-0.071142389713377746</v>
       </c>
       <c r="C11">
-        <v>-0.00028683737752833061</v>
+        <v>-3.0593206335037479e-05</v>
       </c>
       <c r="D11">
-        <v>1.2143907099235864e-05</v>
+        <v>3.0899032643850771e-06</v>
       </c>
       <c r="E11">
-        <v>3.841691273959718e-05</v>
+        <v>-1.1340096863135722e-05</v>
       </c>
       <c r="F11">
-        <v>-4.4555498084698835e-07</v>
+        <v>1.4277629272208715e-07</v>
       </c>
       <c r="G11">
-        <v>-6.0332344000403756e-05</v>
+        <v>-3.2808599970423157e-05</v>
       </c>
       <c r="H11">
-        <v>-0.00056997044953129613</v>
+        <v>-9.3552762080917795e-05</v>
       </c>
       <c r="I11">
-        <v>1.2263063017742003e-06</v>
+        <v>7.7595637113846023e-07</v>
       </c>
       <c r="J11">
-        <v>1.0771681665320797e-05</v>
+        <v>1.9192673242762582e-06</v>
       </c>
       <c r="K11">
-        <v>-3.9218961996986305e-05</v>
+        <v>-0.00011035552383841623</v>
       </c>
       <c r="L11">
-        <v>0.003321068015656548</v>
+        <v>0.00021361871890326719</v>
       </c>
       <c r="M11">
-        <v>1.9473030651958505e-06</v>
+        <v>-4.6401978890251903e-07</v>
       </c>
       <c r="N11">
-        <v>8.7244270353972167e-06</v>
+        <v>-5.2916737142418794e-06</v>
       </c>
       <c r="O11">
-        <v>1.4742824534149821e-05</v>
+        <v>-9.897401144103683e-06</v>
       </c>
       <c r="P11">
-        <v>9.7135696694266552e-06</v>
+        <v>-1.1154289291371927e-05</v>
       </c>
       <c r="Q11">
-        <v>-1.562448986181933e-05</v>
+        <v>-6.4484341091051955e-06</v>
       </c>
       <c r="R11">
-        <v>-1.0956883040093351e-05</v>
+        <v>-3.4091826417708757e-06</v>
       </c>
       <c r="S11">
-        <v>5.4065448195434943e-06</v>
+        <v>-2.4618847921282577e-06</v>
       </c>
       <c r="T11">
-        <v>-6.754186885884511e-06</v>
+        <v>-4.6965827888657116e-06</v>
       </c>
       <c r="U11">
-        <v>8.2211571203110157e-06</v>
+        <v>-5.4452538270770068e-06</v>
       </c>
       <c r="V11">
-        <v>1.4671527136994214e-05</v>
+        <v>4.3054478666509737e-06</v>
       </c>
       <c r="W11">
-        <v>-7.4309136767208855e-06</v>
+        <v>-3.2083549705464349e-06</v>
       </c>
       <c r="X11">
-        <v>-2.9111968417128596e-05</v>
+        <v>-7.1832783393610755e-06</v>
       </c>
       <c r="Y11">
-        <v>-0.00071992333683462348</v>
+        <v>0.00020857984561314282</v>
       </c>
     </row>
     <row r="12">
@@ -3128,76 +3128,76 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>0.22774479455038815</v>
+        <v>0.16627566388520262</v>
       </c>
       <c r="C12">
-        <v>-2.5807732715972184e-06</v>
+        <v>8.1451424063230457e-07</v>
       </c>
       <c r="D12">
-        <v>5.5022057819434356e-06</v>
+        <v>6.1584748857115287e-06</v>
       </c>
       <c r="E12">
-        <v>1.4913293897839792e-06</v>
+        <v>1.7972441888854037e-06</v>
       </c>
       <c r="F12">
-        <v>-1.813676760997569e-08</v>
+        <v>-2.0742673358443559e-08</v>
       </c>
       <c r="G12">
-        <v>-1.0566522706814078e-06</v>
+        <v>6.2998570857282109e-06</v>
       </c>
       <c r="H12">
-        <v>5.9926171016395566e-06</v>
+        <v>6.595168468449342e-06</v>
       </c>
       <c r="I12">
-        <v>-6.0968424069681744e-08</v>
+        <v>-2.1086753819495792e-07</v>
       </c>
       <c r="J12">
-        <v>-1.7037559348692194e-07</v>
+        <v>-1.8240829761097256e-07</v>
       </c>
       <c r="K12">
-        <v>-7.6004769005007201e-06</v>
+        <v>-7.0570154316241152e-06</v>
       </c>
       <c r="L12">
-        <v>1.9473030651958505e-06</v>
+        <v>-4.6401978890251903e-07</v>
       </c>
       <c r="M12">
-        <v>0.0057745760910762611</v>
+        <v>0.0047403022034546195</v>
       </c>
       <c r="N12">
-        <v>0.0047819014267983006</v>
+        <v>0.0038930219198128249</v>
       </c>
       <c r="O12">
-        <v>0.0047801769777425594</v>
+        <v>0.0038916340266215701</v>
       </c>
       <c r="P12">
-        <v>0.0047779856725034993</v>
+        <v>0.00388982212086435</v>
       </c>
       <c r="Q12">
-        <v>1.1759698693194616e-05</v>
+        <v>9.8135710890202127e-06</v>
       </c>
       <c r="R12">
-        <v>8.9742904114076624e-06</v>
+        <v>5.4467675971230724e-06</v>
       </c>
       <c r="S12">
-        <v>1.912798683664904e-07</v>
+        <v>-1.3079083319450394e-06</v>
       </c>
       <c r="T12">
-        <v>4.095404382028887e-06</v>
+        <v>2.9265692149753987e-06</v>
       </c>
       <c r="U12">
-        <v>1.2345215254236423e-05</v>
+        <v>7.136691153376414e-06</v>
       </c>
       <c r="V12">
-        <v>2.0123675183939937e-06</v>
+        <v>2.6182428855198913e-06</v>
       </c>
       <c r="W12">
-        <v>-9.3463584703514809e-07</v>
+        <v>-1.3556909987937132e-06</v>
       </c>
       <c r="X12">
-        <v>-4.921581141314747e-06</v>
+        <v>-4.9414103891404907e-06</v>
       </c>
       <c r="Y12">
-        <v>-0.0048079674914148617</v>
+        <v>-0.0039260031461625022</v>
       </c>
     </row>
     <row r="13">
@@ -3205,76 +3205,76 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>0.65215086724084803</v>
+        <v>0.61625138071883057</v>
       </c>
       <c r="C13">
-        <v>2.2449223507265445e-06</v>
+        <v>5.2516755494281457e-06</v>
       </c>
       <c r="D13">
-        <v>1.0633711617590407e-05</v>
+        <v>8.7362210170806128e-06</v>
       </c>
       <c r="E13">
-        <v>3.7773045482607974e-06</v>
+        <v>3.9677836071922204e-06</v>
       </c>
       <c r="F13">
-        <v>-4.2587128415869166e-08</v>
+        <v>-4.4417070425668185e-08</v>
       </c>
       <c r="G13">
-        <v>4.4415982986075906e-06</v>
+        <v>1.1616314376034311e-05</v>
       </c>
       <c r="H13">
-        <v>7.2397517129888693e-06</v>
+        <v>9.7102020257150727e-06</v>
       </c>
       <c r="I13">
-        <v>-1.0139020786646742e-07</v>
+        <v>-2.9243053409817955e-07</v>
       </c>
       <c r="J13">
-        <v>-3.4626067462249874e-08</v>
+        <v>-1.3375345390145304e-07</v>
       </c>
       <c r="K13">
-        <v>-1.218270947647014e-05</v>
+        <v>-8.1620334106983963e-06</v>
       </c>
       <c r="L13">
-        <v>8.7244270353972167e-06</v>
+        <v>-5.2916737142418794e-06</v>
       </c>
       <c r="M13">
-        <v>0.0047819014267983006</v>
+        <v>0.0038930219198128249</v>
       </c>
       <c r="N13">
-        <v>0.0049658196652320897</v>
+        <v>0.0040531068044618156</v>
       </c>
       <c r="O13">
-        <v>0.0047839502503286679</v>
+        <v>0.003894609859351444</v>
       </c>
       <c r="P13">
-        <v>0.004784049861645729</v>
+        <v>0.0038948225549202192</v>
       </c>
       <c r="Q13">
-        <v>4.9598564429616796e-06</v>
+        <v>4.4224526467484451e-06</v>
       </c>
       <c r="R13">
-        <v>-1.2959440681927956e-06</v>
+        <v>-3.0855684194046595e-06</v>
       </c>
       <c r="S13">
-        <v>-1.2175125501668219e-05</v>
+        <v>-1.0996434993788847e-05</v>
       </c>
       <c r="T13">
-        <v>-4.0842236171308583e-06</v>
+        <v>-4.0316322069063894e-06</v>
       </c>
       <c r="U13">
-        <v>3.4655904526250205e-07</v>
+        <v>-3.130433976287556e-06</v>
       </c>
       <c r="V13">
-        <v>-9.0407583303293799e-06</v>
+        <v>-8.8040636403090522e-06</v>
       </c>
       <c r="W13">
-        <v>-2.1683503841257326e-06</v>
+        <v>-2.9113400901915666e-06</v>
       </c>
       <c r="X13">
-        <v>-6.5375264993869841e-06</v>
+        <v>-6.5313501605727725e-06</v>
       </c>
       <c r="Y13">
-        <v>-0.0048550492459284288</v>
+        <v>-0.0039684595616753726</v>
       </c>
     </row>
     <row r="14">
@@ -3282,76 +3282,76 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0.87253001618960668</v>
+        <v>0.85196728271191591</v>
       </c>
       <c r="C14">
-        <v>1.1131559091931821e-05</v>
+        <v>1.3574403627642298e-05</v>
       </c>
       <c r="D14">
-        <v>2.0418435026734166e-05</v>
+        <v>1.6296170461959572e-05</v>
       </c>
       <c r="E14">
-        <v>5.7320576508925695e-06</v>
+        <v>5.9906863780168437e-06</v>
       </c>
       <c r="F14">
-        <v>-5.3362782066716421e-08</v>
+        <v>-5.7511358333741033e-08</v>
       </c>
       <c r="G14">
-        <v>1.7965915899443305e-06</v>
+        <v>1.0634478621029562e-05</v>
       </c>
       <c r="H14">
-        <v>2.3097342580070783e-06</v>
+        <v>8.9704729425338402e-06</v>
       </c>
       <c r="I14">
-        <v>1.9437373507396579e-07</v>
+        <v>-7.754482250792062e-08</v>
       </c>
       <c r="J14">
-        <v>4.8762065098008017e-07</v>
+        <v>2.3673839023044497e-07</v>
       </c>
       <c r="K14">
-        <v>-1.8584357651659845e-05</v>
+        <v>-1.135505270575036e-05</v>
       </c>
       <c r="L14">
-        <v>1.4742824534149821e-05</v>
+        <v>-9.897401144103683e-06</v>
       </c>
       <c r="M14">
-        <v>0.0047801769777425594</v>
+        <v>0.0038916340266215701</v>
       </c>
       <c r="N14">
-        <v>0.0047839502503286679</v>
+        <v>0.003894609859351444</v>
       </c>
       <c r="O14">
-        <v>0.0048474915402331956</v>
+        <v>0.0039514114708592493</v>
       </c>
       <c r="P14">
-        <v>0.0048066575561497823</v>
+        <v>0.0039142311181402717</v>
       </c>
       <c r="Q14">
-        <v>1.1254154947917979e-06</v>
+        <v>1.4373122825228862e-06</v>
       </c>
       <c r="R14">
-        <v>-7.4310610776348563e-06</v>
+        <v>-6.7394280491303658e-06</v>
       </c>
       <c r="S14">
-        <v>-1.6593664541966332e-05</v>
+        <v>-1.463974879293817e-05</v>
       </c>
       <c r="T14">
-        <v>-6.2250385280830157e-06</v>
+        <v>-4.8628611382178034e-06</v>
       </c>
       <c r="U14">
-        <v>-2.0656496600463415e-06</v>
+        <v>-5.2237151995880842e-06</v>
       </c>
       <c r="V14">
-        <v>-2.3247995583761593e-06</v>
+        <v>-1.8005579362521338e-06</v>
       </c>
       <c r="W14">
-        <v>-2.80883941783318e-06</v>
+        <v>-4.4401585189376866e-06</v>
       </c>
       <c r="X14">
-        <v>-2.7427582930699747e-06</v>
+        <v>-3.9346942739277752e-06</v>
       </c>
       <c r="Y14">
-        <v>-0.0049391848959026525</v>
+        <v>-0.0040473251642220553</v>
       </c>
     </row>
     <row r="15">
@@ -3359,76 +3359,76 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>0.88846439281509948</v>
+        <v>0.87867284981098215</v>
       </c>
       <c r="C15">
-        <v>9.0443193928869113e-06</v>
+        <v>1.0409829902196513e-05</v>
       </c>
       <c r="D15">
-        <v>2.5592259870643269e-05</v>
+        <v>2.0649284692382934e-05</v>
       </c>
       <c r="E15">
-        <v>1.1524196383877076e-05</v>
+        <v>1.1405668610090365e-05</v>
       </c>
       <c r="F15">
-        <v>-9.7211342333525317e-08</v>
+        <v>-9.9584726958435395e-08</v>
       </c>
       <c r="G15">
-        <v>1.837633076279049e-05</v>
+        <v>2.3313705154268485e-05</v>
       </c>
       <c r="H15">
-        <v>3.7842266690118836e-05</v>
+        <v>3.8080107364049523e-05</v>
       </c>
       <c r="I15">
-        <v>-4.7402737994483427e-08</v>
+        <v>-2.4438220384864619e-07</v>
       </c>
       <c r="J15">
-        <v>-1.0748778501240509e-08</v>
+        <v>-1.5338639367471443e-07</v>
       </c>
       <c r="K15">
-        <v>-1.9633909771095949e-05</v>
+        <v>-1.2200835958301007e-05</v>
       </c>
       <c r="L15">
-        <v>9.7135696694266552e-06</v>
+        <v>-1.1154289291371927e-05</v>
       </c>
       <c r="M15">
-        <v>0.0047779856725034993</v>
+        <v>0.00388982212086435</v>
       </c>
       <c r="N15">
-        <v>0.004784049861645729</v>
+        <v>0.0038948225549202192</v>
       </c>
       <c r="O15">
-        <v>0.0048066575561497823</v>
+        <v>0.0039142311181402717</v>
       </c>
       <c r="P15">
-        <v>0.0050050684359274162</v>
+        <v>0.0040976458269792373</v>
       </c>
       <c r="Q15">
-        <v>-4.6164957813229758e-06</v>
+        <v>-2.74113629743431e-06</v>
       </c>
       <c r="R15">
-        <v>-1.5689504152163422e-05</v>
+        <v>-1.369519334991702e-05</v>
       </c>
       <c r="S15">
-        <v>-1.9026374733207223e-05</v>
+        <v>-1.6902907372494234e-05</v>
       </c>
       <c r="T15">
-        <v>-1.9198716051258179e-05</v>
+        <v>-1.5663377653003625e-05</v>
       </c>
       <c r="U15">
-        <v>-1.3879248732277458e-05</v>
+        <v>-1.4907747462991578e-05</v>
       </c>
       <c r="V15">
-        <v>-1.4121242175962859e-05</v>
+        <v>-1.1334228750512927e-05</v>
       </c>
       <c r="W15">
-        <v>-7.3103236347676152e-06</v>
+        <v>-8.9437289691714801e-06</v>
       </c>
       <c r="X15">
-        <v>-5.1111078295608531e-06</v>
+        <v>-5.8095064108495878e-06</v>
       </c>
       <c r="Y15">
-        <v>-0.0051160007903314157</v>
+        <v>-0.0042099395338169848</v>
       </c>
     </row>
     <row r="16">
@@ -3436,76 +3436,76 @@
         <v>36</v>
       </c>
       <c r="B16">
-        <v>0.035772240868528857</v>
+        <v>0.06523109340489297</v>
       </c>
       <c r="C16">
-        <v>7.2456559364568627e-06</v>
+        <v>4.7139542634746805e-06</v>
       </c>
       <c r="D16">
-        <v>7.5294385777120658e-06</v>
+        <v>5.6289877470251649e-06</v>
       </c>
       <c r="E16">
-        <v>3.5215394732287934e-07</v>
+        <v>1.1376983638802547e-06</v>
       </c>
       <c r="F16">
-        <v>-3.5589737379494572e-09</v>
+        <v>-1.3023512750519646e-08</v>
       </c>
       <c r="G16">
-        <v>1.3598296649109354e-05</v>
+        <v>1.033380214884674e-05</v>
       </c>
       <c r="H16">
-        <v>1.7006070005523222e-05</v>
+        <v>1.3755952924265165e-05</v>
       </c>
       <c r="I16">
-        <v>-2.3188828964921934e-07</v>
+        <v>-1.7597343318703924e-07</v>
       </c>
       <c r="J16">
-        <v>-1.3740885584091291e-07</v>
+        <v>-1.0494553494808636e-07</v>
       </c>
       <c r="K16">
-        <v>-1.5982326030038879e-06</v>
+        <v>1.5913325136274265e-06</v>
       </c>
       <c r="L16">
-        <v>-1.562448986181933e-05</v>
+        <v>-6.4484341091051955e-06</v>
       </c>
       <c r="M16">
-        <v>1.1759698693194616e-05</v>
+        <v>9.8135710890202127e-06</v>
       </c>
       <c r="N16">
-        <v>4.9598564429616796e-06</v>
+        <v>4.4224526467484451e-06</v>
       </c>
       <c r="O16">
-        <v>1.1254154947917979e-06</v>
+        <v>1.4373122825228862e-06</v>
       </c>
       <c r="P16">
-        <v>-4.6164957813229758e-06</v>
+        <v>-2.74113629743431e-06</v>
       </c>
       <c r="Q16">
-        <v>0.00046398720800014214</v>
+        <v>0.00042832217986366234</v>
       </c>
       <c r="R16">
-        <v>0.00024828944271723316</v>
+        <v>0.00022708055567406265</v>
       </c>
       <c r="S16">
-        <v>0.00024480097573438352</v>
+        <v>0.00022450465058317809</v>
       </c>
       <c r="T16">
-        <v>0.00024671949046909449</v>
+        <v>0.00022604538442442789</v>
       </c>
       <c r="U16">
-        <v>0.00024475710751927123</v>
+        <v>0.00022456941302367904</v>
       </c>
       <c r="V16">
-        <v>0.00024477806859044958</v>
+        <v>0.00022432489412153934</v>
       </c>
       <c r="W16">
-        <v>5.5001110873580757e-06</v>
+        <v>5.2792927337328599e-06</v>
       </c>
       <c r="X16">
-        <v>4.7524926420566386e-06</v>
+        <v>4.4121196453801455e-06</v>
       </c>
       <c r="Y16">
-        <v>-0.00026285859601497033</v>
+        <v>-0.00025535226197773018</v>
       </c>
     </row>
     <row r="17">
@@ -3513,76 +3513,76 @@
         <v>37</v>
       </c>
       <c r="B17">
-        <v>-0.047961207944290325</v>
+        <v>-0.0062842375936854817</v>
       </c>
       <c r="C17">
-        <v>4.6786959759314729e-06</v>
+        <v>1.475789271907036e-06</v>
       </c>
       <c r="D17">
-        <v>5.8498764915852253e-06</v>
+        <v>4.9529091190151011e-06</v>
       </c>
       <c r="E17">
-        <v>-4.788584723277864e-07</v>
+        <v>1.3520636707573905e-07</v>
       </c>
       <c r="F17">
-        <v>5.1556238432710148e-09</v>
+        <v>-2.1917872757918884e-09</v>
       </c>
       <c r="G17">
-        <v>3.3446012570931049e-07</v>
+        <v>-1.5983658163690932e-06</v>
       </c>
       <c r="H17">
-        <v>1.1214253004292201e-05</v>
+        <v>6.0822533613291908e-06</v>
       </c>
       <c r="I17">
-        <v>2.0222481588391114e-07</v>
+        <v>2.0023807243427352e-07</v>
       </c>
       <c r="J17">
-        <v>2.5273990251856378e-07</v>
+        <v>2.8374691822122306e-07</v>
       </c>
       <c r="K17">
-        <v>-6.1145754506021908e-06</v>
+        <v>-3.9312042216032015e-06</v>
       </c>
       <c r="L17">
-        <v>-1.0956883040093351e-05</v>
+        <v>-3.4091826417708757e-06</v>
       </c>
       <c r="M17">
-        <v>8.9742904114076624e-06</v>
+        <v>5.4467675971230724e-06</v>
       </c>
       <c r="N17">
-        <v>-1.2959440681927956e-06</v>
+        <v>-3.0855684194046595e-06</v>
       </c>
       <c r="O17">
-        <v>-7.4310610776348563e-06</v>
+        <v>-6.7394280491303658e-06</v>
       </c>
       <c r="P17">
-        <v>-1.5689504152163422e-05</v>
+        <v>-1.369519334991702e-05</v>
       </c>
       <c r="Q17">
-        <v>0.00024828944271723316</v>
+        <v>0.00022708055567406265</v>
       </c>
       <c r="R17">
-        <v>0.00055755697618271069</v>
+        <v>0.00051200281380742239</v>
       </c>
       <c r="S17">
-        <v>0.00024404471236330036</v>
+        <v>0.00022382136463458909</v>
       </c>
       <c r="T17">
-        <v>0.00024748082554298012</v>
+        <v>0.00022654064949469355</v>
       </c>
       <c r="U17">
-        <v>0.00024495755623901483</v>
+        <v>0.00022464497208162524</v>
       </c>
       <c r="V17">
-        <v>0.00024503011586069824</v>
+        <v>0.0002246568224508247</v>
       </c>
       <c r="W17">
-        <v>8.3710227685053373e-07</v>
+        <v>1.8032814053186563e-06</v>
       </c>
       <c r="X17">
-        <v>-7.2203952460360568e-06</v>
+        <v>-5.1379565714724444e-06</v>
       </c>
       <c r="Y17">
-        <v>-0.00023944567755706451</v>
+        <v>-0.00022862382284855395</v>
       </c>
     </row>
     <row r="18">
@@ -3590,76 +3590,76 @@
         <v>38</v>
       </c>
       <c r="B18">
-        <v>-0.0099586383628289168</v>
+        <v>-0.014430187908926735</v>
       </c>
       <c r="C18">
-        <v>4.4968088864321487e-06</v>
+        <v>5.0773710577164088e-06</v>
       </c>
       <c r="D18">
-        <v>3.461372794127233e-06</v>
+        <v>3.7391885805211703e-06</v>
       </c>
       <c r="E18">
-        <v>3.1799205785004463e-07</v>
+        <v>3.856358699013978e-07</v>
       </c>
       <c r="F18">
-        <v>-1.2916800895048729e-09</v>
+        <v>-2.2879595987887436e-09</v>
       </c>
       <c r="G18">
-        <v>3.0979378589852233e-06</v>
+        <v>3.2841584103402222e-06</v>
       </c>
       <c r="H18">
-        <v>-1.3339835607572016e-05</v>
+        <v>-9.8248169219184643e-06</v>
       </c>
       <c r="I18">
-        <v>-1.3976972193366799e-07</v>
+        <v>-1.4347763511109743e-07</v>
       </c>
       <c r="J18">
-        <v>-6.6261763486728533e-08</v>
+        <v>-1.0341255561561333e-07</v>
       </c>
       <c r="K18">
-        <v>-7.1006594844046298e-07</v>
+        <v>4.8638431624895905e-07</v>
       </c>
       <c r="L18">
-        <v>5.4065448195434943e-06</v>
+        <v>-2.4618847921282577e-06</v>
       </c>
       <c r="M18">
-        <v>1.912798683664904e-07</v>
+        <v>-1.3079083319450394e-06</v>
       </c>
       <c r="N18">
-        <v>-1.2175125501668219e-05</v>
+        <v>-1.0996434993788847e-05</v>
       </c>
       <c r="O18">
-        <v>-1.6593664541966332e-05</v>
+        <v>-1.463974879293817e-05</v>
       </c>
       <c r="P18">
-        <v>-1.9026374733207223e-05</v>
+        <v>-1.6902907372494234e-05</v>
       </c>
       <c r="Q18">
-        <v>0.00024480097573438352</v>
+        <v>0.00022450465058317809</v>
       </c>
       <c r="R18">
-        <v>0.00024404471236330036</v>
+        <v>0.00022382136463458909</v>
       </c>
       <c r="S18">
-        <v>0.00044036551939691324</v>
+        <v>0.00040226629257242226</v>
       </c>
       <c r="T18">
-        <v>0.00024576202309815984</v>
+        <v>0.00022529362316647266</v>
       </c>
       <c r="U18">
-        <v>0.00024751315721820459</v>
+        <v>0.00022688816140487367</v>
       </c>
       <c r="V18">
-        <v>0.00024604668432688892</v>
+        <v>0.0002253067882303158</v>
       </c>
       <c r="W18">
-        <v>-2.3909358245420085e-06</v>
+        <v>-1.5058069435629418e-06</v>
       </c>
       <c r="X18">
-        <v>-1.2412780384941919e-06</v>
+        <v>-9.74592210611528e-07</v>
       </c>
       <c r="Y18">
-        <v>-0.00023469585957665515</v>
+        <v>-0.00021770546718838539</v>
       </c>
     </row>
     <row r="19">
@@ -3667,76 +3667,76 @@
         <v>39</v>
       </c>
       <c r="B19">
-        <v>0.021573077040099933</v>
+        <v>0.053105085497117378</v>
       </c>
       <c r="C19">
-        <v>5.5963377198540407e-06</v>
+        <v>5.0413155862304047e-06</v>
       </c>
       <c r="D19">
-        <v>3.6105993138311025e-06</v>
+        <v>2.8678310875438164e-06</v>
       </c>
       <c r="E19">
-        <v>3.3620727800952382e-07</v>
+        <v>1.0623117599141848e-06</v>
       </c>
       <c r="F19">
-        <v>-3.1192837767867353e-09</v>
+        <v>-1.135626081217945e-08</v>
       </c>
       <c r="G19">
-        <v>1.4234135488934159e-07</v>
+        <v>1.2198167281873962e-06</v>
       </c>
       <c r="H19">
-        <v>-9.6056342678271775e-06</v>
+        <v>-6.5845070314333895e-06</v>
       </c>
       <c r="I19">
-        <v>-4.96494742982345e-08</v>
+        <v>-7.8919752797592873e-08</v>
       </c>
       <c r="J19">
-        <v>2.4506734068147263e-07</v>
+        <v>1.7205688342084376e-07</v>
       </c>
       <c r="K19">
-        <v>-5.254379638952359e-06</v>
+        <v>-2.4263538692595373e-06</v>
       </c>
       <c r="L19">
-        <v>-6.754186885884511e-06</v>
+        <v>-4.6965827888657116e-06</v>
       </c>
       <c r="M19">
-        <v>4.095404382028887e-06</v>
+        <v>2.9265692149753987e-06</v>
       </c>
       <c r="N19">
-        <v>-4.0842236171308583e-06</v>
+        <v>-4.0316322069063894e-06</v>
       </c>
       <c r="O19">
-        <v>-6.2250385280830157e-06</v>
+        <v>-4.8628611382178034e-06</v>
       </c>
       <c r="P19">
-        <v>-1.9198716051258179e-05</v>
+        <v>-1.5663377653003625e-05</v>
       </c>
       <c r="Q19">
-        <v>0.00024671949046909449</v>
+        <v>0.00022604538442442789</v>
       </c>
       <c r="R19">
-        <v>0.00024748082554298012</v>
+        <v>0.00022654064949469355</v>
       </c>
       <c r="S19">
-        <v>0.00024576202309815984</v>
+        <v>0.00022529362316647266</v>
       </c>
       <c r="T19">
-        <v>0.00038740668546035197</v>
+        <v>0.00034869245399130034</v>
       </c>
       <c r="U19">
-        <v>0.00024680956801047054</v>
+        <v>0.00022618966129471629</v>
       </c>
       <c r="V19">
-        <v>0.00024622155425128937</v>
+        <v>0.00022547167070155024</v>
       </c>
       <c r="W19">
-        <v>8.1393119473376692e-06</v>
+        <v>9.5411654398226646e-06</v>
       </c>
       <c r="X19">
-        <v>5.4295910347743422e-06</v>
+        <v>7.2317327120563419e-06</v>
       </c>
       <c r="Y19">
-        <v>-0.00024633193862060818</v>
+        <v>-0.0002415196802777973</v>
       </c>
     </row>
     <row r="20">
@@ -3744,76 +3744,76 @@
         <v>40</v>
       </c>
       <c r="B20">
-        <v>-0.090261766173713412</v>
+        <v>-0.084363934370389013</v>
       </c>
       <c r="C20">
-        <v>-3.7407432588798661e-06</v>
+        <v>-5.5285281196880353e-07</v>
       </c>
       <c r="D20">
-        <v>-5.2066045992323442e-06</v>
+        <v>-3.6402324597503306e-06</v>
       </c>
       <c r="E20">
-        <v>-7.8068490041055079e-07</v>
+        <v>-3.9097935948372816e-07</v>
       </c>
       <c r="F20">
-        <v>1.1404235299276586e-08</v>
+        <v>6.7051813669920668e-09</v>
       </c>
       <c r="G20">
-        <v>-9.657051726672173e-06</v>
+        <v>-7.1341812363080214e-06</v>
       </c>
       <c r="H20">
-        <v>-3.6630246879555746e-05</v>
+        <v>-2.6950809347737109e-05</v>
       </c>
       <c r="I20">
-        <v>1.1420549954854578e-07</v>
+        <v>6.7134884473391549e-08</v>
       </c>
       <c r="J20">
-        <v>4.7437413414241964e-07</v>
+        <v>2.9814959143307689e-07</v>
       </c>
       <c r="K20">
-        <v>-8.2404119105670048e-06</v>
+        <v>-4.0107813510467981e-06</v>
       </c>
       <c r="L20">
-        <v>8.2211571203110157e-06</v>
+        <v>-5.4452538270770068e-06</v>
       </c>
       <c r="M20">
-        <v>1.2345215254236423e-05</v>
+        <v>7.136691153376414e-06</v>
       </c>
       <c r="N20">
-        <v>3.4655904526250205e-07</v>
+        <v>-3.130433976287556e-06</v>
       </c>
       <c r="O20">
-        <v>-2.0656496600463415e-06</v>
+        <v>-5.2237151995880842e-06</v>
       </c>
       <c r="P20">
-        <v>-1.3879248732277458e-05</v>
+        <v>-1.4907747462991578e-05</v>
       </c>
       <c r="Q20">
-        <v>0.00024475710751927123</v>
+        <v>0.00022456941302367904</v>
       </c>
       <c r="R20">
-        <v>0.00024495755623901483</v>
+        <v>0.00022464497208162524</v>
       </c>
       <c r="S20">
-        <v>0.00024751315721820459</v>
+        <v>0.00022688816140487367</v>
       </c>
       <c r="T20">
-        <v>0.00024680956801047054</v>
+        <v>0.00022618966129471629</v>
       </c>
       <c r="U20">
-        <v>0.00041021804326797092</v>
+        <v>0.00037307943059568103</v>
       </c>
       <c r="V20">
-        <v>0.00024773881862780487</v>
+        <v>0.0002265770997219273</v>
       </c>
       <c r="W20">
-        <v>-2.8211321965545443e-07</v>
+        <v>1.0161843698381578e-06</v>
       </c>
       <c r="X20">
-        <v>-4.5600031851447997e-07</v>
+        <v>4.8447017718101804e-07</v>
       </c>
       <c r="Y20">
-        <v>-0.00021936391431912701</v>
+        <v>-0.00020549649817245403</v>
       </c>
     </row>
     <row r="21">
@@ -3821,76 +3821,76 @@
         <v>41</v>
       </c>
       <c r="B21">
-        <v>-0.080131495975958436</v>
+        <v>-0.074610262536690092</v>
       </c>
       <c r="C21">
-        <v>-2.0324119055380697e-06</v>
+        <v>2.8447485046941679e-07</v>
       </c>
       <c r="D21">
-        <v>-8.9386513252424649e-06</v>
+        <v>-7.5315705023342392e-06</v>
       </c>
       <c r="E21">
-        <v>-1.6160452525814243e-06</v>
+        <v>-1.7237746172763759e-06</v>
       </c>
       <c r="F21">
-        <v>1.8967771427845141e-08</v>
+        <v>2.0539560819921629e-08</v>
       </c>
       <c r="G21">
-        <v>-1.6736609328579967e-05</v>
+        <v>-1.6149463471300828e-05</v>
       </c>
       <c r="H21">
-        <v>-2.0791676948765986e-05</v>
+        <v>-1.6774356798898917e-05</v>
       </c>
       <c r="I21">
-        <v>2.3154987275362712e-07</v>
+        <v>2.489725370848461e-07</v>
       </c>
       <c r="J21">
-        <v>3.4264700537060355e-07</v>
+        <v>2.8503368931597679e-07</v>
       </c>
       <c r="K21">
-        <v>4.9793400878022437e-06</v>
+        <v>2.8524696327124353e-06</v>
       </c>
       <c r="L21">
-        <v>1.4671527136994214e-05</v>
+        <v>4.3054478666509737e-06</v>
       </c>
       <c r="M21">
-        <v>2.0123675183939937e-06</v>
+        <v>2.6182428855198913e-06</v>
       </c>
       <c r="N21">
-        <v>-9.0407583303293799e-06</v>
+        <v>-8.8040636403090522e-06</v>
       </c>
       <c r="O21">
-        <v>-2.3247995583761593e-06</v>
+        <v>-1.8005579362521338e-06</v>
       </c>
       <c r="P21">
-        <v>-1.4121242175962859e-05</v>
+        <v>-1.1334228750512927e-05</v>
       </c>
       <c r="Q21">
-        <v>0.00024477806859044958</v>
+        <v>0.00022432489412153934</v>
       </c>
       <c r="R21">
-        <v>0.00024503011586069824</v>
+        <v>0.0002246568224508247</v>
       </c>
       <c r="S21">
-        <v>0.00024604668432688892</v>
+        <v>0.0002253067882303158</v>
       </c>
       <c r="T21">
-        <v>0.00024622155425128937</v>
+        <v>0.00022547167070155024</v>
       </c>
       <c r="U21">
-        <v>0.00024773881862780487</v>
+        <v>0.0002265770997219273</v>
       </c>
       <c r="V21">
-        <v>0.0010541690376712693</v>
+        <v>0.00095895101091874062</v>
       </c>
       <c r="W21">
-        <v>5.2807664048829268e-06</v>
+        <v>5.4054820268133583e-06</v>
       </c>
       <c r="X21">
-        <v>1.9605768827186995e-06</v>
+        <v>2.3593985310642801e-06</v>
       </c>
       <c r="Y21">
-        <v>-0.00020700455199358791</v>
+        <v>-0.00018719933015364345</v>
       </c>
     </row>
     <row r="22">
@@ -3898,76 +3898,76 @@
         <v>42</v>
       </c>
       <c r="B22">
-        <v>-0.039625551381243254</v>
+        <v>-0.069929299218011429</v>
       </c>
       <c r="C22">
-        <v>9.6384478227815581e-06</v>
+        <v>9.8708634542819802e-06</v>
       </c>
       <c r="D22">
-        <v>8.1890817646018631e-06</v>
+        <v>6.7521108945201596e-06</v>
       </c>
       <c r="E22">
-        <v>3.3325530035804443e-07</v>
+        <v>5.2972168521386966e-07</v>
       </c>
       <c r="F22">
-        <v>-5.4103383631268919e-09</v>
+        <v>-6.811222601876056e-09</v>
       </c>
       <c r="G22">
-        <v>6.4824673322319149e-06</v>
+        <v>3.5164232718433765e-06</v>
       </c>
       <c r="H22">
-        <v>1.5942545712687472e-05</v>
+        <v>1.3440128479261074e-05</v>
       </c>
       <c r="I22">
-        <v>-1.5242565842766108e-07</v>
+        <v>-8.9457257439142707e-08</v>
       </c>
       <c r="J22">
-        <v>-2.47302376772063e-07</v>
+        <v>-2.3589796548736957e-07</v>
       </c>
       <c r="K22">
-        <v>2.9848961278604991e-06</v>
+        <v>2.7034192129034835e-06</v>
       </c>
       <c r="L22">
-        <v>-7.4309136767208855e-06</v>
+        <v>-3.2083549705464349e-06</v>
       </c>
       <c r="M22">
-        <v>-9.3463584703514809e-07</v>
+        <v>-1.3556909987937132e-06</v>
       </c>
       <c r="N22">
-        <v>-2.1683503841257326e-06</v>
+        <v>-2.9113400901915666e-06</v>
       </c>
       <c r="O22">
-        <v>-2.80883941783318e-06</v>
+        <v>-4.4401585189376866e-06</v>
       </c>
       <c r="P22">
-        <v>-7.3103236347676152e-06</v>
+        <v>-8.9437289691714801e-06</v>
       </c>
       <c r="Q22">
-        <v>5.5001110873580757e-06</v>
+        <v>5.2792927337328599e-06</v>
       </c>
       <c r="R22">
-        <v>8.3710227685053373e-07</v>
+        <v>1.8032814053186563e-06</v>
       </c>
       <c r="S22">
-        <v>-2.3909358245420085e-06</v>
+        <v>-1.5058069435629418e-06</v>
       </c>
       <c r="T22">
-        <v>8.1393119473376692e-06</v>
+        <v>9.5411654398226646e-06</v>
       </c>
       <c r="U22">
-        <v>-2.8211321965545443e-07</v>
+        <v>1.0161843698381578e-06</v>
       </c>
       <c r="V22">
-        <v>5.2807664048829268e-06</v>
+        <v>5.4054820268133583e-06</v>
       </c>
       <c r="W22">
-        <v>0.00052647483248267457</v>
+        <v>0.00054229008954361402</v>
       </c>
       <c r="X22">
-        <v>3.7482334371068409e-05</v>
+        <v>3.2941834480353262e-05</v>
       </c>
       <c r="Y22">
-        <v>-4.4649934583265899e-05</v>
+        <v>-4.3338269283435703e-05</v>
       </c>
     </row>
     <row r="23">
@@ -3975,76 +3975,76 @@
         <v>43</v>
       </c>
       <c r="B23">
-        <v>0.10152919136694535</v>
+        <v>0.10585350426389045</v>
       </c>
       <c r="C23">
-        <v>2.9188835806084935e-06</v>
+        <v>5.8212419359163504e-07</v>
       </c>
       <c r="D23">
-        <v>9.5969579910589285e-06</v>
+        <v>6.5766276111471332e-06</v>
       </c>
       <c r="E23">
-        <v>-6.7546704682154576e-07</v>
+        <v>2.81561731566845e-07</v>
       </c>
       <c r="F23">
-        <v>2.8470515065478158e-09</v>
+        <v>-7.3035174080840374e-09</v>
       </c>
       <c r="G23">
-        <v>1.0146859009114377e-05</v>
+        <v>6.1814706224520246e-06</v>
       </c>
       <c r="H23">
-        <v>1.282983737758712e-05</v>
+        <v>8.0929138313141475e-06</v>
       </c>
       <c r="I23">
-        <v>-1.3822898401567202e-07</v>
+        <v>-9.0324261697324879e-08</v>
       </c>
       <c r="J23">
-        <v>-7.2897794159852285e-08</v>
+        <v>-5.2446991717774343e-08</v>
       </c>
       <c r="K23">
-        <v>6.4606430594300683e-06</v>
+        <v>8.1932214358755726e-06</v>
       </c>
       <c r="L23">
-        <v>-2.9111968417128596e-05</v>
+        <v>-7.1832783393610755e-06</v>
       </c>
       <c r="M23">
-        <v>-4.921581141314747e-06</v>
+        <v>-4.9414103891404907e-06</v>
       </c>
       <c r="N23">
-        <v>-6.5375264993869841e-06</v>
+        <v>-6.5313501605727725e-06</v>
       </c>
       <c r="O23">
-        <v>-2.7427582930699747e-06</v>
+        <v>-3.9346942739277752e-06</v>
       </c>
       <c r="P23">
-        <v>-5.1111078295608531e-06</v>
+        <v>-5.8095064108495878e-06</v>
       </c>
       <c r="Q23">
-        <v>4.7524926420566386e-06</v>
+        <v>4.4121196453801455e-06</v>
       </c>
       <c r="R23">
-        <v>-7.2203952460360568e-06</v>
+        <v>-5.1379565714724444e-06</v>
       </c>
       <c r="S23">
-        <v>-1.2412780384941919e-06</v>
+        <v>-9.74592210611528e-07</v>
       </c>
       <c r="T23">
-        <v>5.4295910347743422e-06</v>
+        <v>7.2317327120563419e-06</v>
       </c>
       <c r="U23">
-        <v>-4.5600031851447997e-07</v>
+        <v>4.8447017718101804e-07</v>
       </c>
       <c r="V23">
-        <v>1.9605768827186995e-06</v>
+        <v>2.3593985310642801e-06</v>
       </c>
       <c r="W23">
-        <v>3.7482334371068409e-05</v>
+        <v>3.2941834480353262e-05</v>
       </c>
       <c r="X23">
-        <v>0.00061924335570956207</v>
+        <v>0.00065287306084434876</v>
       </c>
       <c r="Y23">
-        <v>-2.059539587623336e-05</v>
+        <v>-3.2956895014691565e-05</v>
       </c>
     </row>
     <row r="24">
@@ -4052,76 +4052,76 @@
         <v>44</v>
       </c>
       <c r="B24">
-        <v>-2.0718776811725865</v>
+        <v>-2.345887481015275</v>
       </c>
       <c r="C24">
-        <v>-0.0010294999162681253</v>
+        <v>-0.0010091629345850475</v>
       </c>
       <c r="D24">
-        <v>-0.00021579444375254827</v>
+        <v>-0.00017795279878205056</v>
       </c>
       <c r="E24">
-        <v>-0.00026373953153217405</v>
+        <v>-0.00023829272713437683</v>
       </c>
       <c r="F24">
-        <v>2.4784389354271559e-06</v>
+        <v>2.2520893764479928e-06</v>
       </c>
       <c r="G24">
-        <v>-0.0017176667705921383</v>
+        <v>-0.0015973748514898495</v>
       </c>
       <c r="H24">
-        <v>-0.001641534893640093</v>
+        <v>-0.0017070767879386211</v>
       </c>
       <c r="I24">
-        <v>3.4119827807001024e-05</v>
+        <v>3.1810528837995031e-05</v>
       </c>
       <c r="J24">
-        <v>3.1628269683129238e-05</v>
+        <v>3.3037982872207643e-05</v>
       </c>
       <c r="K24">
-        <v>0.00024292610784200461</v>
+        <v>0.0001003666649968226</v>
       </c>
       <c r="L24">
-        <v>-0.00071992333683462348</v>
+        <v>0.00020857984561314282</v>
       </c>
       <c r="M24">
-        <v>-0.0048079674914148617</v>
+        <v>-0.0039260031461625022</v>
       </c>
       <c r="N24">
-        <v>-0.0048550492459284288</v>
+        <v>-0.0039684595616753726</v>
       </c>
       <c r="O24">
-        <v>-0.0049391848959026525</v>
+        <v>-0.0040473251642220553</v>
       </c>
       <c r="P24">
-        <v>-0.0051160007903314157</v>
+        <v>-0.0042099395338169848</v>
       </c>
       <c r="Q24">
-        <v>-0.00026285859601497033</v>
+        <v>-0.00025535226197773018</v>
       </c>
       <c r="R24">
-        <v>-0.00023944567755706451</v>
+        <v>-0.00022862382284855395</v>
       </c>
       <c r="S24">
-        <v>-0.00023469585957665515</v>
+        <v>-0.00021770546718838539</v>
       </c>
       <c r="T24">
-        <v>-0.00024633193862060818</v>
+        <v>-0.0002415196802777973</v>
       </c>
       <c r="U24">
-        <v>-0.00021936391431912701</v>
+        <v>-0.00020549649817245403</v>
       </c>
       <c r="V24">
-        <v>-0.00020700455199358791</v>
+        <v>-0.00018719933015364345</v>
       </c>
       <c r="W24">
-        <v>-4.4649934583265899e-05</v>
+        <v>-4.3338269283435703e-05</v>
       </c>
       <c r="X24">
-        <v>-2.059539587623336e-05</v>
+        <v>-3.2956895014691565e-05</v>
       </c>
       <c r="Y24">
-        <v>0.011687416587102381</v>
+        <v>0.010128412532825152</v>
       </c>
     </row>
   </sheetData>
@@ -4209,70 +4209,70 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>0.17014374725874731</v>
+        <v>0.18089287681396107</v>
       </c>
       <c r="C2">
-        <v>2.7641248179177731e-05</v>
+        <v>2.8212913668428682e-05</v>
       </c>
       <c r="D2">
-        <v>-2.9752309138037896e-07</v>
+        <v>-3.0691379851234826e-07</v>
       </c>
       <c r="E2">
-        <v>5.8394029302185777e-05</v>
+        <v>6.063477857212771e-05</v>
       </c>
       <c r="F2">
-        <v>1.9943208227427917e-05</v>
+        <v>3.3356012755703419e-05</v>
       </c>
       <c r="G2">
-        <v>-1.1948458505697271e-06</v>
+        <v>-1.2559209551958806e-06</v>
       </c>
       <c r="H2">
-        <v>-2.9320010919685017e-07</v>
+        <v>-6.3503684383640648e-07</v>
       </c>
       <c r="I2">
-        <v>-2.9712524022510405e-05</v>
+        <v>-1.4397647411004721e-05</v>
       </c>
       <c r="J2">
-        <v>0.00016081141338037384</v>
+        <v>-3.9679366302887217e-05</v>
       </c>
       <c r="K2">
-        <v>3.6510617712709015e-06</v>
+        <v>4.2028376785807685e-06</v>
       </c>
       <c r="L2">
-        <v>6.2889950113016039e-06</v>
+        <v>7.4441482841678547e-06</v>
       </c>
       <c r="M2">
-        <v>8.2166831471416972e-06</v>
+        <v>1.0437781295209378e-05</v>
       </c>
       <c r="N2">
-        <v>1.6531827363676571e-05</v>
+        <v>1.7487215950198862e-05</v>
       </c>
       <c r="O2">
-        <v>7.705159970196287e-07</v>
+        <v>2.8229266893473244e-06</v>
       </c>
       <c r="P2">
-        <v>1.2761219926602492e-06</v>
+        <v>3.966196669338332e-06</v>
       </c>
       <c r="Q2">
-        <v>-4.5510911764586781e-08</v>
+        <v>2.4485614070246394e-06</v>
       </c>
       <c r="R2">
-        <v>2.7833101866618982e-06</v>
+        <v>5.4005619281371689e-06</v>
       </c>
       <c r="S2">
-        <v>1.0676091693178568e-06</v>
+        <v>3.7941119332633169e-06</v>
       </c>
       <c r="T2">
-        <v>-1.5859953528869536e-06</v>
+        <v>-2.260043436936677e-07</v>
       </c>
       <c r="U2">
-        <v>6.4428046560659967e-07</v>
+        <v>7.4443879859393309e-07</v>
       </c>
       <c r="V2">
-        <v>-2.4608444896981984e-06</v>
+        <v>-1.2530163930393205e-06</v>
       </c>
       <c r="W2">
-        <v>-0.00059359067019433044</v>
+        <v>-0.00059580463930211712</v>
       </c>
     </row>
     <row r="3">
@@ -4280,70 +4280,70 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>-0.0018508176979263615</v>
+        <v>-0.0019629843801187408</v>
       </c>
       <c r="C3">
-        <v>-2.9752309138037896e-07</v>
+        <v>-3.0691379851234826e-07</v>
       </c>
       <c r="D3">
-        <v>3.35302866193851e-09</v>
+        <v>3.4688889446205778e-09</v>
       </c>
       <c r="E3">
-        <v>-8.3657930650728686e-08</v>
+        <v>-1.9754853126007579e-07</v>
       </c>
       <c r="F3">
-        <v>3.540701833779376e-07</v>
+        <v>1.0942923784018472e-07</v>
       </c>
       <c r="G3">
-        <v>1.6798347094729204e-10</v>
+        <v>2.9943114029847789e-09</v>
       </c>
       <c r="H3">
-        <v>-1.0014637822747125e-08</v>
+        <v>-3.9311914200199616e-09</v>
       </c>
       <c r="I3">
-        <v>2.9914837004289935e-07</v>
+        <v>1.2577045123085712e-07</v>
       </c>
       <c r="J3">
-        <v>-1.8367437377076091e-06</v>
+        <v>4.6375741995682274e-07</v>
       </c>
       <c r="K3">
-        <v>-3.9295665709805132e-08</v>
+        <v>-4.7539607402531409e-08</v>
       </c>
       <c r="L3">
-        <v>-6.2576892984300325e-08</v>
+        <v>-7.927015650839e-08</v>
       </c>
       <c r="M3">
-        <v>-6.4585399908488573e-08</v>
+        <v>-9.6075044869187431e-08</v>
       </c>
       <c r="N3">
-        <v>-1.236459840830648e-07</v>
+        <v>-1.4499094689611371e-07</v>
       </c>
       <c r="O3">
-        <v>-9.060370695877769e-09</v>
+        <v>-3.303726107889257e-08</v>
       </c>
       <c r="P3">
-        <v>-1.8017851790243963e-08</v>
+        <v>-4.7734409116666451e-08</v>
       </c>
       <c r="Q3">
-        <v>-3.333472753250566e-10</v>
+        <v>-2.8193403910187247e-08</v>
       </c>
       <c r="R3">
-        <v>-2.932623301597289e-08</v>
+        <v>-5.9293833597263886e-08</v>
       </c>
       <c r="S3">
-        <v>-8.8701674518747906e-09</v>
+        <v>-4.0261836804159125e-08</v>
       </c>
       <c r="T3">
-        <v>2.1438709781452967e-08</v>
+        <v>5.7295706707113009e-09</v>
       </c>
       <c r="U3">
-        <v>-1.2732135065008081e-08</v>
+        <v>-1.1439799954674747e-08</v>
       </c>
       <c r="V3">
-        <v>2.1652126458575811e-08</v>
+        <v>1.1122820945452113e-08</v>
       </c>
       <c r="W3">
-        <v>6.0770771535445493e-06</v>
+        <v>6.2060900132489428e-06</v>
       </c>
     </row>
     <row r="4">
@@ -4351,70 +4351,70 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>-0.33802256165219158</v>
+        <v>-0.27152055268581243</v>
       </c>
       <c r="C4">
-        <v>5.8394029302185777e-05</v>
+        <v>6.063477857212771e-05</v>
       </c>
       <c r="D4">
-        <v>-8.3657930650728686e-08</v>
+        <v>-1.9754853126007579e-07</v>
       </c>
       <c r="E4">
-        <v>0.0062484818541166977</v>
+        <v>0.0054203978755018433</v>
       </c>
       <c r="F4">
-        <v>0.0023390144439787252</v>
+        <v>0.0020539264026555202</v>
       </c>
       <c r="G4">
-        <v>-0.00013190667385029422</v>
+        <v>-0.00011340164810100889</v>
       </c>
       <c r="H4">
-        <v>-5.0650915671182051e-05</v>
+        <v>-4.4202376761918845e-05</v>
       </c>
       <c r="I4">
-        <v>-3.4766794955318233e-05</v>
+        <v>2.0658265705622886e-06</v>
       </c>
       <c r="J4">
-        <v>-0.00091301477034113254</v>
+        <v>-0.0001080580730689578</v>
       </c>
       <c r="K4">
-        <v>3.2614017622155135e-05</v>
+        <v>4.2464294603838156e-05</v>
       </c>
       <c r="L4">
-        <v>3.9119554126281782e-05</v>
+        <v>4.3060216919538143e-05</v>
       </c>
       <c r="M4">
-        <v>2.6904312381815766e-05</v>
+        <v>3.9098711939538353e-05</v>
       </c>
       <c r="N4">
-        <v>7.1764061345541696e-05</v>
+        <v>8.1062023029481985e-05</v>
       </c>
       <c r="O4">
-        <v>2.0966854594261814e-05</v>
+        <v>2.599957346847167e-05</v>
       </c>
       <c r="P4">
-        <v>2.8900472890601289e-05</v>
+        <v>3.0139903629620366e-05</v>
       </c>
       <c r="Q4">
-        <v>8.5898755718704239e-06</v>
+        <v>1.6520134236658164e-05</v>
       </c>
       <c r="R4">
-        <v>2.4301926811353437e-06</v>
+        <v>1.5319065618404014e-05</v>
       </c>
       <c r="S4">
-        <v>-2.9850623349376928e-05</v>
+        <v>-1.0223069220110485e-05</v>
       </c>
       <c r="T4">
-        <v>-8.6732879960193984e-06</v>
+        <v>-1.6559814167977748e-07</v>
       </c>
       <c r="U4">
-        <v>1.8501259477093743e-05</v>
+        <v>1.5951222429015683e-05</v>
       </c>
       <c r="V4">
-        <v>2.8483267344695754e-05</v>
+        <v>2.8115213761436599e-05</v>
       </c>
       <c r="W4">
-        <v>-0.0025197464125829567</v>
+        <v>-0.0023801401078947602</v>
       </c>
     </row>
     <row r="5">
@@ -4422,70 +4422,70 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>-0.38331208009613871</v>
+        <v>-0.36622317016271977</v>
       </c>
       <c r="C5">
-        <v>1.9943208227427917e-05</v>
+        <v>3.3356012755703419e-05</v>
       </c>
       <c r="D5">
-        <v>3.540701833779376e-07</v>
+        <v>1.0942923784018472e-07</v>
       </c>
       <c r="E5">
-        <v>0.0023390144439787252</v>
+        <v>0.0020539264026555202</v>
       </c>
       <c r="F5">
-        <v>0.0056137678150741431</v>
+        <v>0.0050535262368869016</v>
       </c>
       <c r="G5">
-        <v>-5.0982736715361419e-05</v>
+        <v>-4.4455034063569681e-05</v>
       </c>
       <c r="H5">
-        <v>-0.00011520850467847132</v>
+        <v>-0.00010307170964818179</v>
       </c>
       <c r="I5">
-        <v>-2.4273691368978177e-05</v>
+        <v>2.2843827951540523e-05</v>
       </c>
       <c r="J5">
-        <v>-0.0015435138978368913</v>
+        <v>-0.00015317044663431837</v>
       </c>
       <c r="K5">
-        <v>3.8335730390101046e-05</v>
+        <v>3.1424032450837755e-05</v>
       </c>
       <c r="L5">
-        <v>1.1874579954668238e-06</v>
+        <v>-1.1132732308966357e-06</v>
       </c>
       <c r="M5">
-        <v>-1.9503099936211304e-05</v>
+        <v>-1.1206726195968309e-05</v>
       </c>
       <c r="N5">
-        <v>4.8283929973070806e-05</v>
+        <v>4.7530408677333024e-05</v>
       </c>
       <c r="O5">
-        <v>1.9205211876510931e-05</v>
+        <v>2.2028409212036811e-05</v>
       </c>
       <c r="P5">
-        <v>-1.6822782732872847e-05</v>
+        <v>-1.0838641651333534e-05</v>
       </c>
       <c r="Q5">
-        <v>-7.4351468300296375e-05</v>
+        <v>-5.6215128617929705e-05</v>
       </c>
       <c r="R5">
-        <v>-3.704536155166998e-05</v>
+        <v>-2.4961829883317909e-05</v>
       </c>
       <c r="S5">
-        <v>-0.00011679445542834764</v>
+        <v>-9.5365212390587952e-05</v>
       </c>
       <c r="T5">
-        <v>-8.0583503672852257e-05</v>
+        <v>-6.031309723040548e-05</v>
       </c>
       <c r="U5">
-        <v>2.8927638536724631e-05</v>
+        <v>3.2369995515503299e-05</v>
       </c>
       <c r="V5">
-        <v>4.1511906589945642e-05</v>
+        <v>4.3041152185741951e-05</v>
       </c>
       <c r="W5">
-        <v>-0.0016560323521552008</v>
+        <v>-0.0017237712088299412</v>
       </c>
     </row>
     <row r="6">
@@ -4493,70 +4493,70 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>0.0040707227108623982</v>
+        <v>0.0017773661695320868</v>
       </c>
       <c r="C6">
-        <v>-1.1948458505697271e-06</v>
+        <v>-1.2559209551958806e-06</v>
       </c>
       <c r="D6">
-        <v>1.6798347094729204e-10</v>
+        <v>2.9943114029847789e-09</v>
       </c>
       <c r="E6">
-        <v>-0.00013190667385029422</v>
+        <v>-0.00011340164810100889</v>
       </c>
       <c r="F6">
-        <v>-5.0982736715361419e-05</v>
+        <v>-4.4455034063569681e-05</v>
       </c>
       <c r="G6">
-        <v>2.9852442316628557e-06</v>
+        <v>2.5429865299558371e-06</v>
       </c>
       <c r="H6">
-        <v>1.1811109353561096e-06</v>
+        <v>1.0227883541590456e-06</v>
       </c>
       <c r="I6">
-        <v>7.8701214649372011e-07</v>
+        <v>-5.8620147961938666e-08</v>
       </c>
       <c r="J6">
-        <v>1.9033474556482359e-05</v>
+        <v>2.4132211773751256e-06</v>
       </c>
       <c r="K6">
-        <v>-3.7308452549334355e-07</v>
+        <v>-5.4336720171077805e-07</v>
       </c>
       <c r="L6">
-        <v>-5.6590254061306472e-07</v>
+        <v>-5.9585217425194744e-07</v>
       </c>
       <c r="M6">
-        <v>2.1439546846429527e-07</v>
+        <v>-7.732426681770509e-08</v>
       </c>
       <c r="N6">
-        <v>-4.5671431492077351e-07</v>
+        <v>-7.0516570278752119e-07</v>
       </c>
       <c r="O6">
-        <v>-1.7532779879655227e-07</v>
+        <v>-3.0470227802096388e-07</v>
       </c>
       <c r="P6">
-        <v>-4.3421541706204456e-07</v>
+        <v>-5.3078848873932977e-07</v>
       </c>
       <c r="Q6">
-        <v>-1.6469409410990925e-07</v>
+        <v>-3.3794786108738866e-07</v>
       </c>
       <c r="R6">
-        <v>-2.0110568675159677e-07</v>
+        <v>-4.766370617079262e-07</v>
       </c>
       <c r="S6">
-        <v>5.3371271921616794e-07</v>
+        <v>1.4481119756810726e-07</v>
       </c>
       <c r="T6">
-        <v>-4.3486899884683458e-08</v>
+        <v>-1.8760321035369524e-07</v>
       </c>
       <c r="U6">
-        <v>-1.8409577426498135e-07</v>
+        <v>-1.8809430049115851e-07</v>
       </c>
       <c r="V6">
-        <v>-3.7475403016374888e-07</v>
+        <v>-4.5847018074486989e-07</v>
       </c>
       <c r="W6">
-        <v>5.0807519243301652e-05</v>
+        <v>4.8074717002199028e-05</v>
       </c>
     </row>
     <row r="7">
@@ -4564,70 +4564,70 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>-0.00026934857912513368</v>
+        <v>-0.0015926984005508531</v>
       </c>
       <c r="C7">
-        <v>-2.9320010919685017e-07</v>
+        <v>-6.3503684383640648e-07</v>
       </c>
       <c r="D7">
-        <v>-1.0014637822747125e-08</v>
+        <v>-3.9311914200199616e-09</v>
       </c>
       <c r="E7">
-        <v>-5.0650915671182051e-05</v>
+        <v>-4.4202376761918845e-05</v>
       </c>
       <c r="F7">
-        <v>-0.00011520850467847132</v>
+        <v>-0.00010307170964818179</v>
       </c>
       <c r="G7">
-        <v>1.1811109353561096e-06</v>
+        <v>1.0227883541590456e-06</v>
       </c>
       <c r="H7">
-        <v>2.5277830860317053e-06</v>
+        <v>2.2438032928197734e-06</v>
       </c>
       <c r="I7">
-        <v>2.1603443374333957e-07</v>
+        <v>-7.883536688883599e-07</v>
       </c>
       <c r="J7">
-        <v>3.1090882260400725e-05</v>
+        <v>3.416956312080981e-06</v>
       </c>
       <c r="K7">
-        <v>-9.5582888537576614e-07</v>
+        <v>-7.8597116053919424e-07</v>
       </c>
       <c r="L7">
-        <v>9.2499442936916578e-08</v>
+        <v>1.0203691265460072e-07</v>
       </c>
       <c r="M7">
-        <v>1.4409741923628842e-06</v>
+        <v>1.0716499487448371e-06</v>
       </c>
       <c r="N7">
-        <v>5.1103239425865161e-07</v>
+        <v>2.3770926427101751e-07</v>
       </c>
       <c r="O7">
-        <v>1.6360988913932569e-08</v>
+        <v>-1.3503755523513163e-07</v>
       </c>
       <c r="P7">
-        <v>9.7152109445072656e-07</v>
+        <v>7.0406438012282245e-07</v>
       </c>
       <c r="Q7">
-        <v>1.2246797172414812e-06</v>
+        <v>8.5989235956969206e-07</v>
       </c>
       <c r="R7">
-        <v>8.1351876415390696e-07</v>
+        <v>5.1460498825877545e-07</v>
       </c>
       <c r="S7">
-        <v>1.9325278104527057e-06</v>
+        <v>1.5035721594131189e-06</v>
       </c>
       <c r="T7">
-        <v>1.4709641125568748e-06</v>
+        <v>1.0564369302850906e-06</v>
       </c>
       <c r="U7">
-        <v>-2.6681804510713692e-07</v>
+        <v>-4.6454352798112921e-07</v>
       </c>
       <c r="V7">
-        <v>-2.1963049024837856e-07</v>
+        <v>-4.4799985437316903e-07</v>
       </c>
       <c r="W7">
-        <v>3.0501911214222998e-05</v>
+        <v>3.3253971797968724e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4635,70 +4635,70 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>-0.0046494359518024549</v>
+        <v>0.011237057209964908</v>
       </c>
       <c r="C8">
-        <v>-2.9712524022510405e-05</v>
+        <v>-1.4397647411004721e-05</v>
       </c>
       <c r="D8">
-        <v>2.9914837004289935e-07</v>
+        <v>1.2577045123085712e-07</v>
       </c>
       <c r="E8">
-        <v>-3.4766794955318233e-05</v>
+        <v>2.0658265705622886e-06</v>
       </c>
       <c r="F8">
-        <v>-2.4273691368978177e-05</v>
+        <v>2.2843827951540523e-05</v>
       </c>
       <c r="G8">
-        <v>7.8701214649372011e-07</v>
+        <v>-5.8620147961938666e-08</v>
       </c>
       <c r="H8">
-        <v>2.1603443374333957e-07</v>
+        <v>-7.883536688883599e-07</v>
       </c>
       <c r="I8">
-        <v>0.00031806895373103845</v>
+        <v>0.00030541345328910491</v>
       </c>
       <c r="J8">
-        <v>-3.3451692978826539e-05</v>
+        <v>-9.9022114498574442e-05</v>
       </c>
       <c r="K8">
-        <v>-1.163685199377583e-05</v>
+        <v>-1.3873904259895689e-05</v>
       </c>
       <c r="L8">
-        <v>-2.2979749744229155e-05</v>
+        <v>-2.1690594962824576e-05</v>
       </c>
       <c r="M8">
-        <v>-3.6073269483900146e-05</v>
+        <v>-3.1420034970895341e-05</v>
       </c>
       <c r="N8">
-        <v>-3.4098805278405466e-05</v>
+        <v>-2.9780660796980464e-05</v>
       </c>
       <c r="O8">
-        <v>-8.2078193977082233e-06</v>
+        <v>-2.8389918702481635e-06</v>
       </c>
       <c r="P8">
-        <v>7.3286828540267778e-06</v>
+        <v>1.0046695204955815e-05</v>
       </c>
       <c r="Q8">
-        <v>-5.6297964760295236e-06</v>
+        <v>-2.4553952783814192e-06</v>
       </c>
       <c r="R8">
-        <v>-8.7334575095057433e-06</v>
+        <v>-4.2684872494050983e-06</v>
       </c>
       <c r="S8">
-        <v>-2.606697666044876e-06</v>
+        <v>2.0932982755478784e-06</v>
       </c>
       <c r="T8">
-        <v>1.9901236583877612e-05</v>
+        <v>1.9162917473249433e-05</v>
       </c>
       <c r="U8">
-        <v>-5.9311727403353487e-06</v>
+        <v>-4.1330805374154734e-06</v>
       </c>
       <c r="V8">
-        <v>-6.1797809405181669e-06</v>
+        <v>-3.5013528475145101e-06</v>
       </c>
       <c r="W8">
-        <v>0.00052362790018054656</v>
+        <v>0.00025058448675194386</v>
       </c>
     </row>
     <row r="9">
@@ -4706,70 +4706,70 @@
         <v>31</v>
       </c>
       <c r="B9">
-        <v>-1.2249560361058816</v>
+        <v>-0.067066454648628135</v>
       </c>
       <c r="C9">
-        <v>0.00016081141338037384</v>
+        <v>-3.9679366302887217e-05</v>
       </c>
       <c r="D9">
-        <v>-1.8367437377076091e-06</v>
+        <v>4.6375741995682274e-07</v>
       </c>
       <c r="E9">
-        <v>-0.00091301477034113254</v>
+        <v>-0.0001080580730689578</v>
       </c>
       <c r="F9">
-        <v>-0.0015435138978368913</v>
+        <v>-0.00015317044663431837</v>
       </c>
       <c r="G9">
-        <v>1.9033474556482359e-05</v>
+        <v>2.4132211773751256e-06</v>
       </c>
       <c r="H9">
-        <v>3.1090882260400725e-05</v>
+        <v>3.416956312080981e-06</v>
       </c>
       <c r="I9">
-        <v>-3.3451692978826539e-05</v>
+        <v>-9.9022114498574442e-05</v>
       </c>
       <c r="J9">
-        <v>0.26499699863351184</v>
+        <v>0.00035472363758384486</v>
       </c>
       <c r="K9">
-        <v>1.7411053795563521e-06</v>
+        <v>-1.933984459083775e-06</v>
       </c>
       <c r="L9">
-        <v>1.2524489490131492e-05</v>
+        <v>-1.0576689999532813e-05</v>
       </c>
       <c r="M9">
-        <v>4.3658215107989195e-05</v>
+        <v>-2.0697117126476888e-05</v>
       </c>
       <c r="N9">
-        <v>-3.825337019856601e-05</v>
+        <v>-2.1731803636424753e-05</v>
       </c>
       <c r="O9">
-        <v>1.7949650897805859e-05</v>
+        <v>-1.4742208723077788e-05</v>
       </c>
       <c r="P9">
-        <v>4.4802395825620039e-05</v>
+        <v>-1.5373924110957966e-05</v>
       </c>
       <c r="Q9">
-        <v>6.7766769180182033e-05</v>
+        <v>-1.3802407198192849e-05</v>
       </c>
       <c r="R9">
-        <v>5.0253621813979872e-05</v>
+        <v>-1.6767369914502567e-05</v>
       </c>
       <c r="S9">
-        <v>1.9353312420564719e-05</v>
+        <v>-1.8532693821311366e-05</v>
       </c>
       <c r="T9">
-        <v>0.00011820103657441367</v>
+        <v>-7.5491457290265346e-06</v>
       </c>
       <c r="U9">
-        <v>5.2480443651226256e-05</v>
+        <v>-6.1301798897019849e-06</v>
       </c>
       <c r="V9">
-        <v>2.3362080216173504e-05</v>
+        <v>-8.6713804594057136e-06</v>
       </c>
       <c r="W9">
-        <v>-0.003333707186346417</v>
+        <v>0.00073539763712275152</v>
       </c>
     </row>
     <row r="10">
@@ -4777,70 +4777,70 @@
         <v>32</v>
       </c>
       <c r="B10">
-        <v>0.22800117834656972</v>
+        <v>0.18373691429854508</v>
       </c>
       <c r="C10">
-        <v>3.6510617712709015e-06</v>
+        <v>4.2028376785807685e-06</v>
       </c>
       <c r="D10">
-        <v>-3.9295665709805132e-08</v>
+        <v>-4.7539607402531409e-08</v>
       </c>
       <c r="E10">
-        <v>3.2614017622155135e-05</v>
+        <v>4.2464294603838156e-05</v>
       </c>
       <c r="F10">
-        <v>3.8335730390101046e-05</v>
+        <v>3.1424032450837755e-05</v>
       </c>
       <c r="G10">
-        <v>-3.7308452549334355e-07</v>
+        <v>-5.4336720171077805e-07</v>
       </c>
       <c r="H10">
-        <v>-9.5582888537576614e-07</v>
+        <v>-7.8597116053919424e-07</v>
       </c>
       <c r="I10">
-        <v>-1.163685199377583e-05</v>
+        <v>-1.3873904259895689e-05</v>
       </c>
       <c r="J10">
-        <v>1.7411053795563521e-06</v>
+        <v>-1.933984459083775e-06</v>
       </c>
       <c r="K10">
-        <v>0.011996860277546236</v>
+        <v>0.010045728191650874</v>
       </c>
       <c r="L10">
-        <v>0.0099307463012206863</v>
+        <v>0.0083056359566592384</v>
       </c>
       <c r="M10">
-        <v>0.0099278855991242962</v>
+        <v>0.0083025286830316607</v>
       </c>
       <c r="N10">
-        <v>0.0099248852094064467</v>
+        <v>0.0082985549939215315</v>
       </c>
       <c r="O10">
-        <v>2.0991702486070284e-05</v>
+        <v>1.2307005584410866e-05</v>
       </c>
       <c r="P10">
-        <v>4.4083330463202299e-05</v>
+        <v>3.7392509999887669e-05</v>
       </c>
       <c r="Q10">
-        <v>1.8354590839911024e-05</v>
+        <v>2.5549619243840432e-05</v>
       </c>
       <c r="R10">
-        <v>1.7502692522889457e-05</v>
+        <v>2.9361686160015165e-05</v>
       </c>
       <c r="S10">
-        <v>2.6272956383322867e-05</v>
+        <v>2.6052897418697094e-05</v>
       </c>
       <c r="T10">
-        <v>6.0247749972652565e-05</v>
+        <v>6.3604519814932238e-05</v>
       </c>
       <c r="U10">
-        <v>-1.4915699964949509e-05</v>
+        <v>-1.0893199412724915e-05</v>
       </c>
       <c r="V10">
-        <v>3.6694161314550386e-05</v>
+        <v>3.1086774629481877e-05</v>
       </c>
       <c r="W10">
-        <v>-0.010024002271480469</v>
+        <v>-0.0084058833483083573</v>
       </c>
     </row>
     <row r="11">
@@ -4848,70 +4848,70 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>0.458261994672364</v>
+        <v>0.42231251129335928</v>
       </c>
       <c r="C11">
-        <v>6.2889950113016039e-06</v>
+        <v>7.4441482841678547e-06</v>
       </c>
       <c r="D11">
-        <v>-6.2576892984300325e-08</v>
+        <v>-7.927015650839e-08</v>
       </c>
       <c r="E11">
-        <v>3.9119554126281782e-05</v>
+        <v>4.3060216919538143e-05</v>
       </c>
       <c r="F11">
-        <v>1.1874579954668238e-06</v>
+        <v>-1.1132732308966357e-06</v>
       </c>
       <c r="G11">
-        <v>-5.6590254061306472e-07</v>
+        <v>-5.9585217425194744e-07</v>
       </c>
       <c r="H11">
-        <v>9.2499442936916578e-08</v>
+        <v>1.0203691265460072e-07</v>
       </c>
       <c r="I11">
-        <v>-2.2979749744229155e-05</v>
+        <v>-2.1690594962824576e-05</v>
       </c>
       <c r="J11">
-        <v>1.2524489490131492e-05</v>
+        <v>-1.0576689999532813e-05</v>
       </c>
       <c r="K11">
-        <v>0.0099307463012206863</v>
+        <v>0.0083056359566592384</v>
       </c>
       <c r="L11">
-        <v>0.010294318498476172</v>
+        <v>0.0086119814891286797</v>
       </c>
       <c r="M11">
-        <v>0.009936176237852078</v>
+        <v>0.0083097659464238319</v>
       </c>
       <c r="N11">
-        <v>0.009939098564167451</v>
+        <v>0.0083109663353309726</v>
       </c>
       <c r="O11">
-        <v>-1.4966078079019057e-06</v>
+        <v>-7.3782835128364404e-06</v>
       </c>
       <c r="P11">
-        <v>1.4085628590994038e-05</v>
+        <v>1.1574224310175558e-05</v>
       </c>
       <c r="Q11">
-        <v>-1.0119234219867484e-05</v>
+        <v>4.278264441372339e-06</v>
       </c>
       <c r="R11">
-        <v>4.2900460984274778e-06</v>
+        <v>1.6779112074569375e-05</v>
       </c>
       <c r="S11">
-        <v>-2.7713845261787437e-06</v>
+        <v>8.5049575997847311e-07</v>
       </c>
       <c r="T11">
-        <v>1.6082066797378114e-05</v>
+        <v>2.9610352200449452e-05</v>
       </c>
       <c r="U11">
-        <v>-1.81417392115132e-05</v>
+        <v>-1.5517592066413316e-05</v>
       </c>
       <c r="V11">
-        <v>3.2174505271338713e-05</v>
+        <v>2.8611271935898903e-05</v>
       </c>
       <c r="W11">
-        <v>-0.010075066009677398</v>
+        <v>-0.0084661599263487521</v>
       </c>
     </row>
     <row r="12">
@@ -4919,70 +4919,70 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0.62017909682280792</v>
+        <v>0.59055375337138849</v>
       </c>
       <c r="C12">
-        <v>8.2166831471416972e-06</v>
+        <v>1.0437781295209378e-05</v>
       </c>
       <c r="D12">
-        <v>-6.4585399908488573e-08</v>
+        <v>-9.6075044869187431e-08</v>
       </c>
       <c r="E12">
-        <v>2.6904312381815766e-05</v>
+        <v>3.9098711939538353e-05</v>
       </c>
       <c r="F12">
-        <v>-1.9503099936211304e-05</v>
+        <v>-1.1206726195968309e-05</v>
       </c>
       <c r="G12">
-        <v>2.1439546846429527e-07</v>
+        <v>-7.732426681770509e-08</v>
       </c>
       <c r="H12">
-        <v>1.4409741923628842e-06</v>
+        <v>1.0716499487448371e-06</v>
       </c>
       <c r="I12">
-        <v>-3.6073269483900146e-05</v>
+        <v>-3.1420034970895341e-05</v>
       </c>
       <c r="J12">
-        <v>4.3658215107989195e-05</v>
+        <v>-2.0697117126476888e-05</v>
       </c>
       <c r="K12">
-        <v>0.0099278855991242962</v>
+        <v>0.0083025286830316607</v>
       </c>
       <c r="L12">
-        <v>0.009936176237852078</v>
+        <v>0.0083097659464238319</v>
       </c>
       <c r="M12">
-        <v>0.010062435486731488</v>
+        <v>0.0084193913005867708</v>
       </c>
       <c r="N12">
-        <v>0.0099791152717346766</v>
+        <v>0.0083438776297522464</v>
       </c>
       <c r="O12">
-        <v>-1.7926795352679869e-05</v>
+        <v>-1.9062794287339976e-05</v>
       </c>
       <c r="P12">
-        <v>4.7982103806131071e-06</v>
+        <v>6.1133393623238874e-06</v>
       </c>
       <c r="Q12">
-        <v>-2.7373492872553125e-05</v>
+        <v>-9.1106574615597486e-06</v>
       </c>
       <c r="R12">
-        <v>-9.5150565468413429e-06</v>
+        <v>7.4634355775772413e-06</v>
       </c>
       <c r="S12">
-        <v>-1.5376978392558241e-05</v>
+        <v>-8.2807623491552341e-06</v>
       </c>
       <c r="T12">
-        <v>2.5813175832062609e-05</v>
+        <v>3.9261263618007132e-05</v>
       </c>
       <c r="U12">
-        <v>-1.883973666230486e-05</v>
+        <v>-1.8194938227746931e-05</v>
       </c>
       <c r="V12">
-        <v>3.6563390223014352e-05</v>
+        <v>3.0842942201597627e-05</v>
       </c>
       <c r="W12">
-        <v>-0.010180503499418746</v>
+        <v>-0.008581535024973776</v>
       </c>
     </row>
     <row r="13">
@@ -4990,70 +4990,70 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>0.62176838212978269</v>
+        <v>0.61398603387151329</v>
       </c>
       <c r="C13">
-        <v>1.6531827363676571e-05</v>
+        <v>1.7487215950198862e-05</v>
       </c>
       <c r="D13">
-        <v>-1.236459840830648e-07</v>
+        <v>-1.4499094689611371e-07</v>
       </c>
       <c r="E13">
-        <v>7.1764061345541696e-05</v>
+        <v>8.1062023029481985e-05</v>
       </c>
       <c r="F13">
-        <v>4.8283929973070806e-05</v>
+        <v>4.7530408677333024e-05</v>
       </c>
       <c r="G13">
-        <v>-4.5671431492077351e-07</v>
+        <v>-7.0516570278752119e-07</v>
       </c>
       <c r="H13">
-        <v>5.1103239425865161e-07</v>
+        <v>2.3770926427101751e-07</v>
       </c>
       <c r="I13">
-        <v>-3.4098805278405466e-05</v>
+        <v>-2.9780660796980464e-05</v>
       </c>
       <c r="J13">
-        <v>-3.825337019856601e-05</v>
+        <v>-2.1731803636424753e-05</v>
       </c>
       <c r="K13">
-        <v>0.0099248852094064467</v>
+        <v>0.0082985549939215315</v>
       </c>
       <c r="L13">
-        <v>0.009939098564167451</v>
+        <v>0.0083109663353309726</v>
       </c>
       <c r="M13">
-        <v>0.0099791152717346766</v>
+        <v>0.0083438776297522464</v>
       </c>
       <c r="N13">
-        <v>0.010364705026425836</v>
+        <v>0.0086893342071832115</v>
       </c>
       <c r="O13">
-        <v>-3.6511549441189977e-05</v>
+        <v>-3.5069800268511275e-05</v>
       </c>
       <c r="P13">
-        <v>-2.0322990590757065e-05</v>
+        <v>-1.497059078441965e-05</v>
       </c>
       <c r="Q13">
-        <v>-3.8144505001714748e-05</v>
+        <v>-1.6954410243606868e-05</v>
       </c>
       <c r="R13">
-        <v>-4.1644807801824919e-05</v>
+        <v>-1.7618570052276386e-05</v>
       </c>
       <c r="S13">
-        <v>-4.2854933628888447e-05</v>
+        <v>-3.0955975819405522e-05</v>
       </c>
       <c r="T13">
-        <v>4.1535868367828817e-06</v>
+        <v>2.0652545769368004e-05</v>
       </c>
       <c r="U13">
-        <v>-2.5205775768008805e-05</v>
+        <v>-2.547821829792273e-05</v>
       </c>
       <c r="V13">
-        <v>3.3571330108055821e-05</v>
+        <v>2.7384510137669768e-05</v>
       </c>
       <c r="W13">
-        <v>-0.010438023339420467</v>
+        <v>-0.0088014022867021775</v>
       </c>
     </row>
     <row r="14">
@@ -5061,70 +5061,70 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>0.038913533961997489</v>
+        <v>0.047730861148993373</v>
       </c>
       <c r="C14">
-        <v>7.705159970196287e-07</v>
+        <v>2.8229266893473244e-06</v>
       </c>
       <c r="D14">
-        <v>-9.060370695877769e-09</v>
+        <v>-3.303726107889257e-08</v>
       </c>
       <c r="E14">
-        <v>2.0966854594261814e-05</v>
+        <v>2.599957346847167e-05</v>
       </c>
       <c r="F14">
-        <v>1.9205211876510931e-05</v>
+        <v>2.2028409212036811e-05</v>
       </c>
       <c r="G14">
-        <v>-1.7532779879655227e-07</v>
+        <v>-3.0470227802096388e-07</v>
       </c>
       <c r="H14">
-        <v>1.6360988913932569e-08</v>
+        <v>-1.3503755523513163e-07</v>
       </c>
       <c r="I14">
-        <v>-8.2078193977082233e-06</v>
+        <v>-2.8389918702481635e-06</v>
       </c>
       <c r="J14">
-        <v>1.7949650897805859e-05</v>
+        <v>-1.4742208723077788e-05</v>
       </c>
       <c r="K14">
-        <v>2.0991702486070284e-05</v>
+        <v>1.2307005584410866e-05</v>
       </c>
       <c r="L14">
-        <v>-1.4966078079019057e-06</v>
+        <v>-7.3782835128364404e-06</v>
       </c>
       <c r="M14">
-        <v>-1.7926795352679869e-05</v>
+        <v>-1.9062794287339976e-05</v>
       </c>
       <c r="N14">
-        <v>-3.6511549441189977e-05</v>
+        <v>-3.5069800268511275e-05</v>
       </c>
       <c r="O14">
-        <v>0.00088185088718027997</v>
+        <v>0.00078788751528976477</v>
       </c>
       <c r="P14">
-        <v>0.00047211848011037181</v>
+        <v>0.00042442360439880693</v>
       </c>
       <c r="Q14">
-        <v>0.00046923668070882545</v>
+        <v>0.00042216584961812901</v>
       </c>
       <c r="R14">
-        <v>0.0004710651843647419</v>
+        <v>0.00042366929378590614</v>
       </c>
       <c r="S14">
-        <v>0.000469497365033381</v>
+        <v>0.00042262458653135986</v>
       </c>
       <c r="T14">
-        <v>0.00046818112937872293</v>
+        <v>0.00042096771102720658</v>
       </c>
       <c r="U14">
-        <v>1.7360087563435116e-06</v>
+        <v>4.511674315152125e-06</v>
       </c>
       <c r="V14">
-        <v>-5.3093052501861922e-07</v>
+        <v>5.955067363998736e-07</v>
       </c>
       <c r="W14">
-        <v>-0.00047255300945799831</v>
+        <v>-0.00046041484561411771</v>
       </c>
     </row>
     <row r="15">
@@ -5132,70 +5132,70 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>0.042330565213303015</v>
+        <v>0.073644463486289766</v>
       </c>
       <c r="C15">
-        <v>1.2761219926602492e-06</v>
+        <v>3.966196669338332e-06</v>
       </c>
       <c r="D15">
-        <v>-1.8017851790243963e-08</v>
+        <v>-4.7734409116666451e-08</v>
       </c>
       <c r="E15">
-        <v>2.8900472890601289e-05</v>
+        <v>3.0139903629620366e-05</v>
       </c>
       <c r="F15">
-        <v>-1.6822782732872847e-05</v>
+        <v>-1.0838641651333534e-05</v>
       </c>
       <c r="G15">
-        <v>-4.3421541706204456e-07</v>
+        <v>-5.3078848873932977e-07</v>
       </c>
       <c r="H15">
-        <v>9.7152109445072656e-07</v>
+        <v>7.0406438012282245e-07</v>
       </c>
       <c r="I15">
-        <v>7.3286828540267778e-06</v>
+        <v>1.0046695204955815e-05</v>
       </c>
       <c r="J15">
-        <v>4.4802395825620039e-05</v>
+        <v>-1.5373924110957966e-05</v>
       </c>
       <c r="K15">
-        <v>4.4083330463202299e-05</v>
+        <v>3.7392509999887669e-05</v>
       </c>
       <c r="L15">
-        <v>1.4085628590994038e-05</v>
+        <v>1.1574224310175558e-05</v>
       </c>
       <c r="M15">
-        <v>4.7982103806131071e-06</v>
+        <v>6.1133393623238874e-06</v>
       </c>
       <c r="N15">
-        <v>-2.0322990590757065e-05</v>
+        <v>-1.497059078441965e-05</v>
       </c>
       <c r="O15">
-        <v>0.00047211848011037181</v>
+        <v>0.00042442360439880693</v>
       </c>
       <c r="P15">
-        <v>0.0010629374166165224</v>
+        <v>0.00094675269720894935</v>
       </c>
       <c r="Q15">
-        <v>0.00046927009111282924</v>
+        <v>0.00042214722913441744</v>
       </c>
       <c r="R15">
-        <v>0.00047173769707258039</v>
+        <v>0.00042438899469800776</v>
       </c>
       <c r="S15">
-        <v>0.00047014273902040276</v>
+        <v>0.00042329754278658846</v>
       </c>
       <c r="T15">
-        <v>0.00047047650778599451</v>
+        <v>0.00042305978563627678</v>
       </c>
       <c r="U15">
-        <v>-5.1777168574167428e-06</v>
+        <v>-2.3792089849083077e-06</v>
       </c>
       <c r="V15">
-        <v>-1.431906753762378e-05</v>
+        <v>-1.0135363846915328e-05</v>
       </c>
       <c r="W15">
-        <v>-0.00050786740170574057</v>
+        <v>-0.00051168780119030749</v>
       </c>
     </row>
     <row r="16">
@@ -5203,70 +5203,70 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>-0.099250221202378683</v>
+        <v>-0.078750656186057547</v>
       </c>
       <c r="C16">
-        <v>-4.5510911764586781e-08</v>
+        <v>2.4485614070246394e-06</v>
       </c>
       <c r="D16">
-        <v>-3.333472753250566e-10</v>
+        <v>-2.8193403910187247e-08</v>
       </c>
       <c r="E16">
-        <v>8.5898755718704239e-06</v>
+        <v>1.6520134236658164e-05</v>
       </c>
       <c r="F16">
-        <v>-7.4351468300296375e-05</v>
+        <v>-5.6215128617929705e-05</v>
       </c>
       <c r="G16">
-        <v>-1.6469409410990925e-07</v>
+        <v>-3.3794786108738866e-07</v>
       </c>
       <c r="H16">
-        <v>1.2246797172414812e-06</v>
+        <v>8.5989235956969206e-07</v>
       </c>
       <c r="I16">
-        <v>-5.6297964760295236e-06</v>
+        <v>-2.4553952783814192e-06</v>
       </c>
       <c r="J16">
-        <v>6.7766769180182033e-05</v>
+        <v>-1.3802407198192849e-05</v>
       </c>
       <c r="K16">
-        <v>1.8354590839911024e-05</v>
+        <v>2.5549619243840432e-05</v>
       </c>
       <c r="L16">
-        <v>-1.0119234219867484e-05</v>
+        <v>4.278264441372339e-06</v>
       </c>
       <c r="M16">
-        <v>-2.7373492872553125e-05</v>
+        <v>-9.1106574615597486e-06</v>
       </c>
       <c r="N16">
-        <v>-3.8144505001714748e-05</v>
+        <v>-1.6954410243606868e-05</v>
       </c>
       <c r="O16">
-        <v>0.00046923668070882545</v>
+        <v>0.00042216584961812901</v>
       </c>
       <c r="P16">
-        <v>0.00046927009111282924</v>
+        <v>0.00042214722913441744</v>
       </c>
       <c r="Q16">
-        <v>0.00087148373394928301</v>
+        <v>0.000781690444002283</v>
       </c>
       <c r="R16">
-        <v>0.00047043437434652583</v>
+        <v>0.00042322053426806683</v>
       </c>
       <c r="S16">
-        <v>0.00047312580990481359</v>
+        <v>0.00042570182051519914</v>
       </c>
       <c r="T16">
-        <v>0.00047010430500697502</v>
+        <v>0.00042237196742181692</v>
       </c>
       <c r="U16">
-        <v>-1.1203049043353548e-05</v>
+        <v>-8.433700117015425e-06</v>
       </c>
       <c r="V16">
-        <v>-1.1725305442614947e-05</v>
+        <v>-9.5689870257478539e-06</v>
       </c>
       <c r="W16">
-        <v>-0.00043269247586881542</v>
+        <v>-0.00045272100484141194</v>
       </c>
     </row>
     <row r="17">
@@ -5274,70 +5274,70 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>0.03580376024157797</v>
+        <v>0.052858735945145424</v>
       </c>
       <c r="C17">
-        <v>2.7833101866618982e-06</v>
+        <v>5.4005619281371689e-06</v>
       </c>
       <c r="D17">
-        <v>-2.932623301597289e-08</v>
+        <v>-5.9293833597263886e-08</v>
       </c>
       <c r="E17">
-        <v>2.4301926811353437e-06</v>
+        <v>1.5319065618404014e-05</v>
       </c>
       <c r="F17">
-        <v>-3.704536155166998e-05</v>
+        <v>-2.4961829883317909e-05</v>
       </c>
       <c r="G17">
-        <v>-2.0110568675159677e-07</v>
+        <v>-4.766370617079262e-07</v>
       </c>
       <c r="H17">
-        <v>8.1351876415390696e-07</v>
+        <v>5.1460498825877545e-07</v>
       </c>
       <c r="I17">
-        <v>-8.7334575095057433e-06</v>
+        <v>-4.2684872494050983e-06</v>
       </c>
       <c r="J17">
-        <v>5.0253621813979872e-05</v>
+        <v>-1.6767369914502567e-05</v>
       </c>
       <c r="K17">
-        <v>1.7502692522889457e-05</v>
+        <v>2.9361686160015165e-05</v>
       </c>
       <c r="L17">
-        <v>4.2900460984274778e-06</v>
+        <v>1.6779112074569375e-05</v>
       </c>
       <c r="M17">
-        <v>-9.5150565468413429e-06</v>
+        <v>7.4634355775772413e-06</v>
       </c>
       <c r="N17">
-        <v>-4.1644807801824919e-05</v>
+        <v>-1.7618570052276386e-05</v>
       </c>
       <c r="O17">
-        <v>0.0004710651843647419</v>
+        <v>0.00042366929378590614</v>
       </c>
       <c r="P17">
-        <v>0.00047173769707258039</v>
+        <v>0.00042438899469800776</v>
       </c>
       <c r="Q17">
-        <v>0.00047043437434652583</v>
+        <v>0.00042322053426806683</v>
       </c>
       <c r="R17">
-        <v>0.00074315463006871605</v>
+        <v>0.00065228594021584036</v>
       </c>
       <c r="S17">
-        <v>0.00047303262473484331</v>
+        <v>0.00042560259212658704</v>
       </c>
       <c r="T17">
-        <v>0.00047114234067771404</v>
+        <v>0.00042344558241930619</v>
       </c>
       <c r="U17">
-        <v>1.0286197996808977e-05</v>
+        <v>1.4478853865859706e-05</v>
       </c>
       <c r="V17">
-        <v>1.1737240965023073e-05</v>
+        <v>1.4669598420611913e-05</v>
       </c>
       <c r="W17">
-        <v>-0.00051609055701025094</v>
+        <v>-0.00053495396980473664</v>
       </c>
     </row>
     <row r="18">
@@ -5345,70 +5345,70 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>-0.18592944609549883</v>
+        <v>-0.16106599499737467</v>
       </c>
       <c r="C18">
-        <v>1.0676091693178568e-06</v>
+        <v>3.7941119332633169e-06</v>
       </c>
       <c r="D18">
-        <v>-8.8701674518747906e-09</v>
+        <v>-4.0261836804159125e-08</v>
       </c>
       <c r="E18">
-        <v>-2.9850623349376928e-05</v>
+        <v>-1.0223069220110485e-05</v>
       </c>
       <c r="F18">
-        <v>-0.00011679445542834764</v>
+        <v>-9.5365212390587952e-05</v>
       </c>
       <c r="G18">
-        <v>5.3371271921616794e-07</v>
+        <v>1.4481119756810726e-07</v>
       </c>
       <c r="H18">
-        <v>1.9325278104527057e-06</v>
+        <v>1.5035721594131189e-06</v>
       </c>
       <c r="I18">
-        <v>-2.606697666044876e-06</v>
+        <v>2.0932982755478784e-06</v>
       </c>
       <c r="J18">
-        <v>1.9353312420564719e-05</v>
+        <v>-1.8532693821311366e-05</v>
       </c>
       <c r="K18">
-        <v>2.6272956383322867e-05</v>
+        <v>2.6052897418697094e-05</v>
       </c>
       <c r="L18">
-        <v>-2.7713845261787437e-06</v>
+        <v>8.5049575997847311e-07</v>
       </c>
       <c r="M18">
-        <v>-1.5376978392558241e-05</v>
+        <v>-8.2807623491552341e-06</v>
       </c>
       <c r="N18">
-        <v>-4.2854933628888447e-05</v>
+        <v>-3.0955975819405522e-05</v>
       </c>
       <c r="O18">
-        <v>0.000469497365033381</v>
+        <v>0.00042262458653135986</v>
       </c>
       <c r="P18">
-        <v>0.00047014273902040276</v>
+        <v>0.00042329754278658846</v>
       </c>
       <c r="Q18">
-        <v>0.00047312580990481359</v>
+        <v>0.00042570182051519914</v>
       </c>
       <c r="R18">
-        <v>0.00047303262473484331</v>
+        <v>0.00042560259212658704</v>
       </c>
       <c r="S18">
-        <v>0.00082437807573208495</v>
+        <v>0.00073552618280577434</v>
       </c>
       <c r="T18">
-        <v>0.00047377353263053059</v>
+        <v>0.00042567794357330685</v>
       </c>
       <c r="U18">
-        <v>-3.4409571029095844e-06</v>
+        <v>1.1964294534219665e-06</v>
       </c>
       <c r="V18">
-        <v>-4.5646146519466256e-06</v>
+        <v>-1.4660471262690201e-06</v>
       </c>
       <c r="W18">
-        <v>-0.00047264219823420645</v>
+        <v>-0.00048487283954277727</v>
       </c>
     </row>
     <row r="19">
@@ -5416,70 +5416,70 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>-0.16943328765990912</v>
+        <v>-0.135825802120836</v>
       </c>
       <c r="C19">
-        <v>-1.5859953528869536e-06</v>
+        <v>-2.260043436936677e-07</v>
       </c>
       <c r="D19">
-        <v>2.1438709781452967e-08</v>
+        <v>5.7295706707113009e-09</v>
       </c>
       <c r="E19">
-        <v>-8.6732879960193984e-06</v>
+        <v>-1.6559814167977748e-07</v>
       </c>
       <c r="F19">
-        <v>-8.0583503672852257e-05</v>
+        <v>-6.031309723040548e-05</v>
       </c>
       <c r="G19">
-        <v>-4.3486899884683458e-08</v>
+        <v>-1.8760321035369524e-07</v>
       </c>
       <c r="H19">
-        <v>1.4709641125568748e-06</v>
+        <v>1.0564369302850906e-06</v>
       </c>
       <c r="I19">
-        <v>1.9901236583877612e-05</v>
+        <v>1.9162917473249433e-05</v>
       </c>
       <c r="J19">
-        <v>0.00011820103657441367</v>
+        <v>-7.5491457290265346e-06</v>
       </c>
       <c r="K19">
-        <v>6.0247749972652565e-05</v>
+        <v>6.3604519814932238e-05</v>
       </c>
       <c r="L19">
-        <v>1.6082066797378114e-05</v>
+        <v>2.9610352200449452e-05</v>
       </c>
       <c r="M19">
-        <v>2.5813175832062609e-05</v>
+        <v>3.9261263618007132e-05</v>
       </c>
       <c r="N19">
-        <v>4.1535868367828817e-06</v>
+        <v>2.0652545769368004e-05</v>
       </c>
       <c r="O19">
-        <v>0.00046818112937872293</v>
+        <v>0.00042096771102720658</v>
       </c>
       <c r="P19">
-        <v>0.00047047650778599451</v>
+        <v>0.00042305978563627678</v>
       </c>
       <c r="Q19">
-        <v>0.00047010430500697502</v>
+        <v>0.00042237196742181692</v>
       </c>
       <c r="R19">
-        <v>0.00047114234067771404</v>
+        <v>0.00042344558241930619</v>
       </c>
       <c r="S19">
-        <v>0.00047377353263053059</v>
+        <v>0.00042567794357330685</v>
       </c>
       <c r="T19">
-        <v>0.002088132716805365</v>
+        <v>0.0018658660179841919</v>
       </c>
       <c r="U19">
-        <v>6.4620514914735336e-06</v>
+        <v>9.4091446190515509e-06</v>
       </c>
       <c r="V19">
-        <v>9.5869230351245819e-06</v>
+        <v>1.0174472272877877e-05</v>
       </c>
       <c r="W19">
-        <v>-0.00047502079889227838</v>
+        <v>-0.00046567019009640314</v>
       </c>
     </row>
     <row r="20">
@@ -5487,70 +5487,70 @@
         <v>42</v>
       </c>
       <c r="B20">
-        <v>-0.11328358163543387</v>
+        <v>-0.15204688728582652</v>
       </c>
       <c r="C20">
-        <v>6.4428046560659967e-07</v>
+        <v>7.4443879859393309e-07</v>
       </c>
       <c r="D20">
-        <v>-1.2732135065008081e-08</v>
+        <v>-1.1439799954674747e-08</v>
       </c>
       <c r="E20">
-        <v>1.8501259477093743e-05</v>
+        <v>1.5951222429015683e-05</v>
       </c>
       <c r="F20">
-        <v>2.8927638536724631e-05</v>
+        <v>3.2369995515503299e-05</v>
       </c>
       <c r="G20">
-        <v>-1.8409577426498135e-07</v>
+        <v>-1.8809430049115851e-07</v>
       </c>
       <c r="H20">
-        <v>-2.6681804510713692e-07</v>
+        <v>-4.6454352798112921e-07</v>
       </c>
       <c r="I20">
-        <v>-5.9311727403353487e-06</v>
+        <v>-4.1330805374154734e-06</v>
       </c>
       <c r="J20">
-        <v>5.2480443651226256e-05</v>
+        <v>-6.1301798897019849e-06</v>
       </c>
       <c r="K20">
-        <v>-1.4915699964949509e-05</v>
+        <v>-1.0893199412724915e-05</v>
       </c>
       <c r="L20">
-        <v>-1.81417392115132e-05</v>
+        <v>-1.5517592066413316e-05</v>
       </c>
       <c r="M20">
-        <v>-1.883973666230486e-05</v>
+        <v>-1.8194938227746931e-05</v>
       </c>
       <c r="N20">
-        <v>-2.5205775768008805e-05</v>
+        <v>-2.547821829792273e-05</v>
       </c>
       <c r="O20">
-        <v>1.7360087563435116e-06</v>
+        <v>4.511674315152125e-06</v>
       </c>
       <c r="P20">
-        <v>-5.1777168574167428e-06</v>
+        <v>-2.3792089849083077e-06</v>
       </c>
       <c r="Q20">
-        <v>-1.1203049043353548e-05</v>
+        <v>-8.433700117015425e-06</v>
       </c>
       <c r="R20">
-        <v>1.0286197996808977e-05</v>
+        <v>1.4478853865859706e-05</v>
       </c>
       <c r="S20">
-        <v>-3.4409571029095844e-06</v>
+        <v>1.1964294534219665e-06</v>
       </c>
       <c r="T20">
-        <v>6.4620514914735336e-06</v>
+        <v>9.4091446190515509e-06</v>
       </c>
       <c r="U20">
-        <v>0.00092181448671570156</v>
+        <v>0.00091154740707888294</v>
       </c>
       <c r="V20">
-        <v>7.5744778613289876e-05</v>
+        <v>6.4887733205119507e-05</v>
       </c>
       <c r="W20">
-        <v>-5.8595920483942314e-05</v>
+        <v>-5.5688541172194622e-05</v>
       </c>
     </row>
     <row r="21">
@@ -5558,70 +5558,70 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>0.025606980698442285</v>
+        <v>0.026663191684803276</v>
       </c>
       <c r="C21">
-        <v>-2.4608444896981984e-06</v>
+        <v>-1.2530163930393205e-06</v>
       </c>
       <c r="D21">
-        <v>2.1652126458575811e-08</v>
+        <v>1.1122820945452113e-08</v>
       </c>
       <c r="E21">
-        <v>2.8483267344695754e-05</v>
+        <v>2.8115213761436599e-05</v>
       </c>
       <c r="F21">
-        <v>4.1511906589945642e-05</v>
+        <v>4.3041152185741951e-05</v>
       </c>
       <c r="G21">
-        <v>-3.7475403016374888e-07</v>
+        <v>-4.5847018074486989e-07</v>
       </c>
       <c r="H21">
-        <v>-2.1963049024837856e-07</v>
+        <v>-4.4799985437316903e-07</v>
       </c>
       <c r="I21">
-        <v>-6.1797809405181669e-06</v>
+        <v>-3.5013528475145101e-06</v>
       </c>
       <c r="J21">
-        <v>2.3362080216173504e-05</v>
+        <v>-8.6713804594057136e-06</v>
       </c>
       <c r="K21">
-        <v>3.6694161314550386e-05</v>
+        <v>3.1086774629481877e-05</v>
       </c>
       <c r="L21">
-        <v>3.2174505271338713e-05</v>
+        <v>2.8611271935898903e-05</v>
       </c>
       <c r="M21">
-        <v>3.6563390223014352e-05</v>
+        <v>3.0842942201597627e-05</v>
       </c>
       <c r="N21">
-        <v>3.3571330108055821e-05</v>
+        <v>2.7384510137669768e-05</v>
       </c>
       <c r="O21">
-        <v>-5.3093052501861922e-07</v>
+        <v>5.955067363998736e-07</v>
       </c>
       <c r="P21">
-        <v>-1.431906753762378e-05</v>
+        <v>-1.0135363846915328e-05</v>
       </c>
       <c r="Q21">
-        <v>-1.1725305442614947e-05</v>
+        <v>-9.5689870257478539e-06</v>
       </c>
       <c r="R21">
-        <v>1.1737240965023073e-05</v>
+        <v>1.4669598420611913e-05</v>
       </c>
       <c r="S21">
-        <v>-4.5646146519466256e-06</v>
+        <v>-1.4660471262690201e-06</v>
       </c>
       <c r="T21">
-        <v>9.5869230351245819e-06</v>
+        <v>1.0174472272877877e-05</v>
       </c>
       <c r="U21">
-        <v>7.5744778613289876e-05</v>
+        <v>6.4887733205119507e-05</v>
       </c>
       <c r="V21">
-        <v>0.0010538940613670769</v>
+        <v>0.001082927021884643</v>
       </c>
       <c r="W21">
-        <v>-5.2191780212693045e-05</v>
+        <v>-6.4304610506759309e-05</v>
       </c>
     </row>
     <row r="22">
@@ -5629,70 +5629,70 @@
         <v>44</v>
       </c>
       <c r="B22">
-        <v>-2.7948010327052972</v>
+        <v>-2.9550289227465547</v>
       </c>
       <c r="C22">
-        <v>-0.00059359067019433044</v>
+        <v>-0.00059580463930211712</v>
       </c>
       <c r="D22">
-        <v>6.0770771535445493e-06</v>
+        <v>6.2060900132489428e-06</v>
       </c>
       <c r="E22">
-        <v>-0.0025197464125829567</v>
+        <v>-0.0023801401078947602</v>
       </c>
       <c r="F22">
-        <v>-0.0016560323521552008</v>
+        <v>-0.0017237712088299412</v>
       </c>
       <c r="G22">
-        <v>5.0807519243301652e-05</v>
+        <v>4.8074717002199028e-05</v>
       </c>
       <c r="H22">
-        <v>3.0501911214222998e-05</v>
+        <v>3.3253971797968724e-05</v>
       </c>
       <c r="I22">
-        <v>0.00052362790018054656</v>
+        <v>0.00025058448675194386</v>
       </c>
       <c r="J22">
-        <v>-0.003333707186346417</v>
+        <v>0.00073539763712275152</v>
       </c>
       <c r="K22">
-        <v>-0.010024002271480469</v>
+        <v>-0.0084058833483083573</v>
       </c>
       <c r="L22">
-        <v>-0.010075066009677398</v>
+        <v>-0.0084661599263487521</v>
       </c>
       <c r="M22">
-        <v>-0.010180503499418746</v>
+        <v>-0.008581535024973776</v>
       </c>
       <c r="N22">
-        <v>-0.010438023339420467</v>
+        <v>-0.0088014022867021775</v>
       </c>
       <c r="O22">
-        <v>-0.00047255300945799831</v>
+        <v>-0.00046041484561411771</v>
       </c>
       <c r="P22">
-        <v>-0.00050786740170574057</v>
+        <v>-0.00051168780119030749</v>
       </c>
       <c r="Q22">
-        <v>-0.00043269247586881542</v>
+        <v>-0.00045272100484141194</v>
       </c>
       <c r="R22">
-        <v>-0.00051609055701025094</v>
+        <v>-0.00053495396980473664</v>
       </c>
       <c r="S22">
-        <v>-0.00047264219823420645</v>
+        <v>-0.00048487283954277727</v>
       </c>
       <c r="T22">
-        <v>-0.00047502079889227838</v>
+        <v>-0.00046567019009640314</v>
       </c>
       <c r="U22">
-        <v>-5.8595920483942314e-05</v>
+        <v>-5.5688541172194622e-05</v>
       </c>
       <c r="V22">
-        <v>-5.2191780212693045e-05</v>
+        <v>-6.4304610506759309e-05</v>
       </c>
       <c r="W22">
-        <v>0.023966291865025968</v>
+        <v>0.022043792023922266</v>
       </c>
     </row>
   </sheetData>
@@ -5780,70 +5780,70 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>0.17506722218668996</v>
+        <v>0.17442859940526151</v>
       </c>
       <c r="C2">
-        <v>2.4383979518252191e-05</v>
+        <v>2.3540481476380495e-05</v>
       </c>
       <c r="D2">
-        <v>-2.5154161321019696e-07</v>
+        <v>-2.4690738897113527e-07</v>
       </c>
       <c r="E2">
-        <v>9.2684637959449234e-05</v>
+        <v>8.6326187823058498e-05</v>
       </c>
       <c r="F2">
-        <v>6.5735064898773618e-05</v>
+        <v>6.7279629578022288e-05</v>
       </c>
       <c r="G2">
-        <v>-1.9818959085379269e-06</v>
+        <v>-1.841771682607623e-06</v>
       </c>
       <c r="H2">
-        <v>-1.3557146720993352e-06</v>
+        <v>-1.4047848056821556e-06</v>
       </c>
       <c r="I2">
-        <v>-2.9258870682401835e-05</v>
+        <v>-8.3784328262538214e-06</v>
       </c>
       <c r="J2">
-        <v>0.00013315244763569835</v>
+        <v>-3.26669937577565e-05</v>
       </c>
       <c r="K2">
-        <v>1.067612383873258e-06</v>
+        <v>3.8135368253258901e-06</v>
       </c>
       <c r="L2">
-        <v>1.1816989752240151e-06</v>
+        <v>4.1298777112637637e-06</v>
       </c>
       <c r="M2">
-        <v>1.557291920292537e-06</v>
+        <v>5.4177598559751168e-06</v>
       </c>
       <c r="N2">
-        <v>1.2332342093267566e-05</v>
+        <v>1.4982633842108601e-05</v>
       </c>
       <c r="O2">
-        <v>4.3872140298603005e-07</v>
+        <v>1.4492586215457886e-06</v>
       </c>
       <c r="P2">
-        <v>1.0962357744224739e-06</v>
+        <v>2.1257839484117095e-06</v>
       </c>
       <c r="Q2">
-        <v>1.0509072585291445e-06</v>
+        <v>1.8089963045000926e-06</v>
       </c>
       <c r="R2">
-        <v>1.4213483259107471e-06</v>
+        <v>2.9204160683974874e-06</v>
       </c>
       <c r="S2">
-        <v>2.5175172823005021e-07</v>
+        <v>1.8904551487158973e-06</v>
       </c>
       <c r="T2">
-        <v>4.6327688598461331e-07</v>
+        <v>-6.6572586339490597e-07</v>
       </c>
       <c r="U2">
-        <v>1.1102097858498659e-06</v>
+        <v>1.1732112743566433e-06</v>
       </c>
       <c r="V2">
-        <v>-3.7875560303615868e-06</v>
+        <v>-2.8424526832009631e-06</v>
       </c>
       <c r="W2">
-        <v>-0.0005376225640889629</v>
+        <v>-0.00051560859631771924</v>
       </c>
     </row>
     <row r="3">
@@ -5851,70 +5851,70 @@
         <v>25</v>
       </c>
       <c r="B3">
-        <v>-0.0019947230783767074</v>
+        <v>-0.001982681450141399</v>
       </c>
       <c r="C3">
-        <v>-2.5154161321019696e-07</v>
+        <v>-2.4690738897113527e-07</v>
       </c>
       <c r="D3">
-        <v>2.749399772458454e-09</v>
+        <v>2.7261971320221491e-09</v>
       </c>
       <c r="E3">
-        <v>-4.0602176026941059e-07</v>
+        <v>-4.3319953195562748e-07</v>
       </c>
       <c r="F3">
-        <v>-1.0127867610176458e-07</v>
+        <v>-2.205601942484314e-07</v>
       </c>
       <c r="G3">
-        <v>8.2625156777265378e-09</v>
+        <v>9.0139420847144023e-09</v>
       </c>
       <c r="H3">
-        <v>1.2717736372856673e-09</v>
+        <v>4.2066689288053733e-09</v>
       </c>
       <c r="I3">
-        <v>2.6018302588475731e-07</v>
+        <v>2.1102870308185995e-08</v>
       </c>
       <c r="J3">
-        <v>-1.462828374068274e-06</v>
+        <v>3.9420474748565146e-07</v>
       </c>
       <c r="K3">
-        <v>-1.6091183284793418e-08</v>
+        <v>-4.1955528622624714e-08</v>
       </c>
       <c r="L3">
-        <v>-1.0022543965964785e-08</v>
+        <v>-4.1606169583271956e-08</v>
       </c>
       <c r="M3">
-        <v>7.6130078202181579e-09</v>
+        <v>-3.8288062129341314e-08</v>
       </c>
       <c r="N3">
-        <v>-7.4160989483513046e-08</v>
+        <v>-1.1131903512515188e-07</v>
       </c>
       <c r="O3">
-        <v>2.0648083408687755e-09</v>
+        <v>-1.0633933954931216e-08</v>
       </c>
       <c r="P3">
-        <v>-8.5531451048050645e-09</v>
+        <v>-2.0288623176399256e-08</v>
       </c>
       <c r="Q3">
-        <v>-5.4983769330868275e-09</v>
+        <v>-1.5471502880211322e-08</v>
       </c>
       <c r="R3">
-        <v>-1.0102287857832988e-08</v>
+        <v>-2.7270549691602506e-08</v>
       </c>
       <c r="S3">
-        <v>2.3320067725331959e-09</v>
+        <v>-1.743519163661006e-08</v>
       </c>
       <c r="T3">
-        <v>-3.1533175762774457e-09</v>
+        <v>9.075061433684419e-09</v>
       </c>
       <c r="U3">
-        <v>-1.3265344362586473e-08</v>
+        <v>-1.245225106256128e-08</v>
       </c>
       <c r="V3">
-        <v>3.2228859357369165e-08</v>
+        <v>2.4818422905359576e-08</v>
       </c>
       <c r="W3">
-        <v>5.2041780256028574e-06</v>
+        <v>5.1027282669180229e-06</v>
       </c>
     </row>
     <row r="4">
@@ -5922,70 +5922,70 @@
         <v>26</v>
       </c>
       <c r="B4">
-        <v>-0.18970511635980813</v>
+        <v>-0.22303604243477251</v>
       </c>
       <c r="C4">
-        <v>9.2684637959449234e-05</v>
+        <v>8.6326187823058498e-05</v>
       </c>
       <c r="D4">
-        <v>-4.0602176026941059e-07</v>
+        <v>-4.3319953195562748e-07</v>
       </c>
       <c r="E4">
-        <v>0.0061129676552613638</v>
+        <v>0.0052530126720557848</v>
       </c>
       <c r="F4">
-        <v>0.0027289783380811516</v>
+        <v>0.0023632006392280444</v>
       </c>
       <c r="G4">
-        <v>-0.00012658454849789251</v>
+        <v>-0.00010769552662273962</v>
       </c>
       <c r="H4">
-        <v>-5.6197500271803086e-05</v>
+        <v>-4.8206448817158059e-05</v>
       </c>
       <c r="I4">
-        <v>-2.4051419106634025e-05</v>
+        <v>1.5140063761703109e-05</v>
       </c>
       <c r="J4">
-        <v>-0.00012938007513319834</v>
+        <v>-7.5574110702302988e-05</v>
       </c>
       <c r="K4">
-        <v>-3.8216450846375859e-06</v>
+        <v>1.9026621487829628e-05</v>
       </c>
       <c r="L4">
-        <v>1.215049930160794e-05</v>
+        <v>2.5377330503558154e-05</v>
       </c>
       <c r="M4">
-        <v>2.2499087497850764e-06</v>
+        <v>1.701013276155872e-05</v>
       </c>
       <c r="N4">
-        <v>2.2218839697348027e-05</v>
+        <v>3.4848488909314376e-05</v>
       </c>
       <c r="O4">
-        <v>4.8300767906043883e-05</v>
+        <v>4.5527246550326887e-05</v>
       </c>
       <c r="P4">
-        <v>2.2513374964042759e-05</v>
+        <v>2.2485546038093937e-05</v>
       </c>
       <c r="Q4">
-        <v>2.9649431080900753e-05</v>
+        <v>3.0269242733900469e-05</v>
       </c>
       <c r="R4">
-        <v>3.101580451640605e-05</v>
+        <v>3.4038198616015766e-05</v>
       </c>
       <c r="S4">
-        <v>-5.6933961550265461e-06</v>
+        <v>3.9166500075902682e-06</v>
       </c>
       <c r="T4">
-        <v>-1.5312375890319195e-05</v>
+        <v>-1.797114129143143e-05</v>
       </c>
       <c r="U4">
-        <v>1.3754055509507192e-05</v>
+        <v>1.0660073195828203e-05</v>
       </c>
       <c r="V4">
-        <v>2.1926694904936809e-05</v>
+        <v>1.7911249677234527e-05</v>
       </c>
       <c r="W4">
-        <v>-0.0034951515357835084</v>
+        <v>-0.0031596309752217316</v>
       </c>
     </row>
     <row r="5">
@@ -5993,70 +5993,70 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>-0.33214492007443297</v>
+        <v>-0.3681065448670513</v>
       </c>
       <c r="C5">
-        <v>6.5735064898773618e-05</v>
+        <v>6.7279629578022288e-05</v>
       </c>
       <c r="D5">
-        <v>-1.0127867610176458e-07</v>
+        <v>-2.205601942484314e-07</v>
       </c>
       <c r="E5">
-        <v>0.0027289783380811516</v>
+        <v>0.0023632006392280444</v>
       </c>
       <c r="F5">
-        <v>0.0047612206796333132</v>
+        <v>0.0042197355274177333</v>
       </c>
       <c r="G5">
-        <v>-5.6305966152428003e-05</v>
+        <v>-4.828029927428279e-05</v>
       </c>
       <c r="H5">
-        <v>-9.6564051730453789e-05</v>
+        <v>-8.4900586554641382e-05</v>
       </c>
       <c r="I5">
-        <v>-3.022181075841756e-05</v>
+        <v>2.1408138502450647e-05</v>
       </c>
       <c r="J5">
-        <v>-0.00095647360535605088</v>
+        <v>-0.00010774041306279599</v>
       </c>
       <c r="K5">
-        <v>2.0377678816295995e-05</v>
+        <v>1.7419654993261306e-05</v>
       </c>
       <c r="L5">
-        <v>9.1746420983213502e-06</v>
+        <v>-2.0851529617931658e-06</v>
       </c>
       <c r="M5">
-        <v>-8.6869900484101091e-06</v>
+        <v>-1.7230834154677863e-05</v>
       </c>
       <c r="N5">
-        <v>5.2562023301968803e-05</v>
+        <v>3.2197462247023512e-05</v>
       </c>
       <c r="O5">
-        <v>5.6910683863529433e-05</v>
+        <v>5.2569146040668454e-05</v>
       </c>
       <c r="P5">
-        <v>4.0067254405445394e-05</v>
+        <v>3.2682154206748211e-05</v>
       </c>
       <c r="Q5">
-        <v>-1.459545194759504e-05</v>
+        <v>-1.0065880009931665e-05</v>
       </c>
       <c r="R5">
-        <v>2.272125956267224e-06</v>
+        <v>9.8866562788718838e-06</v>
       </c>
       <c r="S5">
-        <v>-6.2825308508051593e-05</v>
+        <v>-4.8109150269245218e-05</v>
       </c>
       <c r="T5">
-        <v>-3.4896278334126017e-05</v>
+        <v>-2.8828232449395916e-05</v>
       </c>
       <c r="U5">
-        <v>3.8510969066483677e-05</v>
+        <v>3.3227023837756691e-05</v>
       </c>
       <c r="V5">
-        <v>2.0384502718689275e-05</v>
+        <v>1.9449267148431614e-05</v>
       </c>
       <c r="W5">
-        <v>-0.0029229828724894602</v>
+        <v>-0.002716288639685099</v>
       </c>
     </row>
     <row r="6">
@@ -6064,70 +6064,70 @@
         <v>28</v>
       </c>
       <c r="B6">
-        <v>0.0028016801426387341</v>
+        <v>0.0024884314897051021</v>
       </c>
       <c r="C6">
-        <v>-1.9818959085379269e-06</v>
+        <v>-1.841771682607623e-06</v>
       </c>
       <c r="D6">
-        <v>8.2625156777265378e-09</v>
+        <v>9.0139420847144023e-09</v>
       </c>
       <c r="E6">
-        <v>-0.00012658454849789251</v>
+        <v>-0.00010769552662273962</v>
       </c>
       <c r="F6">
-        <v>-5.6305966152428003e-05</v>
+        <v>-4.828029927428279e-05</v>
       </c>
       <c r="G6">
-        <v>2.8192459703972366e-06</v>
+        <v>2.3747427634620731e-06</v>
       </c>
       <c r="H6">
-        <v>1.243082381290842e-06</v>
+        <v>1.0557914605659875e-06</v>
       </c>
       <c r="I6">
-        <v>4.7670169970641314e-07</v>
+        <v>-4.9441835118983433e-07</v>
       </c>
       <c r="J6">
-        <v>2.4284385179500861e-06</v>
+        <v>1.7788426622228975e-06</v>
       </c>
       <c r="K6">
-        <v>-5.2823080268943994e-08</v>
+        <v>-5.6989828509411284e-07</v>
       </c>
       <c r="L6">
-        <v>-3.2460690023255557e-07</v>
+        <v>-6.9025219356646058e-07</v>
       </c>
       <c r="M6">
-        <v>2.2103156800620932e-07</v>
+        <v>-2.2880282408566839e-07</v>
       </c>
       <c r="N6">
-        <v>-4.8991675277028192e-08</v>
+        <v>-4.4683293823429392e-07</v>
       </c>
       <c r="O6">
-        <v>-9.5555633216184534e-07</v>
+        <v>-8.9551885398833311e-07</v>
       </c>
       <c r="P6">
-        <v>-2.227092381147214e-07</v>
+        <v>-2.3032673164631348e-07</v>
       </c>
       <c r="Q6">
-        <v>-7.8633380437838424e-07</v>
+        <v>-7.6771661917475667e-07</v>
       </c>
       <c r="R6">
-        <v>-7.4382698762537833e-07</v>
+        <v>-7.7994779567172666e-07</v>
       </c>
       <c r="S6">
-        <v>-4.1411358330712673e-08</v>
+        <v>-2.1150540845897405e-07</v>
       </c>
       <c r="T6">
-        <v>2.3241110484949679e-07</v>
+        <v>3.0132978253550991e-07</v>
       </c>
       <c r="U6">
-        <v>-2.8167438997013632e-07</v>
+        <v>-2.528205994179068e-07</v>
       </c>
       <c r="V6">
-        <v>-3.2808101323384381e-07</v>
+        <v>-2.9313864847253634e-07</v>
       </c>
       <c r="W6">
-        <v>7.1608218535988509e-05</v>
+        <v>6.4544112324254916e-05</v>
       </c>
     </row>
     <row r="7">
@@ -6135,70 +6135,70 @@
         <v>29</v>
       </c>
       <c r="B7">
-        <v>0.0015858785992986881</v>
+        <v>0.0018072833798249547</v>
       </c>
       <c r="C7">
-        <v>-1.3557146720993352e-06</v>
+        <v>-1.4047848056821556e-06</v>
       </c>
       <c r="D7">
-        <v>1.2717736372856673e-09</v>
+        <v>4.2066689288053733e-09</v>
       </c>
       <c r="E7">
-        <v>-5.6197500271803086e-05</v>
+        <v>-4.8206448817158059e-05</v>
       </c>
       <c r="F7">
-        <v>-9.6564051730453789e-05</v>
+        <v>-8.4900586554641382e-05</v>
       </c>
       <c r="G7">
-        <v>1.243082381290842e-06</v>
+        <v>1.0557914605659875e-06</v>
       </c>
       <c r="H7">
-        <v>2.1016170523950299e-06</v>
+        <v>1.8319155251811902e-06</v>
       </c>
       <c r="I7">
-        <v>4.3664284133598971e-07</v>
+        <v>-7.7768997739940933e-07</v>
       </c>
       <c r="J7">
-        <v>1.8558798497279576e-05</v>
+        <v>2.4492094754093477e-06</v>
       </c>
       <c r="K7">
-        <v>-2.6933672667383386e-07</v>
+        <v>-2.939926663553366e-07</v>
       </c>
       <c r="L7">
-        <v>1.5218451887476079e-07</v>
+        <v>2.6043621860971037e-07</v>
       </c>
       <c r="M7">
-        <v>1.1452365498298725e-06</v>
+        <v>1.1239820612721362e-06</v>
       </c>
       <c r="N7">
-        <v>2.686496278392668e-07</v>
+        <v>4.457761217491508e-07</v>
       </c>
       <c r="O7">
-        <v>-8.6391057769693324e-07</v>
+        <v>-8.1171599895270211e-07</v>
       </c>
       <c r="P7">
-        <v>-1.2491177931334186e-07</v>
+        <v>-6.729975605870186e-08</v>
       </c>
       <c r="Q7">
-        <v>-3.3098441281693578e-07</v>
+        <v>-3.5189121771052658e-07</v>
       </c>
       <c r="R7">
-        <v>5.5540469325208818e-09</v>
+        <v>-1.4947989252864334e-07</v>
       </c>
       <c r="S7">
-        <v>7.8909170608581384e-07</v>
+        <v>5.2467382060500317e-07</v>
       </c>
       <c r="T7">
-        <v>6.0078527922802455e-07</v>
+        <v>5.0367721789776936e-07</v>
       </c>
       <c r="U7">
-        <v>-6.6228993684569063e-07</v>
+        <v>-6.4949585722650761e-07</v>
       </c>
       <c r="V7">
-        <v>-1.3548594262643645e-07</v>
+        <v>-2.397107008800051e-07</v>
       </c>
       <c r="W7">
-        <v>5.7525089240895356e-05</v>
+        <v>5.3759915239246632e-05</v>
       </c>
     </row>
     <row r="8">
@@ -6206,70 +6206,70 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>0.17499963997598839</v>
+        <v>0.18118017266028952</v>
       </c>
       <c r="C8">
-        <v>-2.9258870682401835e-05</v>
+        <v>-8.3784328262538214e-06</v>
       </c>
       <c r="D8">
-        <v>2.6018302588475731e-07</v>
+        <v>2.1102870308185995e-08</v>
       </c>
       <c r="E8">
-        <v>-2.4051419106634025e-05</v>
+        <v>1.5140063761703109e-05</v>
       </c>
       <c r="F8">
-        <v>-3.022181075841756e-05</v>
+        <v>2.1408138502450647e-05</v>
       </c>
       <c r="G8">
-        <v>4.7670169970641314e-07</v>
+        <v>-4.9441835118983433e-07</v>
       </c>
       <c r="H8">
-        <v>4.3664284133598971e-07</v>
+        <v>-7.7768997739940933e-07</v>
       </c>
       <c r="I8">
-        <v>0.00034327823176675941</v>
+        <v>0.00039252652657021818</v>
       </c>
       <c r="J8">
-        <v>-7.5027716278430975e-05</v>
+        <v>-0.0001925530822904217</v>
       </c>
       <c r="K8">
-        <v>-1.1092028943360559e-05</v>
+        <v>-1.430822479609374e-05</v>
       </c>
       <c r="L8">
-        <v>-1.5940040212476883e-05</v>
+        <v>-1.3360498493370884e-05</v>
       </c>
       <c r="M8">
-        <v>-2.4447394452737402e-05</v>
+        <v>-1.9186665910185408e-05</v>
       </c>
       <c r="N8">
-        <v>-2.4758126170353e-05</v>
+        <v>-2.0610247432579201e-05</v>
       </c>
       <c r="O8">
-        <v>-1.8460883139649595e-06</v>
+        <v>3.5781469862081961e-06</v>
       </c>
       <c r="P8">
-        <v>-9.0336353472270046e-06</v>
+        <v>-5.886360260662342e-06</v>
       </c>
       <c r="Q8">
-        <v>-4.403391235684271e-06</v>
+        <v>1.5912262714970239e-07</v>
       </c>
       <c r="R8">
-        <v>-9.6204798947946073e-06</v>
+        <v>-3.7783358534563469e-06</v>
       </c>
       <c r="S8">
-        <v>-1.9495668683271825e-05</v>
+        <v>-8.2011121265418905e-06</v>
       </c>
       <c r="T8">
-        <v>4.6038010503024925e-06</v>
+        <v>5.2804444345689541e-06</v>
       </c>
       <c r="U8">
-        <v>-2.9758441612844177e-07</v>
+        <v>2.0687404830747441e-07</v>
       </c>
       <c r="V8">
-        <v>1.3435139598592764e-05</v>
+        <v>1.2270848759757568e-05</v>
       </c>
       <c r="W8">
-        <v>0.00056486995841063684</v>
+        <v>0.00017673063316534754</v>
       </c>
     </row>
     <row r="9">
@@ -6277,70 +6277,70 @@
         <v>31</v>
       </c>
       <c r="B9">
-        <v>-0.3696740041874681</v>
+        <v>0.0084346163214327717</v>
       </c>
       <c r="C9">
-        <v>0.00013315244763569835</v>
+        <v>-3.26669937577565e-05</v>
       </c>
       <c r="D9">
-        <v>-1.462828374068274e-06</v>
+        <v>3.9420474748565146e-07</v>
       </c>
       <c r="E9">
-        <v>-0.00012938007513319834</v>
+        <v>-7.5574110702302988e-05</v>
       </c>
       <c r="F9">
-        <v>-0.00095647360535605088</v>
+        <v>-0.00010774041306279599</v>
       </c>
       <c r="G9">
-        <v>2.4284385179500861e-06</v>
+        <v>1.7788426622228975e-06</v>
       </c>
       <c r="H9">
-        <v>1.8558798497279576e-05</v>
+        <v>2.4492094754093477e-06</v>
       </c>
       <c r="I9">
-        <v>-7.5027716278430975e-05</v>
+        <v>-0.0001925530822904217</v>
       </c>
       <c r="J9">
-        <v>0.044778604189208829</v>
+        <v>0.00038738937217769977</v>
       </c>
       <c r="K9">
-        <v>-1.2399477992222296e-05</v>
+        <v>-9.5594446015547581e-07</v>
       </c>
       <c r="L9">
-        <v>-3.9306622806414596e-06</v>
+        <v>-6.7261859159997749e-06</v>
       </c>
       <c r="M9">
-        <v>9.9750203729218675e-06</v>
+        <v>-1.3352235170336306e-05</v>
       </c>
       <c r="N9">
-        <v>-2.4961417020613514e-05</v>
+        <v>-1.2568228752221557e-05</v>
       </c>
       <c r="O9">
-        <v>-2.6849662710422302e-05</v>
+        <v>-9.8776580981759437e-06</v>
       </c>
       <c r="P9">
-        <v>-2.1991327025974331e-05</v>
+        <v>-5.2227460761625133e-06</v>
       </c>
       <c r="Q9">
-        <v>-2.0824028727684947e-05</v>
+        <v>-7.756584569302615e-06</v>
       </c>
       <c r="R9">
-        <v>-5.6702693440790487e-05</v>
+        <v>-9.1967218759688907e-06</v>
       </c>
       <c r="S9">
-        <v>-5.110144748122501e-06</v>
+        <v>-1.4450608672886047e-05</v>
       </c>
       <c r="T9">
-        <v>5.662081572278844e-05</v>
+        <v>3.6155749779488691e-06</v>
       </c>
       <c r="U9">
-        <v>2.3344505612602102e-05</v>
+        <v>-5.6013434902318745e-06</v>
       </c>
       <c r="V9">
-        <v>-4.0616795497297109e-05</v>
+        <v>-4.1956606850279706e-06</v>
       </c>
       <c r="W9">
-        <v>-0.0027516766328533888</v>
+        <v>0.00061800271623847585</v>
       </c>
     </row>
     <row r="10">
@@ -6348,70 +6348,70 @@
         <v>32</v>
       </c>
       <c r="B10">
-        <v>0.19044755985018055</v>
+        <v>0.18317355276611266</v>
       </c>
       <c r="C10">
-        <v>1.067612383873258e-06</v>
+        <v>3.8135368253258901e-06</v>
       </c>
       <c r="D10">
-        <v>-1.6091183284793418e-08</v>
+        <v>-4.1955528622624714e-08</v>
       </c>
       <c r="E10">
-        <v>-3.8216450846375859e-06</v>
+        <v>1.9026621487829628e-05</v>
       </c>
       <c r="F10">
-        <v>2.0377678816295995e-05</v>
+        <v>1.7419654993261306e-05</v>
       </c>
       <c r="G10">
-        <v>-5.2823080268943994e-08</v>
+        <v>-5.6989828509411284e-07</v>
       </c>
       <c r="H10">
-        <v>-2.6933672667383386e-07</v>
+        <v>-2.939926663553366e-07</v>
       </c>
       <c r="I10">
-        <v>-1.1092028943360559e-05</v>
+        <v>-1.430822479609374e-05</v>
       </c>
       <c r="J10">
-        <v>-1.2399477992222296e-05</v>
+        <v>-9.5594446015547581e-07</v>
       </c>
       <c r="K10">
-        <v>0.011511830058613776</v>
+        <v>0.0091287707700556265</v>
       </c>
       <c r="L10">
-        <v>0.0096602715031731384</v>
+        <v>0.0075787279332324032</v>
       </c>
       <c r="M10">
-        <v>0.0096572662486520584</v>
+        <v>0.0075769016576795753</v>
       </c>
       <c r="N10">
-        <v>0.0096533106970403265</v>
+        <v>0.0075749332213773295</v>
       </c>
       <c r="O10">
-        <v>4.7770986842013629e-06</v>
+        <v>1.2066759158126881e-05</v>
       </c>
       <c r="P10">
-        <v>-5.944174974961879e-07</v>
+        <v>9.214418427847123e-06</v>
       </c>
       <c r="Q10">
-        <v>-2.9312869855195421e-05</v>
+        <v>-1.7769371088324239e-05</v>
       </c>
       <c r="R10">
-        <v>-1.7473094770705755e-05</v>
+        <v>-8.4978045359928363e-06</v>
       </c>
       <c r="S10">
-        <v>1.7048849545395391e-06</v>
+        <v>3.3824494668758707e-06</v>
       </c>
       <c r="T10">
-        <v>1.1732014867307723e-06</v>
+        <v>1.481619248703994e-05</v>
       </c>
       <c r="U10">
-        <v>4.0270479406493028e-06</v>
+        <v>1.3310316153190914e-07</v>
       </c>
       <c r="V10">
-        <v>-6.2258963814059713e-06</v>
+        <v>-7.2460163601834341e-06</v>
       </c>
       <c r="W10">
-        <v>-0.009656403581416749</v>
+        <v>-0.0076458550531630643</v>
       </c>
     </row>
     <row r="11">
@@ -6419,70 +6419,70 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>0.67009213599584516</v>
+        <v>0.66015162492825919</v>
       </c>
       <c r="C11">
-        <v>1.1816989752240151e-06</v>
+        <v>4.1298777112637637e-06</v>
       </c>
       <c r="D11">
-        <v>-1.0022543965964785e-08</v>
+        <v>-4.1606169583271956e-08</v>
       </c>
       <c r="E11">
-        <v>1.215049930160794e-05</v>
+        <v>2.5377330503558154e-05</v>
       </c>
       <c r="F11">
-        <v>9.1746420983213502e-06</v>
+        <v>-2.0851529617931658e-06</v>
       </c>
       <c r="G11">
-        <v>-3.2460690023255557e-07</v>
+        <v>-6.9025219356646058e-07</v>
       </c>
       <c r="H11">
-        <v>1.5218451887476079e-07</v>
+        <v>2.6043621860971037e-07</v>
       </c>
       <c r="I11">
-        <v>-1.5940040212476883e-05</v>
+        <v>-1.3360498493370884e-05</v>
       </c>
       <c r="J11">
-        <v>-3.9306622806414596e-06</v>
+        <v>-6.7261859159997749e-06</v>
       </c>
       <c r="K11">
-        <v>0.0096602715031731384</v>
+        <v>0.0075787279332324032</v>
       </c>
       <c r="L11">
-        <v>0.010015551445784169</v>
+        <v>0.0078798369488180947</v>
       </c>
       <c r="M11">
-        <v>0.0096648652894109899</v>
+        <v>0.0075829129875069155</v>
       </c>
       <c r="N11">
-        <v>0.0096661887986971701</v>
+        <v>0.0075853494344380792</v>
       </c>
       <c r="O11">
-        <v>4.6521039143289761e-06</v>
+        <v>1.0946253038199972e-05</v>
       </c>
       <c r="P11">
-        <v>-1.2458457135501609e-05</v>
+        <v>1.6896487130998159e-07</v>
       </c>
       <c r="Q11">
-        <v>-4.7456789289987367e-05</v>
+        <v>-3.0271987084079494e-05</v>
       </c>
       <c r="R11">
-        <v>-2.7010474321541585e-05</v>
+        <v>-1.4824240716207742e-05</v>
       </c>
       <c r="S11">
-        <v>-1.2146908825660423e-05</v>
+        <v>-6.0374694249166864e-06</v>
       </c>
       <c r="T11">
-        <v>-9.5116862632838159e-06</v>
+        <v>3.4151414074549665e-07</v>
       </c>
       <c r="U11">
-        <v>7.6262764598954057e-06</v>
+        <v>1.707739533103869e-06</v>
       </c>
       <c r="V11">
-        <v>-5.0282638781215512e-06</v>
+        <v>-8.1754913156325658e-06</v>
       </c>
       <c r="W11">
-        <v>-0.0096750486755672726</v>
+        <v>-0.0076619075026903684</v>
       </c>
     </row>
     <row r="12">
@@ -6490,70 +6490,70 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0.88458666854901336</v>
+        <v>0.87334503596806046</v>
       </c>
       <c r="C12">
-        <v>1.557291920292537e-06</v>
+        <v>5.4177598559751168e-06</v>
       </c>
       <c r="D12">
-        <v>7.6130078202181579e-09</v>
+        <v>-3.8288062129341314e-08</v>
       </c>
       <c r="E12">
-        <v>2.2499087497850764e-06</v>
+        <v>1.701013276155872e-05</v>
       </c>
       <c r="F12">
-        <v>-8.6869900484101091e-06</v>
+        <v>-1.7230834154677863e-05</v>
       </c>
       <c r="G12">
-        <v>2.2103156800620932e-07</v>
+        <v>-2.2880282408566839e-07</v>
       </c>
       <c r="H12">
-        <v>1.1452365498298725e-06</v>
+        <v>1.1239820612721362e-06</v>
       </c>
       <c r="I12">
-        <v>-2.4447394452737402e-05</v>
+        <v>-1.9186665910185408e-05</v>
       </c>
       <c r="J12">
-        <v>9.9750203729218675e-06</v>
+        <v>-1.3352235170336306e-05</v>
       </c>
       <c r="K12">
-        <v>0.0096572662486520584</v>
+        <v>0.0075769016576795753</v>
       </c>
       <c r="L12">
-        <v>0.0096648652894109899</v>
+        <v>0.0075829129875069155</v>
       </c>
       <c r="M12">
-        <v>0.0097790175692240404</v>
+        <v>0.0076829782088214289</v>
       </c>
       <c r="N12">
-        <v>0.0097035065413749282</v>
+        <v>0.0076175042916605089</v>
       </c>
       <c r="O12">
-        <v>2.7025835524371946e-06</v>
+        <v>9.1514009541485662e-06</v>
       </c>
       <c r="P12">
-        <v>-2.2576966191663289e-05</v>
+        <v>-5.4263467083948212e-06</v>
       </c>
       <c r="Q12">
-        <v>-5.3278956442177662e-05</v>
+        <v>-3.6030654339676646e-05</v>
       </c>
       <c r="R12">
-        <v>-2.6258303735504035e-05</v>
+        <v>-1.4222841955696582e-05</v>
       </c>
       <c r="S12">
-        <v>-1.4568485737438353e-05</v>
+        <v>-9.5051060439650973e-06</v>
       </c>
       <c r="T12">
-        <v>7.2569544600576911e-06</v>
+        <v>1.8040122792191925e-05</v>
       </c>
       <c r="U12">
-        <v>4.454682823626064e-06</v>
+        <v>-2.545610202908781e-06</v>
       </c>
       <c r="V12">
-        <v>-1.671239411723229e-06</v>
+        <v>-6.110561385893571e-06</v>
       </c>
       <c r="W12">
-        <v>-0.0097596644490405057</v>
+        <v>-0.007751660929322811</v>
       </c>
     </row>
     <row r="13">
@@ -6561,70 +6561,70 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>0.91339255205179559</v>
+        <v>0.93043534444253428</v>
       </c>
       <c r="C13">
-        <v>1.2332342093267566e-05</v>
+        <v>1.4982633842108601e-05</v>
       </c>
       <c r="D13">
-        <v>-7.4160989483513046e-08</v>
+        <v>-1.1131903512515188e-07</v>
       </c>
       <c r="E13">
-        <v>2.2218839697348027e-05</v>
+        <v>3.4848488909314376e-05</v>
       </c>
       <c r="F13">
-        <v>5.2562023301968803e-05</v>
+        <v>3.2197462247023512e-05</v>
       </c>
       <c r="G13">
-        <v>-4.8991675277028192e-08</v>
+        <v>-4.4683293823429392e-07</v>
       </c>
       <c r="H13">
-        <v>2.686496278392668e-07</v>
+        <v>4.457761217491508e-07</v>
       </c>
       <c r="I13">
-        <v>-2.4758126170353e-05</v>
+        <v>-2.0610247432579201e-05</v>
       </c>
       <c r="J13">
-        <v>-2.4961417020613514e-05</v>
+        <v>-1.2568228752221557e-05</v>
       </c>
       <c r="K13">
-        <v>0.0096533106970403265</v>
+        <v>0.0075749332213773295</v>
       </c>
       <c r="L13">
-        <v>0.0096661887986971701</v>
+        <v>0.0075853494344380792</v>
       </c>
       <c r="M13">
-        <v>0.0097035065413749282</v>
+        <v>0.0076175042916605089</v>
       </c>
       <c r="N13">
-        <v>0.010065499892358875</v>
+        <v>0.0079487363934019929</v>
       </c>
       <c r="O13">
-        <v>-9.7268400920737951e-06</v>
+        <v>-2.7626626719943299e-07</v>
       </c>
       <c r="P13">
-        <v>-3.821643540764674e-05</v>
+        <v>-1.6484606955236573e-05</v>
       </c>
       <c r="Q13">
-        <v>-6.0203768992631846e-05</v>
+        <v>-4.1697871549088424e-05</v>
       </c>
       <c r="R13">
-        <v>-5.2752050957380865e-05</v>
+        <v>-3.5121561303235003e-05</v>
       </c>
       <c r="S13">
-        <v>-3.8344098069851079e-05</v>
+        <v>-2.8907810716398229e-05</v>
       </c>
       <c r="T13">
-        <v>-1.8210359731343668e-05</v>
+        <v>-2.1462327603964768e-06</v>
       </c>
       <c r="U13">
-        <v>-2.9422288518517345e-06</v>
+        <v>-1.0478736349004337e-05</v>
       </c>
       <c r="V13">
-        <v>-8.6381259195390145e-06</v>
+        <v>-1.2285942338857328e-05</v>
       </c>
       <c r="W13">
-        <v>-0.010083273930940844</v>
+        <v>-0.0080401891750455576</v>
       </c>
     </row>
     <row r="14">
@@ -6632,70 +6632,70 @@
         <v>36</v>
       </c>
       <c r="B14">
-        <v>0.073773792161670404</v>
+        <v>0.069190686957279243</v>
       </c>
       <c r="C14">
-        <v>4.3872140298603005e-07</v>
+        <v>1.4492586215457886e-06</v>
       </c>
       <c r="D14">
-        <v>2.0648083408687755e-09</v>
+        <v>-1.0633933954931216e-08</v>
       </c>
       <c r="E14">
-        <v>4.8300767906043883e-05</v>
+        <v>4.5527246550326887e-05</v>
       </c>
       <c r="F14">
-        <v>5.6910683863529433e-05</v>
+        <v>5.2569146040668454e-05</v>
       </c>
       <c r="G14">
-        <v>-9.5555633216184534e-07</v>
+        <v>-8.9551885398833311e-07</v>
       </c>
       <c r="H14">
-        <v>-8.6391057769693324e-07</v>
+        <v>-8.1171599895270211e-07</v>
       </c>
       <c r="I14">
-        <v>-1.8460883139649595e-06</v>
+        <v>3.5781469862081961e-06</v>
       </c>
       <c r="J14">
-        <v>-2.6849662710422302e-05</v>
+        <v>-9.8776580981759437e-06</v>
       </c>
       <c r="K14">
-        <v>4.7770986842013629e-06</v>
+        <v>1.2066759158126881e-05</v>
       </c>
       <c r="L14">
-        <v>4.6521039143289761e-06</v>
+        <v>1.0946253038199972e-05</v>
       </c>
       <c r="M14">
-        <v>2.7025835524371946e-06</v>
+        <v>9.1514009541485662e-06</v>
       </c>
       <c r="N14">
-        <v>-9.7268400920737951e-06</v>
+        <v>-2.7626626719943299e-07</v>
       </c>
       <c r="O14">
-        <v>0.00085188450627591823</v>
+        <v>0.00077000748332730175</v>
       </c>
       <c r="P14">
-        <v>0.0004591764686186453</v>
+        <v>0.00041717281603157553</v>
       </c>
       <c r="Q14">
-        <v>0.00045504423856345316</v>
+        <v>0.00041384963517607525</v>
       </c>
       <c r="R14">
-        <v>0.00045779644369693733</v>
+        <v>0.00041626155201825019</v>
       </c>
       <c r="S14">
-        <v>0.00045558358824117134</v>
+        <v>0.00041442414588120457</v>
       </c>
       <c r="T14">
-        <v>0.00045650447631648109</v>
+        <v>0.00041478874938270745</v>
       </c>
       <c r="U14">
-        <v>5.61043068727634e-06</v>
+        <v>6.073500478057615e-06</v>
       </c>
       <c r="V14">
-        <v>4.1519655496266016e-06</v>
+        <v>4.6126928665743164e-06</v>
       </c>
       <c r="W14">
-        <v>-0.00049034256180230287</v>
+        <v>-0.00047283649417752971</v>
       </c>
     </row>
     <row r="15">
@@ -6703,70 +6703,70 @@
         <v>37</v>
       </c>
       <c r="B15">
-        <v>0.016201815744773387</v>
+        <v>0.024647006097917118</v>
       </c>
       <c r="C15">
-        <v>1.0962357744224739e-06</v>
+        <v>2.1257839484117095e-06</v>
       </c>
       <c r="D15">
-        <v>-8.5531451048050645e-09</v>
+        <v>-2.0288623176399256e-08</v>
       </c>
       <c r="E15">
-        <v>2.2513374964042759e-05</v>
+        <v>2.2485546038093937e-05</v>
       </c>
       <c r="F15">
-        <v>4.0067254405445394e-05</v>
+        <v>3.2682154206748211e-05</v>
       </c>
       <c r="G15">
-        <v>-2.227092381147214e-07</v>
+        <v>-2.3032673164631348e-07</v>
       </c>
       <c r="H15">
-        <v>-1.2491177931334186e-07</v>
+        <v>-6.729975605870186e-08</v>
       </c>
       <c r="I15">
-        <v>-9.0336353472270046e-06</v>
+        <v>-5.886360260662342e-06</v>
       </c>
       <c r="J15">
-        <v>-2.1991327025974331e-05</v>
+        <v>-5.2227460761625133e-06</v>
       </c>
       <c r="K15">
-        <v>-5.944174974961879e-07</v>
+        <v>9.214418427847123e-06</v>
       </c>
       <c r="L15">
-        <v>-1.2458457135501609e-05</v>
+        <v>1.6896487130998159e-07</v>
       </c>
       <c r="M15">
-        <v>-2.2576966191663289e-05</v>
+        <v>-5.4263467083948212e-06</v>
       </c>
       <c r="N15">
-        <v>-3.821643540764674e-05</v>
+        <v>-1.6484606955236573e-05</v>
       </c>
       <c r="O15">
-        <v>0.0004591764686186453</v>
+        <v>0.00041717281603157553</v>
       </c>
       <c r="P15">
-        <v>0.0010481331800292898</v>
+        <v>0.00093504658143020393</v>
       </c>
       <c r="Q15">
-        <v>0.00045412513950462204</v>
+        <v>0.00041282945650045281</v>
       </c>
       <c r="R15">
-        <v>0.00045869565606238992</v>
+        <v>0.00041672751216224099</v>
       </c>
       <c r="S15">
-        <v>0.00045577226547236936</v>
+        <v>0.0004142531003056002</v>
       </c>
       <c r="T15">
-        <v>0.00045648725447521732</v>
+        <v>0.00041471591399255483</v>
       </c>
       <c r="U15">
-        <v>-3.3915979216699326e-06</v>
+        <v>-2.1115892635215897e-06</v>
       </c>
       <c r="V15">
-        <v>-1.9559921153166349e-05</v>
+        <v>-1.2822743613043456e-05</v>
       </c>
       <c r="W15">
-        <v>-0.00047616259705704603</v>
+        <v>-0.00047078789341754629</v>
       </c>
     </row>
     <row r="16">
@@ -6774,70 +6774,70 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>-0.064679135437807039</v>
+        <v>-0.069678774954667982</v>
       </c>
       <c r="C16">
-        <v>1.0509072585291445e-06</v>
+        <v>1.8089963045000926e-06</v>
       </c>
       <c r="D16">
-        <v>-5.4983769330868275e-09</v>
+        <v>-1.5471502880211322e-08</v>
       </c>
       <c r="E16">
-        <v>2.9649431080900753e-05</v>
+        <v>3.0269242733900469e-05</v>
       </c>
       <c r="F16">
-        <v>-1.459545194759504e-05</v>
+        <v>-1.0065880009931665e-05</v>
       </c>
       <c r="G16">
-        <v>-7.8633380437838424e-07</v>
+        <v>-7.6771661917475667e-07</v>
       </c>
       <c r="H16">
-        <v>-3.3098441281693578e-07</v>
+        <v>-3.5189121771052658e-07</v>
       </c>
       <c r="I16">
-        <v>-4.403391235684271e-06</v>
+        <v>1.5912262714970239e-07</v>
       </c>
       <c r="J16">
-        <v>-2.0824028727684947e-05</v>
+        <v>-7.756584569302615e-06</v>
       </c>
       <c r="K16">
-        <v>-2.9312869855195421e-05</v>
+        <v>-1.7769371088324239e-05</v>
       </c>
       <c r="L16">
-        <v>-4.7456789289987367e-05</v>
+        <v>-3.0271987084079494e-05</v>
       </c>
       <c r="M16">
-        <v>-5.3278956442177662e-05</v>
+        <v>-3.6030654339676646e-05</v>
       </c>
       <c r="N16">
-        <v>-6.0203768992631846e-05</v>
+        <v>-4.1697871549088424e-05</v>
       </c>
       <c r="O16">
-        <v>0.00045504423856345316</v>
+        <v>0.00041384963517607525</v>
       </c>
       <c r="P16">
-        <v>0.00045412513950462204</v>
+        <v>0.00041282945650045281</v>
       </c>
       <c r="Q16">
-        <v>0.00079329124471609201</v>
+        <v>0.00071787682315140782</v>
       </c>
       <c r="R16">
-        <v>0.00045701417411151259</v>
+        <v>0.00041535799384057309</v>
       </c>
       <c r="S16">
-        <v>0.00046013846310186406</v>
+        <v>0.00041838650803731396</v>
       </c>
       <c r="T16">
-        <v>0.00045715126013975077</v>
+        <v>0.00041511656591378967</v>
       </c>
       <c r="U16">
-        <v>-7.1726262594326638e-06</v>
+        <v>-4.9947029892120068e-06</v>
       </c>
       <c r="V16">
-        <v>-6.7636576269655553e-06</v>
+        <v>-5.5193359418054806e-06</v>
       </c>
       <c r="W16">
-        <v>-0.00042236919031441638</v>
+        <v>-0.00041325986896345254</v>
       </c>
     </row>
     <row r="17">
@@ -6845,70 +6845,70 @@
         <v>39</v>
       </c>
       <c r="B17">
-        <v>0.027287359773946529</v>
+        <v>0.023169664787710036</v>
       </c>
       <c r="C17">
-        <v>1.4213483259107471e-06</v>
+        <v>2.9204160683974874e-06</v>
       </c>
       <c r="D17">
-        <v>-1.0102287857832988e-08</v>
+        <v>-2.7270549691602506e-08</v>
       </c>
       <c r="E17">
-        <v>3.101580451640605e-05</v>
+        <v>3.4038198616015766e-05</v>
       </c>
       <c r="F17">
-        <v>2.272125956267224e-06</v>
+        <v>9.8866562788718838e-06</v>
       </c>
       <c r="G17">
-        <v>-7.4382698762537833e-07</v>
+        <v>-7.7994779567172666e-07</v>
       </c>
       <c r="H17">
-        <v>5.5540469325208818e-09</v>
+        <v>-1.4947989252864334e-07</v>
       </c>
       <c r="I17">
-        <v>-9.6204798947946073e-06</v>
+        <v>-3.7783358534563469e-06</v>
       </c>
       <c r="J17">
-        <v>-5.6702693440790487e-05</v>
+        <v>-9.1967218759688907e-06</v>
       </c>
       <c r="K17">
-        <v>-1.7473094770705755e-05</v>
+        <v>-8.4978045359928363e-06</v>
       </c>
       <c r="L17">
-        <v>-2.7010474321541585e-05</v>
+        <v>-1.4824240716207742e-05</v>
       </c>
       <c r="M17">
-        <v>-2.6258303735504035e-05</v>
+        <v>-1.4222841955696582e-05</v>
       </c>
       <c r="N17">
-        <v>-5.2752050957380865e-05</v>
+        <v>-3.5121561303235003e-05</v>
       </c>
       <c r="O17">
-        <v>0.00045779644369693733</v>
+        <v>0.00041626155201825019</v>
       </c>
       <c r="P17">
-        <v>0.00045869565606238992</v>
+        <v>0.00041672751216224099</v>
       </c>
       <c r="Q17">
-        <v>0.00045701417411151259</v>
+        <v>0.00041535799384057309</v>
       </c>
       <c r="R17">
-        <v>0.00071759616113220852</v>
+        <v>0.00063389242032125767</v>
       </c>
       <c r="S17">
-        <v>0.00045890183158109972</v>
+        <v>0.0004170031744904781</v>
       </c>
       <c r="T17">
-        <v>0.00045835114642473011</v>
+        <v>0.00041612161306906615</v>
       </c>
       <c r="U17">
-        <v>1.1051330255817302e-05</v>
+        <v>1.464070092988265e-05</v>
       </c>
       <c r="V17">
-        <v>6.8479165008000864e-06</v>
+        <v>1.0174941497393464e-05</v>
       </c>
       <c r="W17">
-        <v>-0.00046510661863207944</v>
+        <v>-0.00046798244563567363</v>
       </c>
     </row>
     <row r="18">
@@ -6916,70 +6916,70 @@
         <v>40</v>
       </c>
       <c r="B18">
-        <v>-0.11854054557536563</v>
+        <v>-0.12921933829819451</v>
       </c>
       <c r="C18">
-        <v>2.5175172823005021e-07</v>
+        <v>1.8904551487158973e-06</v>
       </c>
       <c r="D18">
-        <v>2.3320067725331959e-09</v>
+        <v>-1.743519163661006e-08</v>
       </c>
       <c r="E18">
-        <v>-5.6933961550265461e-06</v>
+        <v>3.9166500075902682e-06</v>
       </c>
       <c r="F18">
-        <v>-6.2825308508051593e-05</v>
+        <v>-4.8109150269245218e-05</v>
       </c>
       <c r="G18">
-        <v>-4.1411358330712673e-08</v>
+        <v>-2.1150540845897405e-07</v>
       </c>
       <c r="H18">
-        <v>7.8909170608581384e-07</v>
+        <v>5.2467382060500317e-07</v>
       </c>
       <c r="I18">
-        <v>-1.9495668683271825e-05</v>
+        <v>-8.2011121265418905e-06</v>
       </c>
       <c r="J18">
-        <v>-5.110144748122501e-06</v>
+        <v>-1.4450608672886047e-05</v>
       </c>
       <c r="K18">
-        <v>1.7048849545395391e-06</v>
+        <v>3.3824494668758707e-06</v>
       </c>
       <c r="L18">
-        <v>-1.2146908825660423e-05</v>
+        <v>-6.0374694249166864e-06</v>
       </c>
       <c r="M18">
-        <v>-1.4568485737438353e-05</v>
+        <v>-9.5051060439650973e-06</v>
       </c>
       <c r="N18">
-        <v>-3.8344098069851079e-05</v>
+        <v>-2.8907810716398229e-05</v>
       </c>
       <c r="O18">
-        <v>0.00045558358824117134</v>
+        <v>0.00041442414588120457</v>
       </c>
       <c r="P18">
-        <v>0.00045577226547236936</v>
+        <v>0.0004142531003056002</v>
       </c>
       <c r="Q18">
-        <v>0.00046013846310186406</v>
+        <v>0.00041838650803731396</v>
       </c>
       <c r="R18">
-        <v>0.00045890183158109972</v>
+        <v>0.0004170031744904781</v>
       </c>
       <c r="S18">
-        <v>0.00076814794722531864</v>
+        <v>0.00068784708859319767</v>
       </c>
       <c r="T18">
-        <v>0.00045887739900240144</v>
+        <v>0.00041636070603264392</v>
       </c>
       <c r="U18">
-        <v>-3.7711783392627753e-06</v>
+        <v>1.1402193500351788e-07</v>
       </c>
       <c r="V18">
-        <v>-4.4244624726818801e-06</v>
+        <v>-1.6509465377052728e-06</v>
       </c>
       <c r="W18">
-        <v>-0.00043108848861972892</v>
+        <v>-0.00043093230257717726</v>
       </c>
     </row>
     <row r="19">
@@ -6987,70 +6987,70 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>-0.12849091305817534</v>
+        <v>-0.14926305479798871</v>
       </c>
       <c r="C19">
-        <v>4.6327688598461331e-07</v>
+        <v>-6.6572586339490597e-07</v>
       </c>
       <c r="D19">
-        <v>-3.1533175762774457e-09</v>
+        <v>9.075061433684419e-09</v>
       </c>
       <c r="E19">
-        <v>-1.5312375890319195e-05</v>
+        <v>-1.797114129143143e-05</v>
       </c>
       <c r="F19">
-        <v>-3.4896278334126017e-05</v>
+        <v>-2.8828232449395916e-05</v>
       </c>
       <c r="G19">
-        <v>2.3241110484949679e-07</v>
+        <v>3.0132978253550991e-07</v>
       </c>
       <c r="H19">
-        <v>6.0078527922802455e-07</v>
+        <v>5.0367721789776936e-07</v>
       </c>
       <c r="I19">
-        <v>4.6038010503024925e-06</v>
+        <v>5.2804444345689541e-06</v>
       </c>
       <c r="J19">
-        <v>5.662081572278844e-05</v>
+        <v>3.6155749779488691e-06</v>
       </c>
       <c r="K19">
-        <v>1.1732014867307723e-06</v>
+        <v>1.481619248703994e-05</v>
       </c>
       <c r="L19">
-        <v>-9.5116862632838159e-06</v>
+        <v>3.4151414074549665e-07</v>
       </c>
       <c r="M19">
-        <v>7.2569544600576911e-06</v>
+        <v>1.8040122792191925e-05</v>
       </c>
       <c r="N19">
-        <v>-1.8210359731343668e-05</v>
+        <v>-2.1462327603964768e-06</v>
       </c>
       <c r="O19">
-        <v>0.00045650447631648109</v>
+        <v>0.00041478874938270745</v>
       </c>
       <c r="P19">
-        <v>0.00045648725447521732</v>
+        <v>0.00041471591399255483</v>
       </c>
       <c r="Q19">
-        <v>0.00045715126013975077</v>
+        <v>0.00041511656591378967</v>
       </c>
       <c r="R19">
-        <v>0.00045835114642473011</v>
+        <v>0.00041612161306906615</v>
       </c>
       <c r="S19">
-        <v>0.00045887739900240144</v>
+        <v>0.00041636070603264392</v>
       </c>
       <c r="T19">
-        <v>0.0020285640819254144</v>
+        <v>0.0017919283938224509</v>
       </c>
       <c r="U19">
-        <v>1.0325058584687925e-05</v>
+        <v>1.0769361950415997e-05</v>
       </c>
       <c r="V19">
-        <v>1.285403673742524e-06</v>
+        <v>3.6313079182258825e-06</v>
       </c>
       <c r="W19">
-        <v>-0.00047100216080141189</v>
+        <v>-0.00041903953640824672</v>
       </c>
     </row>
     <row r="20">
@@ -7058,70 +7058,70 @@
         <v>42</v>
       </c>
       <c r="B20">
-        <v>-0.042526837026015632</v>
+        <v>-0.068637034543818004</v>
       </c>
       <c r="C20">
-        <v>1.1102097858498659e-06</v>
+        <v>1.1732112743566433e-06</v>
       </c>
       <c r="D20">
-        <v>-1.3265344362586473e-08</v>
+        <v>-1.245225106256128e-08</v>
       </c>
       <c r="E20">
-        <v>1.3754055509507192e-05</v>
+        <v>1.0660073195828203e-05</v>
       </c>
       <c r="F20">
-        <v>3.8510969066483677e-05</v>
+        <v>3.3227023837756691e-05</v>
       </c>
       <c r="G20">
-        <v>-2.8167438997013632e-07</v>
+        <v>-2.528205994179068e-07</v>
       </c>
       <c r="H20">
-        <v>-6.6228993684569063e-07</v>
+        <v>-6.4949585722650761e-07</v>
       </c>
       <c r="I20">
-        <v>-2.9758441612844177e-07</v>
+        <v>2.0687404830747441e-07</v>
       </c>
       <c r="J20">
-        <v>2.3344505612602102e-05</v>
+        <v>-5.6013434902318745e-06</v>
       </c>
       <c r="K20">
-        <v>4.0270479406493028e-06</v>
+        <v>1.3310316153190914e-07</v>
       </c>
       <c r="L20">
-        <v>7.6262764598954057e-06</v>
+        <v>1.707739533103869e-06</v>
       </c>
       <c r="M20">
-        <v>4.454682823626064e-06</v>
+        <v>-2.545610202908781e-06</v>
       </c>
       <c r="N20">
-        <v>-2.9422288518517345e-06</v>
+        <v>-1.0478736349004337e-05</v>
       </c>
       <c r="O20">
-        <v>5.61043068727634e-06</v>
+        <v>6.073500478057615e-06</v>
       </c>
       <c r="P20">
-        <v>-3.3915979216699326e-06</v>
+        <v>-2.1115892635215897e-06</v>
       </c>
       <c r="Q20">
-        <v>-7.1726262594326638e-06</v>
+        <v>-4.9947029892120068e-06</v>
       </c>
       <c r="R20">
-        <v>1.1051330255817302e-05</v>
+        <v>1.464070092988265e-05</v>
       </c>
       <c r="S20">
-        <v>-3.7711783392627753e-06</v>
+        <v>1.1402193500351788e-07</v>
       </c>
       <c r="T20">
-        <v>1.0325058584687925e-05</v>
+        <v>1.0769361950415997e-05</v>
       </c>
       <c r="U20">
-        <v>0.00089509256497684331</v>
+        <v>0.00089079758868779678</v>
       </c>
       <c r="V20">
-        <v>6.8306639607071523e-05</v>
+        <v>5.8560093931156922e-05</v>
       </c>
       <c r="W20">
-        <v>-9.6150934237597866e-05</v>
+        <v>-8.2864152426535042e-05</v>
       </c>
     </row>
     <row r="21">
@@ -7129,70 +7129,70 @@
         <v>43</v>
       </c>
       <c r="B21">
-        <v>0.090132539167039894</v>
+        <v>0.10454114967837186</v>
       </c>
       <c r="C21">
-        <v>-3.7875560303615868e-06</v>
+        <v>-2.8424526832009631e-06</v>
       </c>
       <c r="D21">
-        <v>3.2228859357369165e-08</v>
+        <v>2.4818422905359576e-08</v>
       </c>
       <c r="E21">
-        <v>2.1926694904936809e-05</v>
+        <v>1.7911249677234527e-05</v>
       </c>
       <c r="F21">
-        <v>2.0384502718689275e-05</v>
+        <v>1.9449267148431614e-05</v>
       </c>
       <c r="G21">
-        <v>-3.2808101323384381e-07</v>
+        <v>-2.9313864847253634e-07</v>
       </c>
       <c r="H21">
-        <v>-1.3548594262643645e-07</v>
+        <v>-2.397107008800051e-07</v>
       </c>
       <c r="I21">
-        <v>1.3435139598592764e-05</v>
+        <v>1.2270848759757568e-05</v>
       </c>
       <c r="J21">
-        <v>-4.0616795497297109e-05</v>
+        <v>-4.1956606850279706e-06</v>
       </c>
       <c r="K21">
-        <v>-6.2258963814059713e-06</v>
+        <v>-7.2460163601834341e-06</v>
       </c>
       <c r="L21">
-        <v>-5.0282638781215512e-06</v>
+        <v>-8.1754913156325658e-06</v>
       </c>
       <c r="M21">
-        <v>-1.671239411723229e-06</v>
+        <v>-6.110561385893571e-06</v>
       </c>
       <c r="N21">
-        <v>-8.6381259195390145e-06</v>
+        <v>-1.2285942338857328e-05</v>
       </c>
       <c r="O21">
-        <v>4.1519655496266016e-06</v>
+        <v>4.6126928665743164e-06</v>
       </c>
       <c r="P21">
-        <v>-1.9559921153166349e-05</v>
+        <v>-1.2822743613043456e-05</v>
       </c>
       <c r="Q21">
-        <v>-6.7636576269655553e-06</v>
+        <v>-5.5193359418054806e-06</v>
       </c>
       <c r="R21">
-        <v>6.8479165008000864e-06</v>
+        <v>1.0174941497393464e-05</v>
       </c>
       <c r="S21">
-        <v>-4.4244624726818801e-06</v>
+        <v>-1.6509465377052728e-06</v>
       </c>
       <c r="T21">
-        <v>1.285403673742524e-06</v>
+        <v>3.6313079182258825e-06</v>
       </c>
       <c r="U21">
-        <v>6.8306639607071523e-05</v>
+        <v>5.8560093931156922e-05</v>
       </c>
       <c r="V21">
-        <v>0.0010714689164394314</v>
+        <v>0.0011226860874147904</v>
       </c>
       <c r="W21">
-        <v>2.2770166788042257e-05</v>
+        <v>1.2718508345571935e-05</v>
       </c>
     </row>
     <row r="22">
@@ -7200,70 +7200,70 @@
         <v>44</v>
       </c>
       <c r="B22">
-        <v>-3.0546313783400461</v>
+        <v>-2.9914302801842108</v>
       </c>
       <c r="C22">
-        <v>-0.0005376225640889629</v>
+        <v>-0.00051560859631771924</v>
       </c>
       <c r="D22">
-        <v>5.2041780256028574e-06</v>
+        <v>5.1027282669180229e-06</v>
       </c>
       <c r="E22">
-        <v>-0.0034951515357835084</v>
+        <v>-0.0031596309752217316</v>
       </c>
       <c r="F22">
-        <v>-0.0029229828724894602</v>
+        <v>-0.002716288639685099</v>
       </c>
       <c r="G22">
-        <v>7.1608218535988509e-05</v>
+        <v>6.4544112324254916e-05</v>
       </c>
       <c r="H22">
-        <v>5.7525089240895356e-05</v>
+        <v>5.3759915239246632e-05</v>
       </c>
       <c r="I22">
-        <v>0.00056486995841063684</v>
+        <v>0.00017673063316534754</v>
       </c>
       <c r="J22">
-        <v>-0.0027516766328533888</v>
+        <v>0.00061800271623847585</v>
       </c>
       <c r="K22">
-        <v>-0.009656403581416749</v>
+        <v>-0.0076458550531630643</v>
       </c>
       <c r="L22">
-        <v>-0.0096750486755672726</v>
+        <v>-0.0076619075026903684</v>
       </c>
       <c r="M22">
-        <v>-0.0097596644490405057</v>
+        <v>-0.007751660929322811</v>
       </c>
       <c r="N22">
-        <v>-0.010083273930940844</v>
+        <v>-0.0080401891750455576</v>
       </c>
       <c r="O22">
-        <v>-0.00049034256180230287</v>
+        <v>-0.00047283649417752971</v>
       </c>
       <c r="P22">
-        <v>-0.00047616259705704603</v>
+        <v>-0.00047078789341754629</v>
       </c>
       <c r="Q22">
-        <v>-0.00042236919031441638</v>
+        <v>-0.00041325986896345254</v>
       </c>
       <c r="R22">
-        <v>-0.00046510661863207944</v>
+        <v>-0.00046798244563567363</v>
       </c>
       <c r="S22">
-        <v>-0.00043108848861972892</v>
+        <v>-0.00043093230257717726</v>
       </c>
       <c r="T22">
-        <v>-0.00047100216080141189</v>
+        <v>-0.00041903953640824672</v>
       </c>
       <c r="U22">
-        <v>-9.6150934237597866e-05</v>
+        <v>-8.2864152426535042e-05</v>
       </c>
       <c r="V22">
-        <v>2.2770166788042257e-05</v>
+        <v>1.2718508345571935e-05</v>
       </c>
       <c r="W22">
-        <v>0.022916944246539075</v>
+        <v>0.020134109862578915</v>
       </c>
     </row>
   </sheetData>
